--- a/PLAFT/Desarrollo/Minorista_regulado/diccionario_variables.xlsx
+++ b/PLAFT/Desarrollo/Minorista_regulado/diccionario_variables.xlsx
@@ -1,19 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30215"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://interbankpe-my.sharepoint.com/personal/shernandez2_intercorp_com_pe/Documents/PLAFT/PJ/Minorista/New_artefactos/Train/Desarollo/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://interbankpe-my.sharepoint.com/personal/shernandez2_intercorp_com_pe/Documents/PLAFT/Interbank/PLAFT/Desarrollo/Minorista_regulado/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_D4685D6D51B00C8EC238E11B3E10620A61868518" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="114" documentId="11_D4685D6D51B00C8EC238E11B3E10620A61868518" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{401890F3-A291-4395-B8DF-473F2906D5F8}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-1095" windowWidth="29040" windowHeight="15720" xr2:uid="{953A7621-5D67-4682-9C09-2CA2A8669DE6}"/>
   </bookViews>
   <sheets>
-    <sheet name="Hoja2" sheetId="2" r:id="rId1"/>
+    <sheet name="Diccionario" sheetId="2" r:id="rId1"/>
+    <sheet name="Variables finales" sheetId="4" r:id="rId2"/>
+    <sheet name="Modelo" sheetId="5" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -39,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1175" uniqueCount="888">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1452" uniqueCount="926">
   <si>
     <t>TABLA AGREGADA ALERTAS PLAFT - AWS</t>
   </si>
@@ -2703,13 +2705,127 @@
   </si>
   <si>
     <t>Esta variable calcula la relación entre la cantidad de reportes de operaciones sospechosas (ROS) históricos y el número total de transacciones de egresos en los últimos 3 meses. Es un indicador de riesgo asociado a las operaciones recientes.</t>
+  </si>
+  <si>
+    <t>share_cp_egresos</t>
+  </si>
+  <si>
+    <t>ratio_egresos_exterior</t>
+  </si>
+  <si>
+    <t>share_cp_ingresos</t>
+  </si>
+  <si>
+    <t>rat_pastot_x_ingtot_6m</t>
+  </si>
+  <si>
+    <t>rat_ing_tot_x_factura_6m</t>
+  </si>
+  <si>
+    <t>rat_abonos_1m_vs_6m</t>
+  </si>
+  <si>
+    <t>rat_cntros_x_cnttrxegr_3m</t>
+  </si>
+  <si>
+    <t>rat_ing_ext_x_ing_tot_12m</t>
+  </si>
+  <si>
+    <t>cnt_trx_sinenv_alext_12m</t>
+  </si>
+  <si>
+    <t>ESQUEMA</t>
+  </si>
+  <si>
+    <t>TABLA</t>
+  </si>
+  <si>
+    <t>VARIABLE Usuario</t>
+  </si>
+  <si>
+    <t>VARIABLE Dataset</t>
+  </si>
+  <si>
+    <t>TIPO_DATO</t>
+  </si>
+  <si>
+    <t>DESCRIPCION_FUNCIONAL</t>
+  </si>
+  <si>
+    <t>e_perm_aws</t>
+  </si>
+  <si>
+    <t>t_agg_alertas_plaft</t>
+  </si>
+  <si>
+    <t>Periodo de referencia en formato año-mes(YYYYMM).</t>
+  </si>
+  <si>
+    <t>cod_cli</t>
+  </si>
+  <si>
+    <t>cod_tip_doc</t>
+  </si>
+  <si>
+    <t>Número de documento encriptado del cliente, correspondiente al tipo de documento indicado.</t>
+  </si>
+  <si>
+    <t>t_alertas_plaft</t>
+  </si>
+  <si>
+    <t>tipo_alerta_n2</t>
+  </si>
+  <si>
+    <t>tip_alerta</t>
+  </si>
+  <si>
+    <t>Tipo de alerta para el periodo cerrado</t>
+  </si>
+  <si>
+    <t>decimal (38,6)</t>
+  </si>
+  <si>
+    <t>Relación entre el pasivo total en soles y los ingresos totales (abonos) en los últimos 6 meses. Es un indicador de la capacidad de la empresa para cubrir sus pasivos con los ingresos generados.</t>
+  </si>
+  <si>
+    <t>Cantidad de meses, dentro de los últimos 12 meses, en que no se registraron cargos.</t>
+  </si>
+  <si>
+    <t>Este ratio mide la aceleración o desaceleración de los ingresos (abonos) en el último mes en comparación con el promedio mensual de los últimos 6 meses. Es útil para identificar cambios recientes en el comportamiento de ingresos.</t>
+  </si>
+  <si>
+    <t>rat_cnt_alert_x_num_antig</t>
+  </si>
+  <si>
+    <t>rat_cargos_1m_vs_6m</t>
+  </si>
+  <si>
+    <t>Partición de la tabla agregada (YYYYMM)</t>
+  </si>
+  <si>
+    <t>Ratio que mide la concentración de egresos hacia la principal contraparte. Se calcula como el promedio mensual de egresos hacia contrapartes en los últimos 12 meses respecto al monto total de cargos en los últimos 6 meses. Un valor alto indica que el cliente canaliza la mayoría de sus salidas de dinero hacia un único destinatario.</t>
+  </si>
+  <si>
+    <t>Conteo de transacciones sin envío al exterior en los últimos 12 meses</t>
+  </si>
+  <si>
+    <t>rat_egr_ext_x_egr_tot_12m</t>
+  </si>
+  <si>
+    <t>Esta variable mide la proporción de egresos provenientes del exterior en relación con los egresos totales en los últimos 12 meses. Es un indicador de la dependencia de la empresa en egresos internacionales.</t>
+  </si>
+  <si>
+    <t>Ratio que mide la concentración de ingresos hacia la principal contraparte. Se calcula como el promedio mensual de ingresos hacia contrapartes en los últimos 12 meses respecto al monto total de ingresos en los últimos 6 meses. Un valor alto indica que el cliente canaliza la mayoría de sus ingresos de dinero hacia un único destinatario.</t>
+  </si>
+  <si>
+    <t>Cantidad de trx sin envio la exterior en los ultimos 12 meses</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2753,12 +2869,14 @@
       <sz val="10"/>
       <color theme="0"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -2769,6 +2887,7 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -2785,8 +2904,20 @@
       <charset val="1"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2796,12 +2927,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
@@ -2847,8 +2972,32 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0070C0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="12">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -2985,16 +3134,27 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -3007,16 +3167,16 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
@@ -3026,7 +3186,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
@@ -3038,10 +3198,10 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
@@ -3059,7 +3219,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3082,13 +3242,13 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
@@ -3100,20 +3260,58 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="4">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -3474,5334 +3672,5334 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{703CF939-515C-401A-82C6-8C1F712E2F9B}">
-  <dimension ref="A1:H300"/>
-  <sheetFormatPr defaultColWidth="10.85546875" defaultRowHeight="14.45"/>
+  <dimension ref="A1:H302"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="6.42578125" style="6" customWidth="1"/>
-    <col min="2" max="2" width="33.7109375" style="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.5703125" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.28515625" style="5" customWidth="1"/>
-    <col min="5" max="5" width="5" style="6" customWidth="1"/>
-    <col min="6" max="6" width="80" style="6" customWidth="1"/>
-    <col min="7" max="7" width="46.5703125" style="5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="45.140625" style="5" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="10.85546875" style="5"/>
+    <col min="1" max="1" width="6.453125" style="4" customWidth="1"/>
+    <col min="2" max="2" width="33.7265625" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.54296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.26953125" style="3" customWidth="1"/>
+    <col min="5" max="5" width="5" style="4" customWidth="1"/>
+    <col min="6" max="6" width="80" style="4" customWidth="1"/>
+    <col min="7" max="7" width="46.54296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="45.1796875" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="10.81640625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="14.45" customHeight="1">
-      <c r="A1" s="30" t="s">
+    <row r="1" spans="1:8" ht="14.5" customHeight="1">
+      <c r="A1" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="32"/>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="30"/>
     </row>
     <row r="2" spans="1:8" ht="15" customHeight="1" thickBot="1">
-      <c r="A2" s="33"/>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="35"/>
+      <c r="A2" s="31"/>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="33"/>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="36" t="s">
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="37"/>
-      <c r="F4" s="37"/>
-      <c r="G4" s="38"/>
+      <c r="E4" s="35"/>
+      <c r="F4" s="35"/>
+      <c r="G4" s="36"/>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="39" t="s">
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="40"/>
-      <c r="F5" s="40"/>
-      <c r="G5" s="41"/>
+      <c r="E5" s="38"/>
+      <c r="F5" s="38"/>
+      <c r="G5" s="39"/>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="8"/>
-      <c r="B6" s="9" t="s">
+      <c r="A6" s="6"/>
+      <c r="B6" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="42" t="s">
+      <c r="C6" s="40" t="s">
         <v>6</v>
       </c>
-      <c r="D6" s="43"/>
-      <c r="E6" s="43"/>
-      <c r="F6" s="43"/>
-      <c r="G6" s="44"/>
+      <c r="D6" s="41"/>
+      <c r="E6" s="41"/>
+      <c r="F6" s="41"/>
+      <c r="G6" s="42"/>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="10" t="s">
+      <c r="A7" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="C7" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="D7" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E7" s="12" t="s">
+      <c r="E7" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="F7" s="12" t="s">
+      <c r="F7" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="G7" s="12" t="s">
+      <c r="G7" s="10" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="13">
+      <c r="A8" s="11">
         <v>1</v>
       </c>
-      <c r="B8" s="14" t="s">
+      <c r="B8" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="15" t="s">
+      <c r="C8" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="D8" s="15" t="s">
+      <c r="D8" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E8" s="16"/>
-      <c r="F8" s="17" t="s">
+      <c r="E8" s="14"/>
+      <c r="F8" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="G8" s="18"/>
-      <c r="H8" s="19"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="17"/>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="13">
+      <c r="A9" s="11">
         <v>2</v>
       </c>
-      <c r="B9" s="14" t="s">
+      <c r="B9" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="15" t="s">
+      <c r="C9" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="D9" s="15" t="s">
+      <c r="D9" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E9" s="13" t="s">
+      <c r="E9" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="F9" s="17" t="s">
+      <c r="F9" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="G9" s="18"/>
-      <c r="H9" s="19"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="17"/>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="13">
+      <c r="A10" s="11">
         <v>3</v>
       </c>
-      <c r="B10" s="14" t="s">
+      <c r="B10" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="15" t="s">
+      <c r="C10" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="15" t="s">
+      <c r="D10" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E10" s="13" t="s">
+      <c r="E10" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="F10" s="17" t="s">
+      <c r="F10" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="G10" s="18"/>
+      <c r="G10" s="16"/>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="13">
+      <c r="A11" s="11">
         <v>4</v>
       </c>
-      <c r="B11" s="14" t="s">
+      <c r="B11" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="15" t="s">
+      <c r="C11" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="D11" s="15" t="s">
+      <c r="D11" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E11" s="13" t="s">
+      <c r="E11" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="F11" s="17" t="s">
+      <c r="F11" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="G11" s="18"/>
-      <c r="H11" s="19"/>
+      <c r="G11" s="16"/>
+      <c r="H11" s="17"/>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="13">
+      <c r="A12" s="11">
         <v>5</v>
       </c>
-      <c r="B12" s="14" t="s">
+      <c r="B12" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="C12" s="15" t="s">
+      <c r="C12" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="D12" s="15" t="s">
+      <c r="D12" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E12" s="16"/>
-      <c r="F12" s="17" t="s">
+      <c r="E12" s="14"/>
+      <c r="F12" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="G12" s="18"/>
+      <c r="G12" s="16"/>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="13">
+      <c r="A13" s="11">
         <v>6</v>
       </c>
-      <c r="B13" s="14" t="s">
+      <c r="B13" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="15" t="s">
+      <c r="C13" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="D13" s="15" t="s">
+      <c r="D13" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="E13" s="16"/>
-      <c r="F13" s="17" t="s">
+      <c r="E13" s="14"/>
+      <c r="F13" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="G13" s="18"/>
+      <c r="G13" s="16"/>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14" s="13">
+      <c r="A14" s="11">
         <v>7</v>
       </c>
-      <c r="B14" s="14" t="s">
+      <c r="B14" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="C14" s="15" t="s">
+      <c r="C14" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="D14" s="15" t="s">
+      <c r="D14" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="E14" s="16"/>
-      <c r="F14" s="17" t="s">
+      <c r="E14" s="14"/>
+      <c r="F14" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="G14" s="18"/>
+      <c r="G14" s="16"/>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="13">
+      <c r="A15" s="11">
         <v>8</v>
       </c>
-      <c r="B15" s="14" t="s">
+      <c r="B15" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="C15" s="15" t="s">
+      <c r="C15" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="D15" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E15" s="16"/>
-      <c r="F15" s="17" t="s">
+      <c r="D15" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E15" s="14"/>
+      <c r="F15" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="G15" s="18"/>
+      <c r="G15" s="16"/>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="13">
+      <c r="A16" s="11">
         <v>9</v>
       </c>
-      <c r="B16" s="14" t="s">
+      <c r="B16" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="C16" s="15" t="s">
+      <c r="C16" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="D16" s="15" t="s">
+      <c r="D16" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E16" s="16"/>
-      <c r="F16" s="17" t="s">
+      <c r="E16" s="14"/>
+      <c r="F16" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="G16" s="18"/>
+      <c r="G16" s="16"/>
     </row>
     <row r="17" spans="1:8">
-      <c r="A17" s="13">
+      <c r="A17" s="11">
         <v>10</v>
       </c>
-      <c r="B17" s="14" t="s">
+      <c r="B17" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="C17" s="15" t="s">
+      <c r="C17" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="D17" s="15" t="s">
+      <c r="D17" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="E17" s="16"/>
-      <c r="F17" s="17" t="s">
+      <c r="E17" s="14"/>
+      <c r="F17" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="G17" s="18"/>
+      <c r="G17" s="16"/>
     </row>
     <row r="18" spans="1:8">
-      <c r="A18" s="13">
+      <c r="A18" s="11">
         <v>11</v>
       </c>
-      <c r="B18" s="14" t="s">
+      <c r="B18" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="C18" s="15" t="s">
+      <c r="C18" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="D18" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E18" s="16"/>
-      <c r="F18" s="17" t="s">
+      <c r="D18" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E18" s="14"/>
+      <c r="F18" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="G18" s="18"/>
+      <c r="G18" s="16"/>
     </row>
     <row r="19" spans="1:8">
-      <c r="A19" s="13">
+      <c r="A19" s="11">
         <v>12</v>
       </c>
-      <c r="B19" s="14" t="s">
+      <c r="B19" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="C19" s="15" t="s">
+      <c r="C19" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="D19" s="15" t="s">
+      <c r="D19" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E19" s="16"/>
-      <c r="F19" s="17" t="s">
+      <c r="E19" s="14"/>
+      <c r="F19" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="G19" s="18"/>
+      <c r="G19" s="16"/>
     </row>
     <row r="20" spans="1:8">
-      <c r="A20" s="13">
+      <c r="A20" s="11">
         <v>13</v>
       </c>
-      <c r="B20" s="14" t="s">
+      <c r="B20" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="C20" s="15" t="s">
+      <c r="C20" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="D20" s="15" t="s">
+      <c r="D20" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E20" s="16"/>
-      <c r="F20" s="17" t="s">
+      <c r="E20" s="14"/>
+      <c r="F20" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="G20" s="18"/>
+      <c r="G20" s="16"/>
     </row>
     <row r="21" spans="1:8">
-      <c r="A21" s="13">
+      <c r="A21" s="11">
         <v>14</v>
       </c>
-      <c r="B21" s="14" t="s">
+      <c r="B21" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="C21" s="15" t="s">
+      <c r="C21" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="D21" s="15" t="s">
+      <c r="D21" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E21" s="16"/>
-      <c r="F21" s="20" t="s">
+      <c r="E21" s="14"/>
+      <c r="F21" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="G21" s="18"/>
+      <c r="G21" s="16"/>
     </row>
     <row r="22" spans="1:8">
-      <c r="A22" s="13">
+      <c r="A22" s="11">
         <v>15</v>
       </c>
-      <c r="B22" s="14" t="s">
+      <c r="B22" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="C22" s="15" t="s">
+      <c r="C22" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="D22" s="15" t="s">
+      <c r="D22" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E22" s="16"/>
-      <c r="F22" s="21" t="s">
+      <c r="E22" s="14"/>
+      <c r="F22" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="G22" s="18"/>
+      <c r="G22" s="16"/>
     </row>
     <row r="23" spans="1:8">
-      <c r="A23" s="13">
+      <c r="A23" s="11">
         <v>16</v>
       </c>
-      <c r="B23" s="14" t="s">
+      <c r="B23" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="C23" s="15" t="s">
+      <c r="C23" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="D23" s="15" t="s">
+      <c r="D23" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E23" s="16"/>
-      <c r="F23" s="20" t="s">
+      <c r="E23" s="14"/>
+      <c r="F23" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="G23" s="18"/>
+      <c r="G23" s="16"/>
     </row>
     <row r="24" spans="1:8">
-      <c r="A24" s="13">
+      <c r="A24" s="11">
         <v>17</v>
       </c>
-      <c r="B24" s="14" t="s">
+      <c r="B24" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="C24" s="15" t="s">
+      <c r="C24" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="D24" s="15" t="s">
+      <c r="D24" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="E24" s="16"/>
-      <c r="F24" s="17" t="s">
+      <c r="E24" s="14"/>
+      <c r="F24" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="G24" s="22"/>
+      <c r="G24" s="20"/>
     </row>
     <row r="25" spans="1:8">
-      <c r="A25" s="13">
+      <c r="A25" s="11">
         <v>18</v>
       </c>
-      <c r="B25" s="14" t="s">
+      <c r="B25" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="C25" s="15" t="s">
+      <c r="C25" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="D25" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E25" s="16"/>
-      <c r="F25" s="20" t="s">
+      <c r="D25" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E25" s="14"/>
+      <c r="F25" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="G25" s="18"/>
+      <c r="G25" s="16"/>
     </row>
     <row r="26" spans="1:8">
-      <c r="A26" s="13">
+      <c r="A26" s="11">
         <v>19</v>
       </c>
-      <c r="B26" s="14" t="s">
+      <c r="B26" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="C26" s="15" t="s">
+      <c r="C26" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="D26" s="15" t="s">
+      <c r="D26" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E26" s="16"/>
-      <c r="F26" s="20" t="s">
+      <c r="E26" s="14"/>
+      <c r="F26" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="G26" s="18"/>
+      <c r="G26" s="16"/>
     </row>
     <row r="27" spans="1:8">
-      <c r="A27" s="13">
+      <c r="A27" s="11">
         <v>20</v>
       </c>
-      <c r="B27" s="14" t="s">
+      <c r="B27" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="C27" s="15" t="s">
+      <c r="C27" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="D27" s="15" t="s">
+      <c r="D27" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E27" s="16"/>
-      <c r="F27" s="20" t="s">
+      <c r="E27" s="14"/>
+      <c r="F27" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="G27" s="18"/>
+      <c r="G27" s="16"/>
     </row>
     <row r="28" spans="1:8">
-      <c r="A28" s="13">
+      <c r="A28" s="11">
         <v>21</v>
       </c>
-      <c r="B28" s="14" t="s">
+      <c r="B28" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="C28" s="15" t="s">
+      <c r="C28" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="D28" s="15" t="s">
+      <c r="D28" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E28" s="16"/>
-      <c r="F28" s="20" t="s">
+      <c r="E28" s="14"/>
+      <c r="F28" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="G28" s="18"/>
-      <c r="H28" s="19"/>
+      <c r="G28" s="16"/>
+      <c r="H28" s="17"/>
     </row>
     <row r="29" spans="1:8">
-      <c r="A29" s="13">
+      <c r="A29" s="11">
         <v>22</v>
       </c>
-      <c r="B29" s="14" t="s">
+      <c r="B29" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="C29" s="15" t="s">
+      <c r="C29" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="D29" s="15" t="s">
+      <c r="D29" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E29" s="16"/>
-      <c r="F29" s="20" t="s">
+      <c r="E29" s="14"/>
+      <c r="F29" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="G29" s="18"/>
+      <c r="G29" s="16"/>
     </row>
     <row r="30" spans="1:8">
-      <c r="A30" s="13">
+      <c r="A30" s="11">
         <v>23</v>
       </c>
-      <c r="B30" s="14" t="s">
+      <c r="B30" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="C30" s="15" t="s">
+      <c r="C30" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="D30" s="15" t="s">
+      <c r="D30" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E30" s="16"/>
-      <c r="F30" s="20" t="s">
+      <c r="E30" s="14"/>
+      <c r="F30" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="G30" s="18"/>
+      <c r="G30" s="16"/>
     </row>
     <row r="31" spans="1:8">
-      <c r="A31" s="13">
+      <c r="A31" s="11">
         <v>24</v>
       </c>
-      <c r="B31" s="14" t="s">
+      <c r="B31" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="C31" s="17" t="s">
+      <c r="C31" s="15" t="s">
         <v>87</v>
       </c>
-      <c r="D31" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E31" s="16"/>
-      <c r="F31" s="20" t="s">
+      <c r="D31" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E31" s="14"/>
+      <c r="F31" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="G31" s="22"/>
+      <c r="G31" s="20"/>
     </row>
     <row r="32" spans="1:8">
-      <c r="A32" s="13">
+      <c r="A32" s="11">
         <v>25</v>
       </c>
-      <c r="B32" s="14" t="s">
+      <c r="B32" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="C32" s="17" t="s">
+      <c r="C32" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="D32" s="15" t="s">
+      <c r="D32" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E32" s="16"/>
-      <c r="F32" s="20" t="s">
+      <c r="E32" s="14"/>
+      <c r="F32" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="G32" s="23"/>
+      <c r="G32" s="21"/>
     </row>
     <row r="33" spans="1:7">
-      <c r="A33" s="13">
+      <c r="A33" s="11">
         <v>26</v>
       </c>
-      <c r="B33" s="14" t="s">
+      <c r="B33" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="C33" s="15" t="s">
+      <c r="C33" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="D33" s="15" t="s">
+      <c r="D33" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E33" s="16"/>
-      <c r="F33" s="20" t="s">
+      <c r="E33" s="14"/>
+      <c r="F33" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="G33" s="24"/>
+      <c r="G33" s="22"/>
     </row>
     <row r="34" spans="1:7">
-      <c r="A34" s="13">
+      <c r="A34" s="11">
         <v>27</v>
       </c>
-      <c r="B34" s="14" t="s">
+      <c r="B34" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="C34" s="15" t="s">
+      <c r="C34" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="D34" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E34" s="16"/>
-      <c r="F34" s="25" t="s">
+      <c r="D34" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E34" s="14"/>
+      <c r="F34" s="23" t="s">
         <v>98</v>
       </c>
-      <c r="G34" s="18"/>
+      <c r="G34" s="16"/>
     </row>
     <row r="35" spans="1:7">
-      <c r="A35" s="13">
+      <c r="A35" s="11">
         <v>28</v>
       </c>
-      <c r="B35" s="14" t="s">
+      <c r="B35" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="C35" s="15" t="s">
+      <c r="C35" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="D35" s="15" t="s">
+      <c r="D35" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E35" s="16"/>
-      <c r="F35" s="25" t="s">
+      <c r="E35" s="14"/>
+      <c r="F35" s="23" t="s">
         <v>101</v>
       </c>
-      <c r="G35" s="18"/>
+      <c r="G35" s="16"/>
     </row>
     <row r="36" spans="1:7">
-      <c r="A36" s="13">
+      <c r="A36" s="11">
         <v>29</v>
       </c>
-      <c r="B36" s="14" t="s">
+      <c r="B36" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="C36" s="15" t="s">
+      <c r="C36" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="D36" s="15" t="s">
+      <c r="D36" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E36" s="16"/>
-      <c r="F36" s="17" t="s">
+      <c r="E36" s="14"/>
+      <c r="F36" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="G36" s="18"/>
+      <c r="G36" s="16"/>
     </row>
     <row r="37" spans="1:7">
-      <c r="A37" s="13">
+      <c r="A37" s="11">
         <v>30</v>
       </c>
-      <c r="B37" s="14" t="s">
+      <c r="B37" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="C37" s="15" t="s">
+      <c r="C37" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="D37" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E37" s="16"/>
-      <c r="F37" s="17" t="s">
+      <c r="D37" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E37" s="14"/>
+      <c r="F37" s="15" t="s">
         <v>107</v>
       </c>
-      <c r="G37" s="18"/>
+      <c r="G37" s="16"/>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="13">
+      <c r="A38" s="11">
         <v>31</v>
       </c>
-      <c r="B38" s="14" t="s">
+      <c r="B38" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="C38" s="15" t="s">
+      <c r="C38" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="D38" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E38" s="16"/>
-      <c r="F38" s="21" t="s">
+      <c r="D38" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E38" s="14"/>
+      <c r="F38" s="19" t="s">
         <v>110</v>
       </c>
-      <c r="G38" s="18"/>
+      <c r="G38" s="16"/>
     </row>
     <row r="39" spans="1:7">
-      <c r="A39" s="13">
+      <c r="A39" s="11">
         <v>32</v>
       </c>
-      <c r="B39" s="14" t="s">
+      <c r="B39" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="C39" s="15" t="s">
+      <c r="C39" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="D39" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E39" s="16"/>
-      <c r="F39" s="17" t="s">
+      <c r="D39" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E39" s="14"/>
+      <c r="F39" s="15" t="s">
         <v>113</v>
       </c>
-      <c r="G39" s="18"/>
+      <c r="G39" s="16"/>
     </row>
     <row r="40" spans="1:7">
-      <c r="A40" s="13">
+      <c r="A40" s="11">
         <v>33</v>
       </c>
-      <c r="B40" s="14" t="s">
+      <c r="B40" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="C40" s="15" t="s">
+      <c r="C40" s="13" t="s">
         <v>115</v>
       </c>
-      <c r="D40" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E40" s="16"/>
-      <c r="F40" s="21" t="s">
+      <c r="D40" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E40" s="14"/>
+      <c r="F40" s="19" t="s">
         <v>116</v>
       </c>
-      <c r="G40" s="18"/>
+      <c r="G40" s="16"/>
     </row>
     <row r="41" spans="1:7">
-      <c r="A41" s="13">
+      <c r="A41" s="11">
         <v>34</v>
       </c>
-      <c r="B41" s="14" t="s">
+      <c r="B41" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="C41" s="15" t="s">
+      <c r="C41" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="D41" s="15" t="s">
+      <c r="D41" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E41" s="16"/>
-      <c r="F41" s="20" t="s">
+      <c r="E41" s="14"/>
+      <c r="F41" s="18" t="s">
         <v>119</v>
       </c>
-      <c r="G41" s="18"/>
+      <c r="G41" s="16"/>
     </row>
     <row r="42" spans="1:7">
-      <c r="A42" s="13">
+      <c r="A42" s="11">
         <v>35</v>
       </c>
-      <c r="B42" s="14" t="s">
+      <c r="B42" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="C42" s="15" t="s">
+      <c r="C42" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="D42" s="15" t="s">
+      <c r="D42" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E42" s="16"/>
-      <c r="F42" s="17" t="s">
+      <c r="E42" s="14"/>
+      <c r="F42" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="G42" s="18"/>
+      <c r="G42" s="16"/>
     </row>
     <row r="43" spans="1:7">
-      <c r="A43" s="13">
+      <c r="A43" s="11">
         <v>36</v>
       </c>
-      <c r="B43" s="14" t="s">
+      <c r="B43" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="C43" s="15" t="s">
+      <c r="C43" s="13" t="s">
         <v>124</v>
       </c>
-      <c r="D43" s="15" t="s">
+      <c r="D43" s="13" t="s">
         <v>125</v>
       </c>
-      <c r="E43" s="16"/>
-      <c r="F43" s="17" t="s">
+      <c r="E43" s="14"/>
+      <c r="F43" s="15" t="s">
         <v>126</v>
       </c>
-      <c r="G43" s="18"/>
+      <c r="G43" s="16"/>
     </row>
     <row r="44" spans="1:7">
-      <c r="A44" s="13">
+      <c r="A44" s="11">
         <v>37</v>
       </c>
-      <c r="B44" s="14" t="s">
+      <c r="B44" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="C44" s="15" t="s">
+      <c r="C44" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="D44" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E44" s="16"/>
-      <c r="F44" s="17" t="s">
+      <c r="D44" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E44" s="14"/>
+      <c r="F44" s="15" t="s">
         <v>129</v>
       </c>
-      <c r="G44" s="18"/>
+      <c r="G44" s="16"/>
     </row>
     <row r="45" spans="1:7">
-      <c r="A45" s="13">
+      <c r="A45" s="11">
         <v>38</v>
       </c>
-      <c r="B45" s="14" t="s">
+      <c r="B45" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="C45" s="15" t="s">
+      <c r="C45" s="13" t="s">
         <v>131</v>
       </c>
-      <c r="D45" s="15" t="s">
+      <c r="D45" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E45" s="16"/>
-      <c r="F45" s="21" t="s">
+      <c r="E45" s="14"/>
+      <c r="F45" s="19" t="s">
         <v>132</v>
       </c>
-      <c r="G45" s="22"/>
+      <c r="G45" s="20"/>
     </row>
     <row r="46" spans="1:7">
-      <c r="A46" s="13">
-        <v>39</v>
-      </c>
-      <c r="B46" s="14" t="s">
+      <c r="A46" s="11">
+        <v>39</v>
+      </c>
+      <c r="B46" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="C46" s="15" t="s">
+      <c r="C46" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="D46" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E46" s="16"/>
-      <c r="F46" s="17" t="s">
+      <c r="D46" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E46" s="14"/>
+      <c r="F46" s="15" t="s">
         <v>135</v>
       </c>
-      <c r="G46" s="22"/>
+      <c r="G46" s="20"/>
     </row>
     <row r="47" spans="1:7">
-      <c r="A47" s="13">
+      <c r="A47" s="11">
         <v>40</v>
       </c>
-      <c r="B47" s="14" t="s">
+      <c r="B47" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="C47" s="15" t="s">
+      <c r="C47" s="13" t="s">
         <v>137</v>
       </c>
-      <c r="D47" s="15" t="s">
+      <c r="D47" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E47" s="16"/>
-      <c r="F47" s="17" t="s">
+      <c r="E47" s="14"/>
+      <c r="F47" s="15" t="s">
         <v>138</v>
       </c>
-      <c r="G47" s="18"/>
+      <c r="G47" s="16"/>
     </row>
     <row r="48" spans="1:7">
-      <c r="A48" s="13">
+      <c r="A48" s="11">
         <v>41</v>
       </c>
-      <c r="B48" s="14" t="s">
+      <c r="B48" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="C48" s="15" t="s">
+      <c r="C48" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="D48" s="15" t="s">
+      <c r="D48" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E48" s="16"/>
-      <c r="F48" s="20" t="s">
+      <c r="E48" s="14"/>
+      <c r="F48" s="18" t="s">
         <v>141</v>
       </c>
-      <c r="G48" s="22"/>
+      <c r="G48" s="20"/>
     </row>
     <row r="49" spans="1:8">
-      <c r="A49" s="13">
+      <c r="A49" s="11">
         <v>42</v>
       </c>
-      <c r="B49" s="14" t="s">
+      <c r="B49" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="C49" s="15" t="s">
+      <c r="C49" s="13" t="s">
         <v>143</v>
       </c>
-      <c r="D49" s="15" t="s">
+      <c r="D49" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E49" s="16"/>
-      <c r="F49" s="20" t="s">
+      <c r="E49" s="14"/>
+      <c r="F49" s="18" t="s">
         <v>144</v>
       </c>
-      <c r="G49" s="18"/>
+      <c r="G49" s="16"/>
     </row>
     <row r="50" spans="1:8">
-      <c r="A50" s="13">
+      <c r="A50" s="11">
         <v>43</v>
       </c>
-      <c r="B50" s="14" t="s">
+      <c r="B50" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="C50" s="15" t="s">
+      <c r="C50" s="13" t="s">
         <v>146</v>
       </c>
-      <c r="D50" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E50" s="16"/>
-      <c r="F50" s="17" t="s">
+      <c r="D50" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E50" s="14"/>
+      <c r="F50" s="15" t="s">
         <v>147</v>
       </c>
-      <c r="G50" s="23"/>
+      <c r="G50" s="21"/>
     </row>
     <row r="51" spans="1:8">
-      <c r="A51" s="13">
+      <c r="A51" s="11">
         <v>44</v>
       </c>
-      <c r="B51" s="14" t="s">
+      <c r="B51" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="C51" s="15" t="s">
+      <c r="C51" s="13" t="s">
         <v>149</v>
       </c>
-      <c r="D51" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E51" s="16"/>
-      <c r="F51" s="17" t="s">
+      <c r="D51" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E51" s="14"/>
+      <c r="F51" s="15" t="s">
         <v>150</v>
       </c>
-      <c r="G51" s="26"/>
+      <c r="G51" s="24"/>
     </row>
     <row r="52" spans="1:8">
-      <c r="A52" s="13">
+      <c r="A52" s="11">
         <v>45</v>
       </c>
-      <c r="B52" s="14" t="s">
+      <c r="B52" s="12" t="s">
         <v>151</v>
       </c>
-      <c r="C52" s="15" t="s">
+      <c r="C52" s="13" t="s">
         <v>152</v>
       </c>
-      <c r="D52" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E52" s="16"/>
-      <c r="F52" s="21" t="s">
+      <c r="D52" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E52" s="14"/>
+      <c r="F52" s="19" t="s">
         <v>153</v>
       </c>
-      <c r="G52" s="18"/>
+      <c r="G52" s="16"/>
     </row>
     <row r="53" spans="1:8">
-      <c r="A53" s="13">
+      <c r="A53" s="11">
         <v>46</v>
       </c>
-      <c r="B53" s="14" t="s">
+      <c r="B53" s="12" t="s">
         <v>154</v>
       </c>
-      <c r="C53" s="17" t="s">
+      <c r="C53" s="15" t="s">
         <v>155</v>
       </c>
-      <c r="D53" s="15" t="s">
+      <c r="D53" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E53" s="16"/>
-      <c r="F53" s="17" t="s">
+      <c r="E53" s="14"/>
+      <c r="F53" s="15" t="s">
         <v>156</v>
       </c>
-      <c r="G53" s="23"/>
+      <c r="G53" s="21"/>
     </row>
     <row r="54" spans="1:8">
-      <c r="A54" s="13">
+      <c r="A54" s="11">
         <v>47</v>
       </c>
-      <c r="B54" s="14" t="s">
+      <c r="B54" s="12" t="s">
         <v>157</v>
       </c>
-      <c r="C54" s="15" t="s">
+      <c r="C54" s="13" t="s">
         <v>158</v>
       </c>
-      <c r="D54" s="15" t="s">
+      <c r="D54" s="13" t="s">
         <v>125</v>
       </c>
-      <c r="E54" s="16"/>
-      <c r="F54" s="20" t="s">
+      <c r="E54" s="14"/>
+      <c r="F54" s="18" t="s">
         <v>159</v>
       </c>
-      <c r="G54" s="26"/>
+      <c r="G54" s="24"/>
     </row>
     <row r="55" spans="1:8">
-      <c r="A55" s="13">
+      <c r="A55" s="11">
         <v>48</v>
       </c>
-      <c r="B55" s="14" t="s">
+      <c r="B55" s="12" t="s">
         <v>160</v>
       </c>
-      <c r="C55" s="15" t="s">
+      <c r="C55" s="13" t="s">
         <v>161</v>
       </c>
-      <c r="D55" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E55" s="16"/>
-      <c r="F55" s="20" t="s">
+      <c r="D55" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E55" s="14"/>
+      <c r="F55" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="G55" s="18"/>
-      <c r="H55" s="19"/>
+      <c r="G55" s="16"/>
+      <c r="H55" s="17"/>
     </row>
     <row r="56" spans="1:8">
-      <c r="A56" s="13">
+      <c r="A56" s="11">
         <v>49</v>
       </c>
-      <c r="B56" s="14" t="s">
+      <c r="B56" s="12" t="s">
         <v>163</v>
       </c>
-      <c r="C56" s="17" t="s">
+      <c r="C56" s="15" t="s">
         <v>164</v>
       </c>
-      <c r="D56" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E56" s="16"/>
-      <c r="F56" s="20" t="s">
+      <c r="D56" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E56" s="14"/>
+      <c r="F56" s="18" t="s">
         <v>165</v>
       </c>
-      <c r="G56" s="23"/>
+      <c r="G56" s="21"/>
     </row>
     <row r="57" spans="1:8">
-      <c r="A57" s="13">
+      <c r="A57" s="11">
         <v>50</v>
       </c>
-      <c r="B57" s="14" t="s">
+      <c r="B57" s="12" t="s">
         <v>166</v>
       </c>
-      <c r="C57" s="17" t="s">
+      <c r="C57" s="15" t="s">
         <v>167</v>
       </c>
-      <c r="D57" s="15" t="s">
+      <c r="D57" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E57" s="16"/>
-      <c r="F57" s="17" t="s">
+      <c r="E57" s="14"/>
+      <c r="F57" s="15" t="s">
         <v>168</v>
       </c>
-      <c r="G57" s="18"/>
+      <c r="G57" s="16"/>
     </row>
     <row r="58" spans="1:8">
-      <c r="A58" s="13">
+      <c r="A58" s="11">
         <v>51</v>
       </c>
-      <c r="B58" s="14" t="s">
+      <c r="B58" s="12" t="s">
         <v>169</v>
       </c>
-      <c r="C58" s="17" t="s">
+      <c r="C58" s="15" t="s">
         <v>170</v>
       </c>
-      <c r="D58" s="15" t="s">
+      <c r="D58" s="13" t="s">
         <v>125</v>
       </c>
-      <c r="E58" s="16"/>
-      <c r="F58" s="20" t="s">
+      <c r="E58" s="14"/>
+      <c r="F58" s="18" t="s">
         <v>171</v>
       </c>
-      <c r="G58" s="18"/>
+      <c r="G58" s="16"/>
     </row>
     <row r="59" spans="1:8">
-      <c r="A59" s="13">
+      <c r="A59" s="11">
         <v>52</v>
       </c>
-      <c r="B59" s="14" t="s">
+      <c r="B59" s="12" t="s">
         <v>172</v>
       </c>
-      <c r="C59" s="17" t="s">
+      <c r="C59" s="15" t="s">
         <v>173</v>
       </c>
-      <c r="D59" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E59" s="16"/>
-      <c r="F59" s="20" t="s">
+      <c r="D59" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E59" s="14"/>
+      <c r="F59" s="18" t="s">
         <v>174</v>
       </c>
-      <c r="G59" s="18"/>
+      <c r="G59" s="16"/>
     </row>
     <row r="60" spans="1:8">
-      <c r="A60" s="13">
+      <c r="A60" s="11">
         <v>53</v>
       </c>
-      <c r="B60" s="14" t="s">
+      <c r="B60" s="12" t="s">
         <v>175</v>
       </c>
-      <c r="C60" s="17" t="s">
+      <c r="C60" s="15" t="s">
         <v>176</v>
       </c>
-      <c r="D60" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E60" s="16"/>
-      <c r="F60" s="27" t="s">
+      <c r="D60" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E60" s="14"/>
+      <c r="F60" s="25" t="s">
         <v>177</v>
       </c>
-      <c r="G60" s="23"/>
+      <c r="G60" s="21"/>
     </row>
     <row r="61" spans="1:8">
-      <c r="A61" s="13">
+      <c r="A61" s="11">
         <v>54</v>
       </c>
-      <c r="B61" s="14" t="s">
+      <c r="B61" s="12" t="s">
         <v>178</v>
       </c>
-      <c r="C61" s="17" t="s">
+      <c r="C61" s="15" t="s">
         <v>179</v>
       </c>
-      <c r="D61" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E61" s="16"/>
-      <c r="F61" s="20" t="s">
+      <c r="D61" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E61" s="14"/>
+      <c r="F61" s="18" t="s">
         <v>180</v>
       </c>
-      <c r="G61" s="18"/>
+      <c r="G61" s="16"/>
     </row>
     <row r="62" spans="1:8">
-      <c r="A62" s="13">
+      <c r="A62" s="11">
         <v>55</v>
       </c>
-      <c r="B62" s="14" t="s">
+      <c r="B62" s="12" t="s">
         <v>181</v>
       </c>
-      <c r="C62" s="17" t="s">
+      <c r="C62" s="15" t="s">
         <v>182</v>
       </c>
-      <c r="D62" s="15" t="s">
+      <c r="D62" s="13" t="s">
         <v>125</v>
       </c>
-      <c r="E62" s="16"/>
-      <c r="F62" s="17" t="s">
+      <c r="E62" s="14"/>
+      <c r="F62" s="15" t="s">
         <v>183</v>
       </c>
-      <c r="G62" s="18"/>
+      <c r="G62" s="16"/>
     </row>
     <row r="63" spans="1:8">
-      <c r="A63" s="13">
+      <c r="A63" s="11">
         <v>56</v>
       </c>
-      <c r="B63" s="14" t="s">
+      <c r="B63" s="12" t="s">
         <v>184</v>
       </c>
-      <c r="C63" s="17" t="s">
+      <c r="C63" s="15" t="s">
         <v>185</v>
       </c>
-      <c r="D63" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E63" s="16"/>
-      <c r="F63" s="17" t="s">
+      <c r="D63" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E63" s="14"/>
+      <c r="F63" s="15" t="s">
         <v>186</v>
       </c>
-      <c r="G63" s="18"/>
+      <c r="G63" s="16"/>
     </row>
     <row r="64" spans="1:8">
-      <c r="A64" s="13">
+      <c r="A64" s="11">
         <v>57</v>
       </c>
-      <c r="B64" s="14" t="s">
+      <c r="B64" s="12" t="s">
         <v>187</v>
       </c>
-      <c r="C64" s="17" t="s">
+      <c r="C64" s="15" t="s">
         <v>188</v>
       </c>
-      <c r="D64" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E64" s="16"/>
-      <c r="F64" s="17" t="s">
+      <c r="D64" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E64" s="14"/>
+      <c r="F64" s="15" t="s">
         <v>189</v>
       </c>
-      <c r="G64" s="18"/>
+      <c r="G64" s="16"/>
     </row>
     <row r="65" spans="1:7">
-      <c r="A65" s="13">
+      <c r="A65" s="11">
         <v>58</v>
       </c>
-      <c r="B65" s="14" t="s">
+      <c r="B65" s="12" t="s">
         <v>190</v>
       </c>
-      <c r="C65" s="17" t="s">
+      <c r="C65" s="15" t="s">
         <v>191</v>
       </c>
-      <c r="D65" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E65" s="16"/>
-      <c r="F65" s="17" t="s">
+      <c r="D65" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E65" s="14"/>
+      <c r="F65" s="15" t="s">
         <v>192</v>
       </c>
-      <c r="G65" s="18"/>
+      <c r="G65" s="16"/>
     </row>
     <row r="66" spans="1:7">
-      <c r="A66" s="13">
+      <c r="A66" s="11">
         <v>59</v>
       </c>
-      <c r="B66" s="14" t="s">
+      <c r="B66" s="12" t="s">
         <v>193</v>
       </c>
-      <c r="C66" s="15" t="s">
+      <c r="C66" s="13" t="s">
         <v>194</v>
       </c>
-      <c r="D66" s="15" t="s">
+      <c r="D66" s="13" t="s">
         <v>125</v>
       </c>
-      <c r="E66" s="16"/>
-      <c r="F66" s="25" t="s">
+      <c r="E66" s="14"/>
+      <c r="F66" s="23" t="s">
         <v>195</v>
       </c>
-      <c r="G66" s="18"/>
+      <c r="G66" s="16"/>
     </row>
     <row r="67" spans="1:7">
-      <c r="A67" s="13">
+      <c r="A67" s="11">
         <v>60</v>
       </c>
-      <c r="B67" s="14" t="s">
+      <c r="B67" s="12" t="s">
         <v>196</v>
       </c>
-      <c r="C67" s="15" t="s">
+      <c r="C67" s="13" t="s">
         <v>197</v>
       </c>
-      <c r="D67" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E67" s="16"/>
-      <c r="F67" s="25" t="s">
+      <c r="D67" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E67" s="14"/>
+      <c r="F67" s="23" t="s">
         <v>198</v>
       </c>
-      <c r="G67" s="23"/>
+      <c r="G67" s="21"/>
     </row>
     <row r="68" spans="1:7">
-      <c r="A68" s="13">
+      <c r="A68" s="11">
         <v>61</v>
       </c>
-      <c r="B68" s="14" t="s">
+      <c r="B68" s="12" t="s">
         <v>199</v>
       </c>
-      <c r="C68" s="15" t="s">
+      <c r="C68" s="13" t="s">
         <v>200</v>
       </c>
-      <c r="D68" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E68" s="16"/>
-      <c r="F68" s="21" t="s">
+      <c r="D68" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E68" s="14"/>
+      <c r="F68" s="19" t="s">
         <v>201</v>
       </c>
-      <c r="G68" s="18"/>
+      <c r="G68" s="16"/>
     </row>
     <row r="69" spans="1:7">
-      <c r="A69" s="13">
+      <c r="A69" s="11">
         <v>62</v>
       </c>
-      <c r="B69" s="14" t="s">
+      <c r="B69" s="12" t="s">
         <v>202</v>
       </c>
-      <c r="C69" s="15" t="s">
+      <c r="C69" s="13" t="s">
         <v>203</v>
       </c>
-      <c r="D69" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E69" s="16"/>
-      <c r="F69" s="21" t="s">
+      <c r="D69" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E69" s="14"/>
+      <c r="F69" s="19" t="s">
         <v>204</v>
       </c>
-      <c r="G69" s="18"/>
+      <c r="G69" s="16"/>
     </row>
     <row r="70" spans="1:7">
-      <c r="A70" s="13">
+      <c r="A70" s="11">
         <v>63</v>
       </c>
-      <c r="B70" s="14" t="s">
+      <c r="B70" s="12" t="s">
         <v>205</v>
       </c>
-      <c r="C70" s="15" t="s">
+      <c r="C70" s="13" t="s">
         <v>206</v>
       </c>
-      <c r="D70" s="15" t="s">
+      <c r="D70" s="13" t="s">
         <v>125</v>
       </c>
-      <c r="E70" s="16"/>
-      <c r="F70" s="17" t="s">
+      <c r="E70" s="14"/>
+      <c r="F70" s="15" t="s">
         <v>207</v>
       </c>
-      <c r="G70" s="18"/>
+      <c r="G70" s="16"/>
     </row>
     <row r="71" spans="1:7">
-      <c r="A71" s="13">
+      <c r="A71" s="11">
         <v>64</v>
       </c>
-      <c r="B71" s="14" t="s">
+      <c r="B71" s="12" t="s">
         <v>208</v>
       </c>
-      <c r="C71" s="15" t="s">
+      <c r="C71" s="13" t="s">
         <v>209</v>
       </c>
-      <c r="D71" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E71" s="16"/>
-      <c r="F71" s="21" t="s">
+      <c r="D71" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E71" s="14"/>
+      <c r="F71" s="19" t="s">
         <v>210</v>
       </c>
-      <c r="G71" s="18"/>
+      <c r="G71" s="16"/>
     </row>
     <row r="72" spans="1:7">
-      <c r="A72" s="13">
+      <c r="A72" s="11">
         <v>65</v>
       </c>
-      <c r="B72" s="14" t="s">
+      <c r="B72" s="12" t="s">
         <v>211</v>
       </c>
-      <c r="C72" s="15" t="s">
+      <c r="C72" s="13" t="s">
         <v>212</v>
       </c>
-      <c r="D72" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E72" s="16"/>
-      <c r="F72" s="20" t="s">
+      <c r="D72" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E72" s="14"/>
+      <c r="F72" s="18" t="s">
         <v>213</v>
       </c>
-      <c r="G72" s="18"/>
+      <c r="G72" s="16"/>
     </row>
     <row r="73" spans="1:7">
-      <c r="A73" s="13">
+      <c r="A73" s="11">
         <v>66</v>
       </c>
-      <c r="B73" s="14" t="s">
+      <c r="B73" s="12" t="s">
         <v>214</v>
       </c>
-      <c r="C73" s="15" t="s">
+      <c r="C73" s="13" t="s">
         <v>215</v>
       </c>
-      <c r="D73" s="15" t="s">
+      <c r="D73" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E73" s="16"/>
-      <c r="F73" s="21" t="s">
+      <c r="E73" s="14"/>
+      <c r="F73" s="19" t="s">
         <v>216</v>
       </c>
-      <c r="G73" s="18"/>
+      <c r="G73" s="16"/>
     </row>
     <row r="74" spans="1:7">
-      <c r="A74" s="13">
+      <c r="A74" s="11">
         <v>67</v>
       </c>
-      <c r="B74" s="14" t="s">
+      <c r="B74" s="12" t="s">
         <v>217</v>
       </c>
-      <c r="C74" s="15" t="s">
+      <c r="C74" s="13" t="s">
         <v>218</v>
       </c>
-      <c r="D74" s="15" t="s">
+      <c r="D74" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E74" s="16"/>
-      <c r="F74" s="21" t="s">
+      <c r="E74" s="14"/>
+      <c r="F74" s="19" t="s">
         <v>219</v>
       </c>
-      <c r="G74" s="18"/>
+      <c r="G74" s="16"/>
     </row>
     <row r="75" spans="1:7">
-      <c r="A75" s="13">
+      <c r="A75" s="11">
         <v>68</v>
       </c>
-      <c r="B75" s="14" t="s">
+      <c r="B75" s="12" t="s">
         <v>220</v>
       </c>
-      <c r="C75" s="15" t="s">
+      <c r="C75" s="13" t="s">
         <v>221</v>
       </c>
-      <c r="D75" s="15" t="s">
+      <c r="D75" s="13" t="s">
         <v>125</v>
       </c>
-      <c r="E75" s="16"/>
-      <c r="F75" s="20" t="s">
+      <c r="E75" s="14"/>
+      <c r="F75" s="18" t="s">
         <v>222</v>
       </c>
-      <c r="G75" s="18"/>
+      <c r="G75" s="16"/>
     </row>
     <row r="76" spans="1:7">
-      <c r="A76" s="13">
+      <c r="A76" s="11">
         <v>69</v>
       </c>
-      <c r="B76" s="14" t="s">
+      <c r="B76" s="12" t="s">
         <v>223</v>
       </c>
-      <c r="C76" s="15" t="s">
+      <c r="C76" s="13" t="s">
         <v>224</v>
       </c>
-      <c r="D76" s="15" t="s">
+      <c r="D76" s="13" t="s">
         <v>125</v>
       </c>
-      <c r="E76" s="16"/>
-      <c r="F76" s="20" t="s">
+      <c r="E76" s="14"/>
+      <c r="F76" s="18" t="s">
         <v>225</v>
       </c>
-      <c r="G76" s="18"/>
+      <c r="G76" s="16"/>
     </row>
     <row r="77" spans="1:7">
-      <c r="A77" s="13">
+      <c r="A77" s="11">
         <v>70</v>
       </c>
-      <c r="B77" s="14" t="s">
+      <c r="B77" s="12" t="s">
         <v>226</v>
       </c>
-      <c r="C77" s="15" t="s">
+      <c r="C77" s="13" t="s">
         <v>227</v>
       </c>
-      <c r="D77" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E77" s="16"/>
-      <c r="F77" s="21" t="s">
+      <c r="D77" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E77" s="14"/>
+      <c r="F77" s="19" t="s">
         <v>228</v>
       </c>
-      <c r="G77" s="18"/>
+      <c r="G77" s="16"/>
     </row>
     <row r="78" spans="1:7">
-      <c r="A78" s="13">
+      <c r="A78" s="11">
         <v>71</v>
       </c>
-      <c r="B78" s="14" t="s">
+      <c r="B78" s="12" t="s">
         <v>229</v>
       </c>
-      <c r="C78" s="15" t="s">
+      <c r="C78" s="13" t="s">
         <v>230</v>
       </c>
-      <c r="D78" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E78" s="16"/>
-      <c r="F78" s="20" t="s">
+      <c r="D78" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E78" s="14"/>
+      <c r="F78" s="18" t="s">
         <v>231</v>
       </c>
-      <c r="G78" s="18"/>
+      <c r="G78" s="16"/>
     </row>
     <row r="79" spans="1:7">
-      <c r="A79" s="13">
+      <c r="A79" s="11">
         <v>72</v>
       </c>
-      <c r="B79" s="14" t="s">
+      <c r="B79" s="12" t="s">
         <v>232</v>
       </c>
-      <c r="C79" s="15" t="s">
+      <c r="C79" s="13" t="s">
         <v>233</v>
       </c>
-      <c r="D79" s="15" t="s">
+      <c r="D79" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="E79" s="16"/>
-      <c r="F79" s="17" t="s">
+      <c r="E79" s="14"/>
+      <c r="F79" s="15" t="s">
         <v>234</v>
       </c>
-      <c r="G79" s="18"/>
+      <c r="G79" s="16"/>
     </row>
     <row r="80" spans="1:7">
-      <c r="A80" s="13">
+      <c r="A80" s="11">
         <v>73</v>
       </c>
-      <c r="B80" s="14" t="s">
+      <c r="B80" s="12" t="s">
         <v>235</v>
       </c>
-      <c r="C80" s="15" t="s">
+      <c r="C80" s="13" t="s">
         <v>236</v>
       </c>
-      <c r="D80" s="15" t="s">
+      <c r="D80" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E80" s="16"/>
-      <c r="F80" s="17" t="s">
+      <c r="E80" s="14"/>
+      <c r="F80" s="15" t="s">
         <v>237</v>
       </c>
-      <c r="G80" s="18"/>
+      <c r="G80" s="16"/>
     </row>
     <row r="81" spans="1:7">
-      <c r="A81" s="13">
+      <c r="A81" s="11">
         <v>74</v>
       </c>
-      <c r="B81" s="14" t="s">
+      <c r="B81" s="12" t="s">
         <v>238</v>
       </c>
-      <c r="C81" s="15" t="s">
+      <c r="C81" s="13" t="s">
         <v>239</v>
       </c>
-      <c r="D81" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E81" s="16"/>
-      <c r="F81" s="17" t="s">
+      <c r="D81" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E81" s="14"/>
+      <c r="F81" s="15" t="s">
         <v>240</v>
       </c>
-      <c r="G81" s="18"/>
+      <c r="G81" s="16"/>
     </row>
     <row r="82" spans="1:7">
-      <c r="A82" s="13">
+      <c r="A82" s="11">
         <v>75</v>
       </c>
-      <c r="B82" s="14" t="s">
+      <c r="B82" s="12" t="s">
         <v>241</v>
       </c>
-      <c r="C82" s="15" t="s">
+      <c r="C82" s="13" t="s">
         <v>242</v>
       </c>
-      <c r="D82" s="15" t="s">
+      <c r="D82" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E82" s="16"/>
-      <c r="F82" s="17" t="s">
+      <c r="E82" s="14"/>
+      <c r="F82" s="15" t="s">
         <v>243</v>
       </c>
-      <c r="G82" s="18"/>
+      <c r="G82" s="16"/>
     </row>
     <row r="83" spans="1:7">
-      <c r="A83" s="13">
+      <c r="A83" s="11">
         <v>76</v>
       </c>
-      <c r="B83" s="14" t="s">
+      <c r="B83" s="12" t="s">
         <v>244</v>
       </c>
-      <c r="C83" s="15" t="s">
+      <c r="C83" s="13" t="s">
         <v>245</v>
       </c>
-      <c r="D83" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E83" s="16"/>
-      <c r="F83" s="17" t="s">
+      <c r="D83" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E83" s="14"/>
+      <c r="F83" s="15" t="s">
         <v>246</v>
       </c>
-      <c r="G83" s="18"/>
+      <c r="G83" s="16"/>
     </row>
     <row r="84" spans="1:7">
-      <c r="A84" s="13">
+      <c r="A84" s="11">
         <v>77</v>
       </c>
-      <c r="B84" s="14" t="s">
+      <c r="B84" s="12" t="s">
         <v>247</v>
       </c>
-      <c r="C84" s="15" t="s">
+      <c r="C84" s="13" t="s">
         <v>248</v>
       </c>
-      <c r="D84" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E84" s="16"/>
-      <c r="F84" s="17" t="s">
+      <c r="D84" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E84" s="14"/>
+      <c r="F84" s="15" t="s">
         <v>249</v>
       </c>
     </row>
     <row r="85" spans="1:7">
-      <c r="A85" s="13">
+      <c r="A85" s="11">
         <v>78</v>
       </c>
-      <c r="B85" s="14" t="s">
+      <c r="B85" s="12" t="s">
         <v>250</v>
       </c>
-      <c r="C85" s="15" t="s">
+      <c r="C85" s="13" t="s">
         <v>251</v>
       </c>
-      <c r="D85" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E85" s="16"/>
-      <c r="F85" s="17" t="s">
+      <c r="D85" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E85" s="14"/>
+      <c r="F85" s="15" t="s">
         <v>252</v>
       </c>
     </row>
     <row r="86" spans="1:7">
-      <c r="A86" s="13">
+      <c r="A86" s="11">
         <v>79</v>
       </c>
-      <c r="B86" s="14" t="s">
+      <c r="B86" s="12" t="s">
         <v>253</v>
       </c>
-      <c r="C86" s="15" t="s">
+      <c r="C86" s="13" t="s">
         <v>254</v>
       </c>
-      <c r="D86" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E86" s="16"/>
-      <c r="F86" s="17" t="s">
+      <c r="D86" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E86" s="14"/>
+      <c r="F86" s="15" t="s">
         <v>255</v>
       </c>
     </row>
     <row r="87" spans="1:7">
-      <c r="A87" s="13">
+      <c r="A87" s="11">
         <v>80</v>
       </c>
-      <c r="B87" s="14" t="s">
+      <c r="B87" s="12" t="s">
         <v>256</v>
       </c>
-      <c r="C87" s="15" t="s">
+      <c r="C87" s="13" t="s">
         <v>257</v>
       </c>
-      <c r="D87" s="15" t="s">
+      <c r="D87" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E87" s="16"/>
-      <c r="F87" s="17" t="s">
+      <c r="E87" s="14"/>
+      <c r="F87" s="15" t="s">
         <v>258</v>
       </c>
     </row>
     <row r="88" spans="1:7">
-      <c r="A88" s="13">
+      <c r="A88" s="11">
         <v>81</v>
       </c>
-      <c r="B88" s="14" t="s">
+      <c r="B88" s="12" t="s">
         <v>259</v>
       </c>
-      <c r="C88" s="15" t="s">
+      <c r="C88" s="13" t="s">
         <v>260</v>
       </c>
-      <c r="D88" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E88" s="16"/>
-      <c r="F88" s="17" t="s">
+      <c r="D88" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E88" s="14"/>
+      <c r="F88" s="15" t="s">
         <v>261</v>
       </c>
     </row>
     <row r="89" spans="1:7">
-      <c r="A89" s="13">
+      <c r="A89" s="11">
         <v>82</v>
       </c>
-      <c r="B89" s="14" t="s">
+      <c r="B89" s="12" t="s">
         <v>262</v>
       </c>
-      <c r="C89" s="15" t="s">
+      <c r="C89" s="13" t="s">
         <v>263</v>
       </c>
-      <c r="D89" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E89" s="16"/>
-      <c r="F89" s="17" t="s">
+      <c r="D89" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E89" s="14"/>
+      <c r="F89" s="15" t="s">
         <v>264</v>
       </c>
     </row>
     <row r="90" spans="1:7">
-      <c r="A90" s="13">
+      <c r="A90" s="11">
         <v>83</v>
       </c>
-      <c r="B90" s="14" t="s">
+      <c r="B90" s="12" t="s">
         <v>265</v>
       </c>
-      <c r="C90" s="15" t="s">
+      <c r="C90" s="13" t="s">
         <v>266</v>
       </c>
-      <c r="D90" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E90" s="16"/>
-      <c r="F90" s="17" t="s">
+      <c r="D90" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E90" s="14"/>
+      <c r="F90" s="15" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="91" spans="1:7">
-      <c r="A91" s="13">
+      <c r="A91" s="11">
         <v>84</v>
       </c>
-      <c r="B91" s="14" t="s">
+      <c r="B91" s="12" t="s">
         <v>268</v>
       </c>
-      <c r="C91" s="15" t="s">
+      <c r="C91" s="13" t="s">
         <v>269</v>
       </c>
-      <c r="D91" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E91" s="16"/>
-      <c r="F91" s="17" t="s">
+      <c r="D91" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E91" s="14"/>
+      <c r="F91" s="15" t="s">
         <v>270</v>
       </c>
     </row>
     <row r="92" spans="1:7">
-      <c r="A92" s="13">
+      <c r="A92" s="11">
         <v>85</v>
       </c>
-      <c r="B92" s="14" t="s">
+      <c r="B92" s="12" t="s">
         <v>271</v>
       </c>
-      <c r="C92" s="15" t="s">
+      <c r="C92" s="13" t="s">
         <v>272</v>
       </c>
-      <c r="D92" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E92" s="16"/>
-      <c r="F92" s="17" t="s">
+      <c r="D92" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E92" s="14"/>
+      <c r="F92" s="15" t="s">
         <v>273</v>
       </c>
     </row>
     <row r="93" spans="1:7">
-      <c r="A93" s="13">
+      <c r="A93" s="11">
         <v>86</v>
       </c>
-      <c r="B93" s="14" t="s">
+      <c r="B93" s="12" t="s">
         <v>274</v>
       </c>
-      <c r="C93" s="15" t="s">
+      <c r="C93" s="13" t="s">
         <v>275</v>
       </c>
-      <c r="D93" s="15" t="s">
+      <c r="D93" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E93" s="16"/>
-      <c r="F93" s="17" t="s">
+      <c r="E93" s="14"/>
+      <c r="F93" s="15" t="s">
         <v>276</v>
       </c>
     </row>
     <row r="94" spans="1:7">
-      <c r="A94" s="13">
+      <c r="A94" s="11">
         <v>87</v>
       </c>
-      <c r="B94" s="14" t="s">
+      <c r="B94" s="12" t="s">
         <v>277</v>
       </c>
-      <c r="C94" s="15" t="s">
+      <c r="C94" s="13" t="s">
         <v>278</v>
       </c>
-      <c r="D94" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E94" s="16"/>
-      <c r="F94" s="17" t="s">
+      <c r="D94" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E94" s="14"/>
+      <c r="F94" s="15" t="s">
         <v>279</v>
       </c>
     </row>
     <row r="95" spans="1:7">
-      <c r="A95" s="13">
-        <v>88</v>
-      </c>
-      <c r="B95" s="14" t="s">
+      <c r="A95" s="11">
+        <v>88</v>
+      </c>
+      <c r="B95" s="12" t="s">
         <v>280</v>
       </c>
-      <c r="C95" s="15" t="s">
+      <c r="C95" s="13" t="s">
         <v>281</v>
       </c>
-      <c r="D95" s="15" t="s">
+      <c r="D95" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E95" s="16"/>
-      <c r="F95" s="17" t="s">
+      <c r="E95" s="14"/>
+      <c r="F95" s="15" t="s">
         <v>282</v>
       </c>
     </row>
     <row r="96" spans="1:7">
-      <c r="A96" s="13">
+      <c r="A96" s="11">
         <v>89</v>
       </c>
-      <c r="B96" s="14" t="s">
+      <c r="B96" s="12" t="s">
         <v>283</v>
       </c>
-      <c r="C96" s="15" t="s">
+      <c r="C96" s="13" t="s">
         <v>284</v>
       </c>
-      <c r="D96" s="15" t="s">
+      <c r="D96" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E96" s="16"/>
-      <c r="F96" s="17" t="s">
+      <c r="E96" s="14"/>
+      <c r="F96" s="15" t="s">
         <v>285</v>
       </c>
     </row>
     <row r="97" spans="1:6">
-      <c r="A97" s="13">
+      <c r="A97" s="11">
         <v>90</v>
       </c>
-      <c r="B97" s="14" t="s">
+      <c r="B97" s="12" t="s">
         <v>286</v>
       </c>
-      <c r="C97" s="15" t="s">
+      <c r="C97" s="13" t="s">
         <v>287</v>
       </c>
-      <c r="D97" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E97" s="16"/>
-      <c r="F97" s="17" t="s">
+      <c r="D97" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E97" s="14"/>
+      <c r="F97" s="15" t="s">
         <v>288</v>
       </c>
     </row>
     <row r="98" spans="1:6">
-      <c r="A98" s="13">
+      <c r="A98" s="11">
         <v>91</v>
       </c>
-      <c r="B98" s="14" t="s">
+      <c r="B98" s="12" t="s">
         <v>289</v>
       </c>
-      <c r="C98" s="15" t="s">
+      <c r="C98" s="13" t="s">
         <v>290</v>
       </c>
-      <c r="D98" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E98" s="16"/>
-      <c r="F98" s="17" t="s">
+      <c r="D98" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E98" s="14"/>
+      <c r="F98" s="15" t="s">
         <v>291</v>
       </c>
     </row>
     <row r="99" spans="1:6">
-      <c r="A99" s="13">
+      <c r="A99" s="11">
         <v>92</v>
       </c>
-      <c r="B99" s="14" t="s">
+      <c r="B99" s="12" t="s">
         <v>292</v>
       </c>
-      <c r="C99" s="15" t="s">
+      <c r="C99" s="13" t="s">
         <v>293</v>
       </c>
-      <c r="D99" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E99" s="16"/>
-      <c r="F99" s="17" t="s">
+      <c r="D99" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E99" s="14"/>
+      <c r="F99" s="15" t="s">
         <v>294</v>
       </c>
     </row>
     <row r="100" spans="1:6">
-      <c r="A100" s="13">
+      <c r="A100" s="11">
         <v>93</v>
       </c>
-      <c r="B100" s="14" t="s">
+      <c r="B100" s="12" t="s">
         <v>295</v>
       </c>
-      <c r="C100" s="15" t="s">
+      <c r="C100" s="13" t="s">
         <v>296</v>
       </c>
-      <c r="D100" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E100" s="16"/>
-      <c r="F100" s="17" t="s">
+      <c r="D100" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E100" s="14"/>
+      <c r="F100" s="15" t="s">
         <v>297</v>
       </c>
     </row>
     <row r="101" spans="1:6">
-      <c r="A101" s="13">
+      <c r="A101" s="11">
         <v>94</v>
       </c>
-      <c r="B101" s="14" t="s">
+      <c r="B101" s="12" t="s">
         <v>298</v>
       </c>
-      <c r="C101" s="15" t="s">
+      <c r="C101" s="13" t="s">
         <v>299</v>
       </c>
-      <c r="D101" s="15" t="s">
+      <c r="D101" s="13" t="s">
         <v>125</v>
       </c>
-      <c r="E101" s="16"/>
-      <c r="F101" s="17" t="s">
+      <c r="E101" s="14"/>
+      <c r="F101" s="15" t="s">
         <v>300</v>
       </c>
     </row>
     <row r="102" spans="1:6">
-      <c r="A102" s="13">
+      <c r="A102" s="11">
         <v>95</v>
       </c>
-      <c r="B102" s="14" t="s">
+      <c r="B102" s="12" t="s">
         <v>301</v>
       </c>
-      <c r="C102" s="15" t="s">
+      <c r="C102" s="13" t="s">
         <v>302</v>
       </c>
-      <c r="D102" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E102" s="16"/>
-      <c r="F102" s="17" t="s">
+      <c r="D102" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E102" s="14"/>
+      <c r="F102" s="15" t="s">
         <v>303</v>
       </c>
     </row>
     <row r="103" spans="1:6">
-      <c r="A103" s="13">
+      <c r="A103" s="11">
         <v>96</v>
       </c>
-      <c r="B103" s="14" t="s">
+      <c r="B103" s="12" t="s">
         <v>304</v>
       </c>
-      <c r="C103" s="15" t="s">
+      <c r="C103" s="13" t="s">
         <v>305</v>
       </c>
-      <c r="D103" s="15" t="s">
+      <c r="D103" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E103" s="16"/>
-      <c r="F103" s="17" t="s">
+      <c r="E103" s="14"/>
+      <c r="F103" s="15" t="s">
         <v>306</v>
       </c>
     </row>
     <row r="104" spans="1:6">
-      <c r="A104" s="13">
+      <c r="A104" s="11">
         <v>97</v>
       </c>
-      <c r="B104" s="14" t="s">
+      <c r="B104" s="12" t="s">
         <v>307</v>
       </c>
-      <c r="C104" s="15" t="s">
+      <c r="C104" s="13" t="s">
         <v>308</v>
       </c>
-      <c r="D104" s="15" t="s">
+      <c r="D104" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E104" s="16"/>
-      <c r="F104" s="17" t="s">
+      <c r="E104" s="14"/>
+      <c r="F104" s="15" t="s">
         <v>309</v>
       </c>
     </row>
     <row r="105" spans="1:6">
-      <c r="A105" s="13">
+      <c r="A105" s="11">
         <v>98</v>
       </c>
-      <c r="B105" s="14" t="s">
+      <c r="B105" s="12" t="s">
         <v>310</v>
       </c>
-      <c r="C105" s="15" t="s">
+      <c r="C105" s="13" t="s">
         <v>311</v>
       </c>
-      <c r="D105" s="15" t="s">
+      <c r="D105" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E105" s="16"/>
-      <c r="F105" s="17" t="s">
+      <c r="E105" s="14"/>
+      <c r="F105" s="15" t="s">
         <v>312</v>
       </c>
     </row>
     <row r="106" spans="1:6">
-      <c r="A106" s="13">
+      <c r="A106" s="11">
         <v>99</v>
       </c>
-      <c r="B106" s="14" t="s">
+      <c r="B106" s="12" t="s">
         <v>313</v>
       </c>
-      <c r="C106" s="15" t="s">
+      <c r="C106" s="13" t="s">
         <v>314</v>
       </c>
-      <c r="D106" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E106" s="16"/>
-      <c r="F106" s="17" t="s">
+      <c r="D106" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E106" s="14"/>
+      <c r="F106" s="15" t="s">
         <v>315</v>
       </c>
     </row>
     <row r="107" spans="1:6">
-      <c r="A107" s="13">
+      <c r="A107" s="11">
         <v>100</v>
       </c>
-      <c r="B107" s="14" t="s">
+      <c r="B107" s="12" t="s">
         <v>316</v>
       </c>
-      <c r="C107" s="15" t="s">
+      <c r="C107" s="13" t="s">
         <v>317</v>
       </c>
-      <c r="D107" s="15" t="s">
+      <c r="D107" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E107" s="16"/>
-      <c r="F107" s="17" t="s">
+      <c r="E107" s="14"/>
+      <c r="F107" s="15" t="s">
         <v>318</v>
       </c>
     </row>
     <row r="108" spans="1:6">
-      <c r="A108" s="13">
+      <c r="A108" s="11">
         <v>101</v>
       </c>
-      <c r="B108" s="14" t="s">
+      <c r="B108" s="12" t="s">
         <v>319</v>
       </c>
-      <c r="C108" s="15" t="s">
+      <c r="C108" s="13" t="s">
         <v>320</v>
       </c>
-      <c r="D108" s="15" t="s">
+      <c r="D108" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E108" s="16"/>
-      <c r="F108" s="17" t="s">
+      <c r="E108" s="14"/>
+      <c r="F108" s="15" t="s">
         <v>285</v>
       </c>
     </row>
     <row r="109" spans="1:6">
-      <c r="A109" s="13">
+      <c r="A109" s="11">
         <v>102</v>
       </c>
-      <c r="B109" s="14" t="s">
+      <c r="B109" s="12" t="s">
         <v>321</v>
       </c>
-      <c r="C109" s="15" t="s">
+      <c r="C109" s="13" t="s">
         <v>322</v>
       </c>
-      <c r="D109" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E109" s="16"/>
-      <c r="F109" s="17" t="s">
+      <c r="D109" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E109" s="14"/>
+      <c r="F109" s="15" t="s">
         <v>323</v>
       </c>
     </row>
     <row r="110" spans="1:6">
-      <c r="A110" s="13">
+      <c r="A110" s="11">
         <v>103</v>
       </c>
-      <c r="B110" s="14" t="s">
+      <c r="B110" s="12" t="s">
         <v>324</v>
       </c>
-      <c r="C110" s="15" t="s">
+      <c r="C110" s="13" t="s">
         <v>325</v>
       </c>
-      <c r="D110" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E110" s="16"/>
-      <c r="F110" s="17" t="s">
+      <c r="D110" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E110" s="14"/>
+      <c r="F110" s="15" t="s">
         <v>326</v>
       </c>
     </row>
     <row r="111" spans="1:6">
-      <c r="A111" s="13">
+      <c r="A111" s="11">
         <v>104</v>
       </c>
-      <c r="B111" s="14" t="s">
+      <c r="B111" s="12" t="s">
         <v>327</v>
       </c>
-      <c r="C111" s="15" t="s">
+      <c r="C111" s="13" t="s">
         <v>328</v>
       </c>
-      <c r="D111" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E111" s="16"/>
-      <c r="F111" s="17" t="s">
+      <c r="D111" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E111" s="14"/>
+      <c r="F111" s="15" t="s">
         <v>329</v>
       </c>
     </row>
     <row r="112" spans="1:6">
-      <c r="A112" s="13">
+      <c r="A112" s="11">
         <v>105</v>
       </c>
-      <c r="B112" s="14" t="s">
+      <c r="B112" s="12" t="s">
         <v>330</v>
       </c>
-      <c r="C112" s="15" t="s">
+      <c r="C112" s="13" t="s">
         <v>331</v>
       </c>
-      <c r="D112" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E112" s="16"/>
-      <c r="F112" s="17" t="s">
+      <c r="D112" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E112" s="14"/>
+      <c r="F112" s="15" t="s">
         <v>332</v>
       </c>
     </row>
     <row r="113" spans="1:6">
-      <c r="A113" s="13">
+      <c r="A113" s="11">
         <v>106</v>
       </c>
-      <c r="B113" s="14" t="s">
+      <c r="B113" s="12" t="s">
         <v>333</v>
       </c>
-      <c r="C113" s="15" t="s">
+      <c r="C113" s="13" t="s">
         <v>334</v>
       </c>
-      <c r="D113" s="15" t="s">
+      <c r="D113" s="13" t="s">
         <v>125</v>
       </c>
-      <c r="E113" s="16"/>
-      <c r="F113" s="17" t="s">
+      <c r="E113" s="14"/>
+      <c r="F113" s="15" t="s">
         <v>335</v>
       </c>
     </row>
     <row r="114" spans="1:6">
-      <c r="A114" s="13">
+      <c r="A114" s="11">
         <v>107</v>
       </c>
-      <c r="B114" s="14" t="s">
+      <c r="B114" s="12" t="s">
         <v>336</v>
       </c>
-      <c r="C114" s="15" t="s">
+      <c r="C114" s="13" t="s">
         <v>337</v>
       </c>
-      <c r="D114" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E114" s="16"/>
-      <c r="F114" s="17" t="s">
+      <c r="D114" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E114" s="14"/>
+      <c r="F114" s="15" t="s">
         <v>338</v>
       </c>
     </row>
     <row r="115" spans="1:6">
-      <c r="A115" s="13">
+      <c r="A115" s="11">
         <v>108</v>
       </c>
-      <c r="B115" s="14" t="s">
+      <c r="B115" s="12" t="s">
         <v>339</v>
       </c>
-      <c r="C115" s="15" t="s">
+      <c r="C115" s="13" t="s">
         <v>340</v>
       </c>
-      <c r="D115" s="15" t="s">
+      <c r="D115" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E115" s="16"/>
-      <c r="F115" s="17" t="s">
+      <c r="E115" s="14"/>
+      <c r="F115" s="15" t="s">
         <v>341</v>
       </c>
     </row>
     <row r="116" spans="1:6">
-      <c r="A116" s="13">
+      <c r="A116" s="11">
         <v>109</v>
       </c>
-      <c r="B116" s="14" t="s">
+      <c r="B116" s="12" t="s">
         <v>342</v>
       </c>
-      <c r="C116" s="15" t="s">
+      <c r="C116" s="13" t="s">
         <v>343</v>
       </c>
-      <c r="D116" s="15" t="s">
+      <c r="D116" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E116" s="16"/>
-      <c r="F116" s="17" t="s">
+      <c r="E116" s="14"/>
+      <c r="F116" s="15" t="s">
         <v>344</v>
       </c>
     </row>
     <row r="117" spans="1:6">
-      <c r="A117" s="13">
+      <c r="A117" s="11">
         <v>110</v>
       </c>
-      <c r="B117" s="14" t="s">
+      <c r="B117" s="12" t="s">
         <v>345</v>
       </c>
-      <c r="C117" s="15" t="s">
+      <c r="C117" s="13" t="s">
         <v>346</v>
       </c>
-      <c r="D117" s="15" t="s">
+      <c r="D117" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E117" s="16"/>
-      <c r="F117" s="17" t="s">
+      <c r="E117" s="14"/>
+      <c r="F117" s="15" t="s">
         <v>347</v>
       </c>
     </row>
     <row r="118" spans="1:6">
-      <c r="A118" s="13">
+      <c r="A118" s="11">
         <v>111</v>
       </c>
-      <c r="B118" s="14" t="s">
+      <c r="B118" s="12" t="s">
         <v>348</v>
       </c>
-      <c r="C118" s="15" t="s">
+      <c r="C118" s="13" t="s">
         <v>349</v>
       </c>
-      <c r="D118" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E118" s="16"/>
-      <c r="F118" s="17" t="s">
+      <c r="D118" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E118" s="14"/>
+      <c r="F118" s="15" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="119" spans="1:6">
-      <c r="A119" s="13">
+      <c r="A119" s="11">
         <v>112</v>
       </c>
-      <c r="B119" s="14" t="s">
+      <c r="B119" s="12" t="s">
         <v>351</v>
       </c>
-      <c r="C119" s="15" t="s">
+      <c r="C119" s="13" t="s">
         <v>352</v>
       </c>
-      <c r="D119" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E119" s="16"/>
-      <c r="F119" s="17" t="s">
+      <c r="D119" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E119" s="14"/>
+      <c r="F119" s="15" t="s">
         <v>353</v>
       </c>
     </row>
     <row r="120" spans="1:6">
-      <c r="A120" s="13">
+      <c r="A120" s="11">
         <v>113</v>
       </c>
-      <c r="B120" s="14" t="s">
+      <c r="B120" s="12" t="s">
         <v>354</v>
       </c>
-      <c r="C120" s="15" t="s">
+      <c r="C120" s="13" t="s">
         <v>355</v>
       </c>
-      <c r="D120" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E120" s="16"/>
-      <c r="F120" s="17" t="s">
+      <c r="D120" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E120" s="14"/>
+      <c r="F120" s="15" t="s">
         <v>356</v>
       </c>
     </row>
     <row r="121" spans="1:6">
-      <c r="A121" s="13">
+      <c r="A121" s="11">
         <v>114</v>
       </c>
-      <c r="B121" s="14" t="s">
+      <c r="B121" s="12" t="s">
         <v>357</v>
       </c>
-      <c r="C121" s="15" t="s">
+      <c r="C121" s="13" t="s">
         <v>358</v>
       </c>
-      <c r="D121" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E121" s="16"/>
-      <c r="F121" s="17" t="s">
+      <c r="D121" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E121" s="14"/>
+      <c r="F121" s="15" t="s">
         <v>359</v>
       </c>
     </row>
     <row r="122" spans="1:6">
-      <c r="A122" s="13">
+      <c r="A122" s="11">
         <v>115</v>
       </c>
-      <c r="B122" s="14" t="s">
+      <c r="B122" s="12" t="s">
         <v>360</v>
       </c>
-      <c r="C122" s="15" t="s">
+      <c r="C122" s="13" t="s">
         <v>361</v>
       </c>
-      <c r="D122" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E122" s="16"/>
-      <c r="F122" s="17" t="s">
+      <c r="D122" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E122" s="14"/>
+      <c r="F122" s="15" t="s">
         <v>362</v>
       </c>
     </row>
     <row r="123" spans="1:6">
-      <c r="A123" s="13">
+      <c r="A123" s="11">
         <v>116</v>
       </c>
-      <c r="B123" s="14" t="s">
+      <c r="B123" s="12" t="s">
         <v>363</v>
       </c>
-      <c r="C123" s="15" t="s">
+      <c r="C123" s="13" t="s">
         <v>364</v>
       </c>
-      <c r="D123" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E123" s="16"/>
-      <c r="F123" s="17" t="s">
+      <c r="D123" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E123" s="14"/>
+      <c r="F123" s="15" t="s">
         <v>365</v>
       </c>
     </row>
     <row r="124" spans="1:6">
-      <c r="A124" s="13">
+      <c r="A124" s="11">
         <v>117</v>
       </c>
-      <c r="B124" s="14" t="s">
+      <c r="B124" s="12" t="s">
         <v>366</v>
       </c>
-      <c r="C124" s="15" t="s">
+      <c r="C124" s="13" t="s">
         <v>367</v>
       </c>
-      <c r="D124" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E124" s="16"/>
-      <c r="F124" s="17" t="s">
+      <c r="D124" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E124" s="14"/>
+      <c r="F124" s="15" t="s">
         <v>368</v>
       </c>
     </row>
     <row r="125" spans="1:6">
-      <c r="A125" s="13">
+      <c r="A125" s="11">
         <v>118</v>
       </c>
-      <c r="B125" s="14" t="s">
+      <c r="B125" s="12" t="s">
         <v>369</v>
       </c>
-      <c r="C125" s="15" t="s">
+      <c r="C125" s="13" t="s">
         <v>370</v>
       </c>
-      <c r="D125" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E125" s="16"/>
-      <c r="F125" s="17" t="s">
+      <c r="D125" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E125" s="14"/>
+      <c r="F125" s="15" t="s">
         <v>371</v>
       </c>
     </row>
     <row r="126" spans="1:6">
-      <c r="A126" s="13">
+      <c r="A126" s="11">
         <v>119</v>
       </c>
-      <c r="B126" s="14" t="s">
+      <c r="B126" s="12" t="s">
         <v>372</v>
       </c>
-      <c r="C126" s="15" t="s">
+      <c r="C126" s="13" t="s">
         <v>373</v>
       </c>
-      <c r="D126" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E126" s="16"/>
-      <c r="F126" s="17" t="s">
+      <c r="D126" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E126" s="14"/>
+      <c r="F126" s="15" t="s">
         <v>374</v>
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="A127" s="13">
+      <c r="A127" s="11">
         <v>120</v>
       </c>
-      <c r="B127" s="14" t="s">
+      <c r="B127" s="12" t="s">
         <v>375</v>
       </c>
-      <c r="C127" s="15" t="s">
+      <c r="C127" s="13" t="s">
         <v>376</v>
       </c>
-      <c r="D127" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E127" s="16"/>
-      <c r="F127" s="17" t="s">
+      <c r="D127" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E127" s="14"/>
+      <c r="F127" s="15" t="s">
         <v>377</v>
       </c>
     </row>
     <row r="128" spans="1:6">
-      <c r="A128" s="13">
+      <c r="A128" s="11">
         <v>121</v>
       </c>
-      <c r="B128" s="14" t="s">
+      <c r="B128" s="12" t="s">
         <v>378</v>
       </c>
-      <c r="C128" s="15" t="s">
+      <c r="C128" s="13" t="s">
         <v>379</v>
       </c>
-      <c r="D128" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E128" s="16"/>
-      <c r="F128" s="17" t="s">
+      <c r="D128" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E128" s="14"/>
+      <c r="F128" s="15" t="s">
         <v>380</v>
       </c>
     </row>
     <row r="129" spans="1:6">
-      <c r="A129" s="13">
+      <c r="A129" s="11">
         <v>122</v>
       </c>
-      <c r="B129" s="14" t="s">
+      <c r="B129" s="12" t="s">
         <v>381</v>
       </c>
-      <c r="C129" s="15" t="s">
+      <c r="C129" s="13" t="s">
         <v>382</v>
       </c>
-      <c r="D129" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E129" s="16"/>
-      <c r="F129" s="17" t="s">
+      <c r="D129" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E129" s="14"/>
+      <c r="F129" s="15" t="s">
         <v>383</v>
       </c>
     </row>
     <row r="130" spans="1:6">
-      <c r="A130" s="13">
+      <c r="A130" s="11">
         <v>123</v>
       </c>
-      <c r="B130" s="14" t="s">
+      <c r="B130" s="12" t="s">
         <v>384</v>
       </c>
-      <c r="C130" s="15" t="s">
+      <c r="C130" s="13" t="s">
         <v>385</v>
       </c>
-      <c r="D130" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E130" s="16"/>
-      <c r="F130" s="17" t="s">
+      <c r="D130" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E130" s="14"/>
+      <c r="F130" s="15" t="s">
         <v>386</v>
       </c>
     </row>
     <row r="131" spans="1:6">
-      <c r="A131" s="13">
+      <c r="A131" s="11">
         <v>124</v>
       </c>
-      <c r="B131" s="14" t="s">
+      <c r="B131" s="12" t="s">
         <v>387</v>
       </c>
-      <c r="C131" s="15" t="s">
+      <c r="C131" s="13" t="s">
         <v>388</v>
       </c>
-      <c r="D131" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E131" s="16"/>
-      <c r="F131" s="17" t="s">
+      <c r="D131" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E131" s="14"/>
+      <c r="F131" s="15" t="s">
         <v>389</v>
       </c>
     </row>
     <row r="132" spans="1:6">
-      <c r="A132" s="13">
+      <c r="A132" s="11">
         <v>125</v>
       </c>
-      <c r="B132" s="14" t="s">
+      <c r="B132" s="12" t="s">
         <v>390</v>
       </c>
-      <c r="C132" s="15" t="s">
+      <c r="C132" s="13" t="s">
         <v>391</v>
       </c>
-      <c r="D132" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E132" s="16"/>
-      <c r="F132" s="17" t="s">
+      <c r="D132" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E132" s="14"/>
+      <c r="F132" s="15" t="s">
         <v>392</v>
       </c>
     </row>
     <row r="133" spans="1:6">
-      <c r="A133" s="13">
+      <c r="A133" s="11">
         <v>126</v>
       </c>
-      <c r="B133" s="14" t="s">
+      <c r="B133" s="12" t="s">
         <v>393</v>
       </c>
-      <c r="C133" s="15" t="s">
+      <c r="C133" s="13" t="s">
         <v>394</v>
       </c>
-      <c r="D133" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E133" s="16"/>
-      <c r="F133" s="17" t="s">
+      <c r="D133" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E133" s="14"/>
+      <c r="F133" s="15" t="s">
         <v>395</v>
       </c>
     </row>
     <row r="134" spans="1:6">
-      <c r="A134" s="13">
+      <c r="A134" s="11">
         <v>127</v>
       </c>
-      <c r="B134" s="14" t="s">
+      <c r="B134" s="12" t="s">
         <v>396</v>
       </c>
-      <c r="C134" s="15" t="s">
+      <c r="C134" s="13" t="s">
         <v>397</v>
       </c>
-      <c r="D134" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E134" s="16"/>
-      <c r="F134" s="17" t="s">
+      <c r="D134" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E134" s="14"/>
+      <c r="F134" s="15" t="s">
         <v>398</v>
       </c>
     </row>
     <row r="135" spans="1:6">
-      <c r="A135" s="13">
+      <c r="A135" s="11">
         <v>128</v>
       </c>
-      <c r="B135" s="14" t="s">
+      <c r="B135" s="12" t="s">
         <v>399</v>
       </c>
-      <c r="C135" s="15" t="s">
+      <c r="C135" s="13" t="s">
         <v>400</v>
       </c>
-      <c r="D135" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E135" s="16"/>
-      <c r="F135" s="17" t="s">
+      <c r="D135" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E135" s="14"/>
+      <c r="F135" s="15" t="s">
         <v>401</v>
       </c>
     </row>
     <row r="136" spans="1:6">
-      <c r="A136" s="13">
+      <c r="A136" s="11">
         <v>129</v>
       </c>
-      <c r="B136" s="14" t="s">
+      <c r="B136" s="12" t="s">
         <v>402</v>
       </c>
-      <c r="C136" s="15" t="s">
+      <c r="C136" s="13" t="s">
         <v>403</v>
       </c>
-      <c r="D136" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E136" s="16"/>
-      <c r="F136" s="17" t="s">
+      <c r="D136" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E136" s="14"/>
+      <c r="F136" s="15" t="s">
         <v>404</v>
       </c>
     </row>
     <row r="137" spans="1:6">
-      <c r="A137" s="13">
+      <c r="A137" s="11">
         <v>130</v>
       </c>
-      <c r="B137" s="14" t="s">
+      <c r="B137" s="12" t="s">
         <v>405</v>
       </c>
-      <c r="C137" s="15" t="s">
+      <c r="C137" s="13" t="s">
         <v>406</v>
       </c>
-      <c r="D137" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E137" s="16"/>
-      <c r="F137" s="17" t="s">
+      <c r="D137" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E137" s="14"/>
+      <c r="F137" s="15" t="s">
         <v>407</v>
       </c>
     </row>
     <row r="138" spans="1:6">
-      <c r="A138" s="13">
+      <c r="A138" s="11">
         <v>131</v>
       </c>
-      <c r="B138" s="14" t="s">
+      <c r="B138" s="12" t="s">
         <v>408</v>
       </c>
-      <c r="C138" s="15" t="s">
+      <c r="C138" s="13" t="s">
         <v>409</v>
       </c>
-      <c r="D138" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E138" s="16"/>
-      <c r="F138" s="17" t="s">
+      <c r="D138" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E138" s="14"/>
+      <c r="F138" s="15" t="s">
         <v>410</v>
       </c>
     </row>
     <row r="139" spans="1:6">
-      <c r="A139" s="13">
+      <c r="A139" s="11">
         <v>132</v>
       </c>
-      <c r="B139" s="14" t="s">
+      <c r="B139" s="12" t="s">
         <v>411</v>
       </c>
-      <c r="C139" s="15" t="s">
+      <c r="C139" s="13" t="s">
         <v>412</v>
       </c>
-      <c r="D139" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E139" s="16"/>
-      <c r="F139" s="17" t="s">
+      <c r="D139" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E139" s="14"/>
+      <c r="F139" s="15" t="s">
         <v>413</v>
       </c>
     </row>
     <row r="140" spans="1:6">
-      <c r="A140" s="13">
+      <c r="A140" s="11">
         <v>133</v>
       </c>
-      <c r="B140" s="14" t="s">
+      <c r="B140" s="12" t="s">
         <v>414</v>
       </c>
-      <c r="C140" s="15" t="s">
+      <c r="C140" s="13" t="s">
         <v>415</v>
       </c>
-      <c r="D140" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E140" s="16"/>
-      <c r="F140" s="17" t="s">
+      <c r="D140" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E140" s="14"/>
+      <c r="F140" s="15" t="s">
         <v>416</v>
       </c>
     </row>
     <row r="141" spans="1:6">
-      <c r="A141" s="13">
+      <c r="A141" s="11">
         <v>134</v>
       </c>
-      <c r="B141" s="14" t="s">
+      <c r="B141" s="12" t="s">
         <v>417</v>
       </c>
-      <c r="C141" s="15" t="s">
+      <c r="C141" s="13" t="s">
         <v>418</v>
       </c>
-      <c r="D141" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E141" s="16"/>
-      <c r="F141" s="17" t="s">
+      <c r="D141" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E141" s="14"/>
+      <c r="F141" s="15" t="s">
         <v>419</v>
       </c>
     </row>
     <row r="142" spans="1:6">
-      <c r="A142" s="13">
+      <c r="A142" s="11">
         <v>135</v>
       </c>
-      <c r="B142" s="14" t="s">
+      <c r="B142" s="12" t="s">
         <v>420</v>
       </c>
-      <c r="C142" s="15" t="s">
+      <c r="C142" s="13" t="s">
         <v>421</v>
       </c>
-      <c r="D142" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E142" s="16"/>
-      <c r="F142" s="17" t="s">
+      <c r="D142" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E142" s="14"/>
+      <c r="F142" s="15" t="s">
         <v>422</v>
       </c>
     </row>
     <row r="143" spans="1:6">
-      <c r="A143" s="13">
+      <c r="A143" s="11">
         <v>136</v>
       </c>
-      <c r="B143" s="14" t="s">
+      <c r="B143" s="12" t="s">
         <v>423</v>
       </c>
-      <c r="C143" s="15" t="s">
+      <c r="C143" s="13" t="s">
         <v>424</v>
       </c>
-      <c r="D143" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E143" s="16"/>
-      <c r="F143" s="17" t="s">
+      <c r="D143" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E143" s="14"/>
+      <c r="F143" s="15" t="s">
         <v>425</v>
       </c>
     </row>
     <row r="144" spans="1:6">
-      <c r="A144" s="13">
+      <c r="A144" s="11">
         <v>137</v>
       </c>
-      <c r="B144" s="14" t="s">
+      <c r="B144" s="12" t="s">
         <v>426</v>
       </c>
-      <c r="C144" s="15" t="s">
+      <c r="C144" s="13" t="s">
         <v>427</v>
       </c>
-      <c r="D144" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E144" s="16"/>
-      <c r="F144" s="17" t="s">
+      <c r="D144" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E144" s="14"/>
+      <c r="F144" s="15" t="s">
         <v>428</v>
       </c>
     </row>
     <row r="145" spans="1:6">
-      <c r="A145" s="13">
+      <c r="A145" s="11">
         <v>138</v>
       </c>
-      <c r="B145" s="14" t="s">
+      <c r="B145" s="12" t="s">
         <v>429</v>
       </c>
-      <c r="C145" s="15" t="s">
+      <c r="C145" s="13" t="s">
         <v>430</v>
       </c>
-      <c r="D145" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E145" s="16"/>
-      <c r="F145" s="17" t="s">
+      <c r="D145" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E145" s="14"/>
+      <c r="F145" s="15" t="s">
         <v>431</v>
       </c>
     </row>
     <row r="146" spans="1:6">
-      <c r="A146" s="13">
+      <c r="A146" s="11">
         <v>139</v>
       </c>
-      <c r="B146" s="14" t="s">
+      <c r="B146" s="12" t="s">
         <v>432</v>
       </c>
-      <c r="C146" s="15" t="s">
+      <c r="C146" s="13" t="s">
         <v>433</v>
       </c>
-      <c r="D146" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E146" s="16"/>
-      <c r="F146" s="17" t="s">
+      <c r="D146" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E146" s="14"/>
+      <c r="F146" s="15" t="s">
         <v>434</v>
       </c>
     </row>
     <row r="147" spans="1:6">
-      <c r="A147" s="13">
+      <c r="A147" s="11">
         <v>140</v>
       </c>
-      <c r="B147" s="14" t="s">
+      <c r="B147" s="12" t="s">
         <v>435</v>
       </c>
-      <c r="C147" s="15" t="s">
+      <c r="C147" s="13" t="s">
         <v>436</v>
       </c>
-      <c r="D147" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E147" s="16"/>
-      <c r="F147" s="17" t="s">
+      <c r="D147" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E147" s="14"/>
+      <c r="F147" s="15" t="s">
         <v>437</v>
       </c>
     </row>
     <row r="148" spans="1:6">
-      <c r="A148" s="13">
+      <c r="A148" s="11">
         <v>141</v>
       </c>
-      <c r="B148" s="14" t="s">
+      <c r="B148" s="12" t="s">
         <v>438</v>
       </c>
-      <c r="C148" s="15" t="s">
+      <c r="C148" s="13" t="s">
         <v>439</v>
       </c>
-      <c r="D148" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E148" s="16"/>
-      <c r="F148" s="17" t="s">
+      <c r="D148" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E148" s="14"/>
+      <c r="F148" s="15" t="s">
         <v>440</v>
       </c>
     </row>
     <row r="149" spans="1:6">
-      <c r="A149" s="13">
+      <c r="A149" s="11">
         <v>142</v>
       </c>
-      <c r="B149" s="14" t="s">
+      <c r="B149" s="12" t="s">
         <v>441</v>
       </c>
-      <c r="C149" s="15" t="s">
+      <c r="C149" s="13" t="s">
         <v>442</v>
       </c>
-      <c r="D149" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E149" s="16"/>
-      <c r="F149" s="17" t="s">
+      <c r="D149" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E149" s="14"/>
+      <c r="F149" s="15" t="s">
         <v>443</v>
       </c>
     </row>
     <row r="150" spans="1:6">
-      <c r="A150" s="13">
+      <c r="A150" s="11">
         <v>143</v>
       </c>
-      <c r="B150" s="14" t="s">
+      <c r="B150" s="12" t="s">
         <v>444</v>
       </c>
-      <c r="C150" s="15" t="s">
+      <c r="C150" s="13" t="s">
         <v>445</v>
       </c>
-      <c r="D150" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E150" s="16"/>
-      <c r="F150" s="17" t="s">
+      <c r="D150" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E150" s="14"/>
+      <c r="F150" s="15" t="s">
         <v>446</v>
       </c>
     </row>
     <row r="151" spans="1:6">
-      <c r="A151" s="13">
+      <c r="A151" s="11">
         <v>144</v>
       </c>
-      <c r="B151" s="14" t="s">
+      <c r="B151" s="12" t="s">
         <v>447</v>
       </c>
-      <c r="C151" s="15" t="s">
+      <c r="C151" s="13" t="s">
         <v>448</v>
       </c>
-      <c r="D151" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E151" s="16"/>
-      <c r="F151" s="17" t="s">
+      <c r="D151" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E151" s="14"/>
+      <c r="F151" s="15" t="s">
         <v>449</v>
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="A152" s="13">
+      <c r="A152" s="11">
         <v>145</v>
       </c>
-      <c r="B152" s="14" t="s">
+      <c r="B152" s="12" t="s">
         <v>450</v>
       </c>
-      <c r="C152" s="15" t="s">
+      <c r="C152" s="13" t="s">
         <v>451</v>
       </c>
-      <c r="D152" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E152" s="16"/>
-      <c r="F152" s="17" t="s">
+      <c r="D152" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E152" s="14"/>
+      <c r="F152" s="15" t="s">
         <v>452</v>
       </c>
     </row>
     <row r="153" spans="1:6">
-      <c r="A153" s="13">
+      <c r="A153" s="11">
         <v>146</v>
       </c>
-      <c r="B153" s="14" t="s">
+      <c r="B153" s="12" t="s">
         <v>453</v>
       </c>
-      <c r="C153" s="15" t="s">
+      <c r="C153" s="13" t="s">
         <v>454</v>
       </c>
-      <c r="D153" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E153" s="16"/>
-      <c r="F153" s="17" t="s">
+      <c r="D153" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E153" s="14"/>
+      <c r="F153" s="15" t="s">
         <v>455</v>
       </c>
     </row>
     <row r="154" spans="1:6">
-      <c r="A154" s="13">
+      <c r="A154" s="11">
         <v>147</v>
       </c>
-      <c r="B154" s="14" t="s">
+      <c r="B154" s="12" t="s">
         <v>456</v>
       </c>
-      <c r="C154" s="15" t="s">
+      <c r="C154" s="13" t="s">
         <v>457</v>
       </c>
-      <c r="D154" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E154" s="16"/>
-      <c r="F154" s="17" t="s">
+      <c r="D154" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E154" s="14"/>
+      <c r="F154" s="15" t="s">
         <v>458</v>
       </c>
     </row>
     <row r="155" spans="1:6">
-      <c r="A155" s="13">
+      <c r="A155" s="11">
         <v>148</v>
       </c>
-      <c r="B155" s="14" t="s">
+      <c r="B155" s="12" t="s">
         <v>459</v>
       </c>
-      <c r="C155" s="15" t="s">
+      <c r="C155" s="13" t="s">
         <v>460</v>
       </c>
-      <c r="D155" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E155" s="16"/>
-      <c r="F155" s="17" t="s">
+      <c r="D155" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E155" s="14"/>
+      <c r="F155" s="15" t="s">
         <v>461</v>
       </c>
     </row>
     <row r="156" spans="1:6">
-      <c r="A156" s="13">
+      <c r="A156" s="11">
         <v>149</v>
       </c>
-      <c r="B156" s="14" t="s">
+      <c r="B156" s="12" t="s">
         <v>462</v>
       </c>
-      <c r="C156" s="15" t="s">
+      <c r="C156" s="13" t="s">
         <v>463</v>
       </c>
-      <c r="D156" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E156" s="16"/>
-      <c r="F156" s="17" t="s">
+      <c r="D156" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E156" s="14"/>
+      <c r="F156" s="15" t="s">
         <v>464</v>
       </c>
     </row>
     <row r="157" spans="1:6">
-      <c r="A157" s="13">
+      <c r="A157" s="11">
         <v>150</v>
       </c>
-      <c r="B157" s="14" t="s">
+      <c r="B157" s="12" t="s">
         <v>465</v>
       </c>
-      <c r="C157" s="15" t="s">
+      <c r="C157" s="13" t="s">
         <v>466</v>
       </c>
-      <c r="D157" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E157" s="16"/>
-      <c r="F157" s="17" t="s">
+      <c r="D157" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E157" s="14"/>
+      <c r="F157" s="15" t="s">
         <v>467</v>
       </c>
     </row>
     <row r="158" spans="1:6">
-      <c r="A158" s="13">
+      <c r="A158" s="11">
         <v>151</v>
       </c>
-      <c r="B158" s="14" t="s">
+      <c r="B158" s="12" t="s">
         <v>468</v>
       </c>
-      <c r="C158" s="15" t="s">
+      <c r="C158" s="13" t="s">
         <v>469</v>
       </c>
-      <c r="D158" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E158" s="16"/>
-      <c r="F158" s="17" t="s">
+      <c r="D158" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E158" s="14"/>
+      <c r="F158" s="15" t="s">
         <v>470</v>
       </c>
     </row>
     <row r="159" spans="1:6">
-      <c r="A159" s="13">
+      <c r="A159" s="11">
         <v>152</v>
       </c>
-      <c r="B159" s="14" t="s">
+      <c r="B159" s="12" t="s">
         <v>471</v>
       </c>
-      <c r="C159" s="15" t="s">
+      <c r="C159" s="13" t="s">
         <v>472</v>
       </c>
-      <c r="D159" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E159" s="16"/>
-      <c r="F159" s="17" t="s">
+      <c r="D159" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E159" s="14"/>
+      <c r="F159" s="15" t="s">
         <v>473</v>
       </c>
     </row>
     <row r="160" spans="1:6">
-      <c r="A160" s="13">
+      <c r="A160" s="11">
         <v>153</v>
       </c>
-      <c r="B160" s="14" t="s">
+      <c r="B160" s="12" t="s">
         <v>474</v>
       </c>
-      <c r="C160" s="15" t="s">
+      <c r="C160" s="13" t="s">
         <v>475</v>
       </c>
-      <c r="D160" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E160" s="16"/>
-      <c r="F160" s="17" t="s">
+      <c r="D160" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E160" s="14"/>
+      <c r="F160" s="15" t="s">
         <v>476</v>
       </c>
     </row>
     <row r="161" spans="1:6">
-      <c r="A161" s="13">
+      <c r="A161" s="11">
         <v>154</v>
       </c>
-      <c r="B161" s="14" t="s">
+      <c r="B161" s="12" t="s">
         <v>477</v>
       </c>
-      <c r="C161" s="15" t="s">
+      <c r="C161" s="13" t="s">
         <v>478</v>
       </c>
-      <c r="D161" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E161" s="16"/>
-      <c r="F161" s="17" t="s">
+      <c r="D161" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E161" s="14"/>
+      <c r="F161" s="15" t="s">
         <v>479</v>
       </c>
     </row>
     <row r="162" spans="1:6">
-      <c r="A162" s="13">
+      <c r="A162" s="11">
         <v>155</v>
       </c>
-      <c r="B162" s="14" t="s">
+      <c r="B162" s="12" t="s">
         <v>480</v>
       </c>
-      <c r="C162" s="15" t="s">
+      <c r="C162" s="13" t="s">
         <v>481</v>
       </c>
-      <c r="D162" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E162" s="16"/>
-      <c r="F162" s="17" t="s">
+      <c r="D162" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E162" s="14"/>
+      <c r="F162" s="15" t="s">
         <v>482</v>
       </c>
     </row>
     <row r="163" spans="1:6">
-      <c r="A163" s="13">
+      <c r="A163" s="11">
         <v>156</v>
       </c>
-      <c r="B163" s="14" t="s">
+      <c r="B163" s="12" t="s">
         <v>483</v>
       </c>
-      <c r="C163" s="15" t="s">
+      <c r="C163" s="13" t="s">
         <v>484</v>
       </c>
-      <c r="D163" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E163" s="16"/>
-      <c r="F163" s="17" t="s">
+      <c r="D163" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E163" s="14"/>
+      <c r="F163" s="15" t="s">
         <v>485</v>
       </c>
     </row>
     <row r="164" spans="1:6">
-      <c r="A164" s="13">
+      <c r="A164" s="11">
         <v>157</v>
       </c>
-      <c r="B164" s="14" t="s">
+      <c r="B164" s="12" t="s">
         <v>486</v>
       </c>
-      <c r="C164" s="15" t="s">
+      <c r="C164" s="13" t="s">
         <v>487</v>
       </c>
-      <c r="D164" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E164" s="16"/>
-      <c r="F164" s="17" t="s">
+      <c r="D164" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E164" s="14"/>
+      <c r="F164" s="15" t="s">
         <v>488</v>
       </c>
     </row>
     <row r="165" spans="1:6">
-      <c r="A165" s="13">
+      <c r="A165" s="11">
         <v>158</v>
       </c>
-      <c r="B165" s="14" t="s">
+      <c r="B165" s="12" t="s">
         <v>489</v>
       </c>
-      <c r="C165" s="15" t="s">
+      <c r="C165" s="13" t="s">
         <v>490</v>
       </c>
-      <c r="D165" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E165" s="16"/>
-      <c r="F165" s="17" t="s">
+      <c r="D165" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E165" s="14"/>
+      <c r="F165" s="15" t="s">
         <v>491</v>
       </c>
     </row>
     <row r="166" spans="1:6">
-      <c r="A166" s="13">
+      <c r="A166" s="11">
         <v>159</v>
       </c>
-      <c r="B166" s="14" t="s">
+      <c r="B166" s="12" t="s">
         <v>492</v>
       </c>
-      <c r="C166" s="15" t="s">
+      <c r="C166" s="13" t="s">
         <v>493</v>
       </c>
-      <c r="D166" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E166" s="16"/>
-      <c r="F166" s="17" t="s">
+      <c r="D166" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E166" s="14"/>
+      <c r="F166" s="15" t="s">
         <v>494</v>
       </c>
     </row>
     <row r="167" spans="1:6">
-      <c r="A167" s="13">
+      <c r="A167" s="11">
         <v>160</v>
       </c>
-      <c r="B167" s="14" t="s">
+      <c r="B167" s="12" t="s">
         <v>495</v>
       </c>
-      <c r="C167" s="15" t="s">
+      <c r="C167" s="13" t="s">
         <v>496</v>
       </c>
-      <c r="D167" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E167" s="16"/>
-      <c r="F167" s="17" t="s">
+      <c r="D167" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E167" s="14"/>
+      <c r="F167" s="15" t="s">
         <v>497</v>
       </c>
     </row>
     <row r="168" spans="1:6">
-      <c r="A168" s="13">
+      <c r="A168" s="11">
         <v>161</v>
       </c>
-      <c r="B168" s="14" t="s">
+      <c r="B168" s="12" t="s">
         <v>498</v>
       </c>
-      <c r="C168" s="15" t="s">
+      <c r="C168" s="13" t="s">
         <v>499</v>
       </c>
-      <c r="D168" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E168" s="16"/>
-      <c r="F168" s="17" t="s">
+      <c r="D168" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E168" s="14"/>
+      <c r="F168" s="15" t="s">
         <v>500</v>
       </c>
     </row>
     <row r="169" spans="1:6">
-      <c r="A169" s="13">
+      <c r="A169" s="11">
         <v>162</v>
       </c>
-      <c r="B169" s="14" t="s">
+      <c r="B169" s="12" t="s">
         <v>501</v>
       </c>
-      <c r="C169" s="15" t="s">
+      <c r="C169" s="13" t="s">
         <v>502</v>
       </c>
-      <c r="D169" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E169" s="16"/>
-      <c r="F169" s="17" t="s">
+      <c r="D169" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E169" s="14"/>
+      <c r="F169" s="15" t="s">
         <v>503</v>
       </c>
     </row>
     <row r="170" spans="1:6">
-      <c r="A170" s="13">
+      <c r="A170" s="11">
         <v>163</v>
       </c>
-      <c r="B170" s="14" t="s">
+      <c r="B170" s="12" t="s">
         <v>504</v>
       </c>
-      <c r="C170" s="15" t="s">
+      <c r="C170" s="13" t="s">
         <v>505</v>
       </c>
-      <c r="D170" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E170" s="16"/>
-      <c r="F170" s="17" t="s">
+      <c r="D170" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E170" s="14"/>
+      <c r="F170" s="15" t="s">
         <v>506</v>
       </c>
     </row>
     <row r="171" spans="1:6">
-      <c r="A171" s="13">
+      <c r="A171" s="11">
         <v>164</v>
       </c>
-      <c r="B171" s="14" t="s">
+      <c r="B171" s="12" t="s">
         <v>507</v>
       </c>
-      <c r="C171" s="15" t="s">
+      <c r="C171" s="13" t="s">
         <v>508</v>
       </c>
-      <c r="D171" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E171" s="16"/>
-      <c r="F171" s="17" t="s">
+      <c r="D171" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E171" s="14"/>
+      <c r="F171" s="15" t="s">
         <v>509</v>
       </c>
     </row>
     <row r="172" spans="1:6">
-      <c r="A172" s="13">
+      <c r="A172" s="11">
         <v>165</v>
       </c>
-      <c r="B172" s="14" t="s">
+      <c r="B172" s="12" t="s">
         <v>510</v>
       </c>
-      <c r="C172" s="15" t="s">
+      <c r="C172" s="13" t="s">
         <v>511</v>
       </c>
-      <c r="D172" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E172" s="16"/>
-      <c r="F172" s="17" t="s">
+      <c r="D172" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E172" s="14"/>
+      <c r="F172" s="15" t="s">
         <v>512</v>
       </c>
     </row>
     <row r="173" spans="1:6">
-      <c r="A173" s="13">
+      <c r="A173" s="11">
         <v>166</v>
       </c>
-      <c r="B173" s="14" t="s">
+      <c r="B173" s="12" t="s">
         <v>513</v>
       </c>
-      <c r="C173" s="15" t="s">
+      <c r="C173" s="13" t="s">
         <v>514</v>
       </c>
-      <c r="D173" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E173" s="16"/>
-      <c r="F173" s="17" t="s">
+      <c r="D173" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E173" s="14"/>
+      <c r="F173" s="15" t="s">
         <v>515</v>
       </c>
     </row>
     <row r="174" spans="1:6">
-      <c r="A174" s="13">
+      <c r="A174" s="11">
         <v>167</v>
       </c>
-      <c r="B174" s="14" t="s">
+      <c r="B174" s="12" t="s">
         <v>516</v>
       </c>
-      <c r="C174" s="15" t="s">
+      <c r="C174" s="13" t="s">
         <v>517</v>
       </c>
-      <c r="D174" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E174" s="16"/>
-      <c r="F174" s="17" t="s">
+      <c r="D174" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E174" s="14"/>
+      <c r="F174" s="15" t="s">
         <v>518</v>
       </c>
     </row>
     <row r="175" spans="1:6">
-      <c r="A175" s="13">
+      <c r="A175" s="11">
         <v>168</v>
       </c>
-      <c r="B175" s="14" t="s">
+      <c r="B175" s="12" t="s">
         <v>519</v>
       </c>
-      <c r="C175" s="15" t="s">
+      <c r="C175" s="13" t="s">
         <v>520</v>
       </c>
-      <c r="D175" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E175" s="16"/>
-      <c r="F175" s="17" t="s">
+      <c r="D175" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E175" s="14"/>
+      <c r="F175" s="15" t="s">
         <v>521</v>
       </c>
     </row>
     <row r="176" spans="1:6">
-      <c r="A176" s="13">
+      <c r="A176" s="11">
         <v>169</v>
       </c>
-      <c r="B176" s="14" t="s">
+      <c r="B176" s="12" t="s">
         <v>522</v>
       </c>
-      <c r="C176" s="15" t="s">
+      <c r="C176" s="13" t="s">
         <v>523</v>
       </c>
-      <c r="D176" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E176" s="16"/>
-      <c r="F176" s="17" t="s">
+      <c r="D176" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E176" s="14"/>
+      <c r="F176" s="15" t="s">
         <v>524</v>
       </c>
     </row>
     <row r="177" spans="1:6">
-      <c r="A177" s="13">
+      <c r="A177" s="11">
         <v>170</v>
       </c>
-      <c r="B177" s="14" t="s">
+      <c r="B177" s="12" t="s">
         <v>525</v>
       </c>
-      <c r="C177" s="15" t="s">
+      <c r="C177" s="13" t="s">
         <v>526</v>
       </c>
-      <c r="D177" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E177" s="16"/>
-      <c r="F177" s="17" t="s">
+      <c r="D177" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E177" s="14"/>
+      <c r="F177" s="15" t="s">
         <v>527</v>
       </c>
     </row>
     <row r="178" spans="1:6">
-      <c r="A178" s="13">
+      <c r="A178" s="11">
         <v>171</v>
       </c>
-      <c r="B178" s="14" t="s">
+      <c r="B178" s="12" t="s">
         <v>528</v>
       </c>
-      <c r="C178" s="15" t="s">
+      <c r="C178" s="13" t="s">
         <v>529</v>
       </c>
-      <c r="D178" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E178" s="16"/>
-      <c r="F178" s="17" t="s">
+      <c r="D178" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E178" s="14"/>
+      <c r="F178" s="15" t="s">
         <v>530</v>
       </c>
     </row>
     <row r="179" spans="1:6">
-      <c r="A179" s="13">
+      <c r="A179" s="11">
         <v>172</v>
       </c>
-      <c r="B179" s="14" t="s">
+      <c r="B179" s="12" t="s">
         <v>531</v>
       </c>
-      <c r="C179" s="15" t="s">
+      <c r="C179" s="13" t="s">
         <v>532</v>
       </c>
-      <c r="D179" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E179" s="16"/>
-      <c r="F179" s="17" t="s">
+      <c r="D179" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E179" s="14"/>
+      <c r="F179" s="15" t="s">
         <v>533</v>
       </c>
     </row>
     <row r="180" spans="1:6">
-      <c r="A180" s="13">
+      <c r="A180" s="11">
         <v>173</v>
       </c>
-      <c r="B180" s="14" t="s">
+      <c r="B180" s="12" t="s">
         <v>534</v>
       </c>
-      <c r="C180" s="15" t="s">
+      <c r="C180" s="13" t="s">
         <v>535</v>
       </c>
-      <c r="D180" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E180" s="16"/>
-      <c r="F180" s="17" t="s">
+      <c r="D180" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E180" s="14"/>
+      <c r="F180" s="15" t="s">
         <v>536</v>
       </c>
     </row>
     <row r="181" spans="1:6">
-      <c r="A181" s="13">
+      <c r="A181" s="11">
         <v>174</v>
       </c>
-      <c r="B181" s="14" t="s">
+      <c r="B181" s="12" t="s">
         <v>537</v>
       </c>
-      <c r="C181" s="15" t="s">
+      <c r="C181" s="13" t="s">
         <v>538</v>
       </c>
-      <c r="D181" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E181" s="16"/>
-      <c r="F181" s="17" t="s">
+      <c r="D181" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E181" s="14"/>
+      <c r="F181" s="15" t="s">
         <v>539</v>
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="A182" s="13">
+      <c r="A182" s="11">
         <v>175</v>
       </c>
-      <c r="B182" s="14" t="s">
+      <c r="B182" s="12" t="s">
         <v>540</v>
       </c>
-      <c r="C182" s="15" t="s">
+      <c r="C182" s="13" t="s">
         <v>541</v>
       </c>
-      <c r="D182" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E182" s="16"/>
-      <c r="F182" s="17" t="s">
+      <c r="D182" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E182" s="14"/>
+      <c r="F182" s="15" t="s">
         <v>542</v>
       </c>
     </row>
     <row r="183" spans="1:6">
-      <c r="A183" s="13">
+      <c r="A183" s="11">
         <v>176</v>
       </c>
-      <c r="B183" s="14" t="s">
+      <c r="B183" s="12" t="s">
         <v>543</v>
       </c>
-      <c r="C183" s="15" t="s">
+      <c r="C183" s="13" t="s">
         <v>544</v>
       </c>
-      <c r="D183" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E183" s="16"/>
-      <c r="F183" s="17" t="s">
+      <c r="D183" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E183" s="14"/>
+      <c r="F183" s="15" t="s">
         <v>545</v>
       </c>
     </row>
     <row r="184" spans="1:6">
-      <c r="A184" s="13">
+      <c r="A184" s="11">
         <v>177</v>
       </c>
-      <c r="B184" s="14" t="s">
+      <c r="B184" s="12" t="s">
         <v>546</v>
       </c>
-      <c r="C184" s="15" t="s">
+      <c r="C184" s="13" t="s">
         <v>547</v>
       </c>
-      <c r="D184" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E184" s="16"/>
-      <c r="F184" s="17" t="s">
+      <c r="D184" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E184" s="14"/>
+      <c r="F184" s="15" t="s">
         <v>548</v>
       </c>
     </row>
     <row r="185" spans="1:6">
-      <c r="A185" s="13">
+      <c r="A185" s="11">
         <v>178</v>
       </c>
-      <c r="B185" s="14" t="s">
+      <c r="B185" s="12" t="s">
         <v>549</v>
       </c>
-      <c r="C185" s="15" t="s">
+      <c r="C185" s="13" t="s">
         <v>550</v>
       </c>
-      <c r="D185" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E185" s="16"/>
-      <c r="F185" s="17" t="s">
+      <c r="D185" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E185" s="14"/>
+      <c r="F185" s="15" t="s">
         <v>551</v>
       </c>
     </row>
     <row r="186" spans="1:6">
-      <c r="A186" s="13">
+      <c r="A186" s="11">
         <v>179</v>
       </c>
-      <c r="B186" s="14" t="s">
+      <c r="B186" s="12" t="s">
         <v>552</v>
       </c>
-      <c r="C186" s="15" t="s">
+      <c r="C186" s="13" t="s">
         <v>553</v>
       </c>
-      <c r="D186" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E186" s="16"/>
-      <c r="F186" s="17" t="s">
+      <c r="D186" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E186" s="14"/>
+      <c r="F186" s="15" t="s">
         <v>554</v>
       </c>
     </row>
     <row r="187" spans="1:6">
-      <c r="A187" s="13">
+      <c r="A187" s="11">
         <v>180</v>
       </c>
-      <c r="B187" s="14" t="s">
+      <c r="B187" s="12" t="s">
         <v>555</v>
       </c>
-      <c r="C187" s="15" t="s">
+      <c r="C187" s="13" t="s">
         <v>556</v>
       </c>
-      <c r="D187" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E187" s="16"/>
-      <c r="F187" s="17" t="s">
+      <c r="D187" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E187" s="14"/>
+      <c r="F187" s="15" t="s">
         <v>557</v>
       </c>
     </row>
     <row r="188" spans="1:6">
-      <c r="A188" s="13">
+      <c r="A188" s="11">
         <v>181</v>
       </c>
-      <c r="B188" s="14" t="s">
+      <c r="B188" s="12" t="s">
         <v>558</v>
       </c>
-      <c r="C188" s="15" t="s">
+      <c r="C188" s="13" t="s">
         <v>559</v>
       </c>
-      <c r="D188" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E188" s="16"/>
-      <c r="F188" s="17" t="s">
+      <c r="D188" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E188" s="14"/>
+      <c r="F188" s="15" t="s">
         <v>560</v>
       </c>
     </row>
     <row r="189" spans="1:6">
-      <c r="A189" s="13">
+      <c r="A189" s="11">
         <v>182</v>
       </c>
-      <c r="B189" s="14" t="s">
+      <c r="B189" s="12" t="s">
         <v>561</v>
       </c>
-      <c r="C189" s="15" t="s">
+      <c r="C189" s="13" t="s">
         <v>562</v>
       </c>
-      <c r="D189" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E189" s="16"/>
-      <c r="F189" s="17" t="s">
+      <c r="D189" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E189" s="14"/>
+      <c r="F189" s="15" t="s">
         <v>563</v>
       </c>
     </row>
     <row r="190" spans="1:6">
-      <c r="A190" s="13">
+      <c r="A190" s="11">
         <v>183</v>
       </c>
-      <c r="B190" s="14" t="s">
+      <c r="B190" s="12" t="s">
         <v>564</v>
       </c>
-      <c r="C190" s="15" t="s">
+      <c r="C190" s="13" t="s">
         <v>565</v>
       </c>
-      <c r="D190" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E190" s="16"/>
-      <c r="F190" s="17" t="s">
+      <c r="D190" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E190" s="14"/>
+      <c r="F190" s="15" t="s">
         <v>566</v>
       </c>
     </row>
     <row r="191" spans="1:6">
-      <c r="A191" s="13">
+      <c r="A191" s="11">
         <v>184</v>
       </c>
-      <c r="B191" s="14" t="s">
+      <c r="B191" s="12" t="s">
         <v>567</v>
       </c>
-      <c r="C191" s="15" t="s">
+      <c r="C191" s="13" t="s">
         <v>568</v>
       </c>
-      <c r="D191" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E191" s="16"/>
-      <c r="F191" s="17" t="s">
+      <c r="D191" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E191" s="14"/>
+      <c r="F191" s="15" t="s">
         <v>569</v>
       </c>
     </row>
     <row r="192" spans="1:6">
-      <c r="A192" s="13">
+      <c r="A192" s="11">
         <v>185</v>
       </c>
-      <c r="B192" s="14" t="s">
+      <c r="B192" s="12" t="s">
         <v>570</v>
       </c>
-      <c r="C192" s="15" t="s">
+      <c r="C192" s="13" t="s">
         <v>571</v>
       </c>
-      <c r="D192" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E192" s="16"/>
-      <c r="F192" s="17" t="s">
+      <c r="D192" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E192" s="14"/>
+      <c r="F192" s="15" t="s">
         <v>572</v>
       </c>
     </row>
     <row r="193" spans="1:6">
-      <c r="A193" s="13">
+      <c r="A193" s="11">
         <v>186</v>
       </c>
-      <c r="B193" s="14" t="s">
+      <c r="B193" s="12" t="s">
         <v>573</v>
       </c>
-      <c r="C193" s="15" t="s">
+      <c r="C193" s="13" t="s">
         <v>574</v>
       </c>
-      <c r="D193" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E193" s="16"/>
-      <c r="F193" s="17" t="s">
+      <c r="D193" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E193" s="14"/>
+      <c r="F193" s="15" t="s">
         <v>575</v>
       </c>
     </row>
     <row r="194" spans="1:6">
-      <c r="A194" s="13">
+      <c r="A194" s="11">
         <v>187</v>
       </c>
-      <c r="B194" s="14" t="s">
+      <c r="B194" s="12" t="s">
         <v>576</v>
       </c>
-      <c r="C194" s="15" t="s">
+      <c r="C194" s="13" t="s">
         <v>577</v>
       </c>
-      <c r="D194" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E194" s="16"/>
-      <c r="F194" s="17" t="s">
+      <c r="D194" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E194" s="14"/>
+      <c r="F194" s="15" t="s">
         <v>578</v>
       </c>
     </row>
     <row r="195" spans="1:6">
-      <c r="A195" s="13">
+      <c r="A195" s="11">
         <v>188</v>
       </c>
-      <c r="B195" s="14" t="s">
+      <c r="B195" s="12" t="s">
         <v>579</v>
       </c>
-      <c r="C195" s="15" t="s">
+      <c r="C195" s="13" t="s">
         <v>580</v>
       </c>
-      <c r="D195" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E195" s="16"/>
-      <c r="F195" s="17" t="s">
+      <c r="D195" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E195" s="14"/>
+      <c r="F195" s="15" t="s">
         <v>581</v>
       </c>
     </row>
     <row r="196" spans="1:6">
-      <c r="A196" s="13">
+      <c r="A196" s="11">
         <v>189</v>
       </c>
-      <c r="B196" s="14" t="s">
+      <c r="B196" s="12" t="s">
         <v>582</v>
       </c>
-      <c r="C196" s="15" t="s">
+      <c r="C196" s="13" t="s">
         <v>583</v>
       </c>
-      <c r="D196" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E196" s="16"/>
-      <c r="F196" s="17" t="s">
+      <c r="D196" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E196" s="14"/>
+      <c r="F196" s="15" t="s">
         <v>584</v>
       </c>
     </row>
     <row r="197" spans="1:6">
-      <c r="A197" s="13">
+      <c r="A197" s="11">
         <v>190</v>
       </c>
-      <c r="B197" s="14" t="s">
+      <c r="B197" s="12" t="s">
         <v>585</v>
       </c>
-      <c r="C197" s="15" t="s">
+      <c r="C197" s="13" t="s">
         <v>586</v>
       </c>
-      <c r="D197" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E197" s="16"/>
-      <c r="F197" s="17" t="s">
+      <c r="D197" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E197" s="14"/>
+      <c r="F197" s="15" t="s">
         <v>587</v>
       </c>
     </row>
     <row r="198" spans="1:6">
-      <c r="A198" s="13">
+      <c r="A198" s="11">
         <v>191</v>
       </c>
-      <c r="B198" s="14" t="s">
+      <c r="B198" s="12" t="s">
         <v>588</v>
       </c>
-      <c r="C198" s="15" t="s">
+      <c r="C198" s="13" t="s">
         <v>589</v>
       </c>
-      <c r="D198" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E198" s="16"/>
-      <c r="F198" s="17" t="s">
+      <c r="D198" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E198" s="14"/>
+      <c r="F198" s="15" t="s">
         <v>590</v>
       </c>
     </row>
     <row r="199" spans="1:6">
-      <c r="A199" s="13">
+      <c r="A199" s="11">
         <v>192</v>
       </c>
-      <c r="B199" s="14" t="s">
+      <c r="B199" s="12" t="s">
         <v>591</v>
       </c>
-      <c r="C199" s="15" t="s">
+      <c r="C199" s="13" t="s">
         <v>592</v>
       </c>
-      <c r="D199" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E199" s="16"/>
-      <c r="F199" s="17" t="s">
+      <c r="D199" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E199" s="14"/>
+      <c r="F199" s="15" t="s">
         <v>593</v>
       </c>
     </row>
     <row r="200" spans="1:6">
-      <c r="A200" s="13">
+      <c r="A200" s="11">
         <v>193</v>
       </c>
-      <c r="B200" s="14" t="s">
+      <c r="B200" s="12" t="s">
         <v>594</v>
       </c>
-      <c r="C200" s="15" t="s">
+      <c r="C200" s="13" t="s">
         <v>595</v>
       </c>
-      <c r="D200" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E200" s="16"/>
-      <c r="F200" s="17" t="s">
+      <c r="D200" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E200" s="14"/>
+      <c r="F200" s="15" t="s">
         <v>596</v>
       </c>
     </row>
     <row r="201" spans="1:6">
-      <c r="A201" s="13">
+      <c r="A201" s="11">
         <v>194</v>
       </c>
-      <c r="B201" s="14" t="s">
+      <c r="B201" s="12" t="s">
         <v>597</v>
       </c>
-      <c r="C201" s="15" t="s">
+      <c r="C201" s="13" t="s">
         <v>598</v>
       </c>
-      <c r="D201" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E201" s="16"/>
-      <c r="F201" s="17" t="s">
+      <c r="D201" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E201" s="14"/>
+      <c r="F201" s="15" t="s">
         <v>599</v>
       </c>
     </row>
     <row r="202" spans="1:6">
-      <c r="A202" s="13">
+      <c r="A202" s="11">
         <v>195</v>
       </c>
-      <c r="B202" s="14" t="s">
+      <c r="B202" s="12" t="s">
         <v>600</v>
       </c>
-      <c r="C202" s="15" t="s">
+      <c r="C202" s="13" t="s">
         <v>601</v>
       </c>
-      <c r="D202" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E202" s="16"/>
-      <c r="F202" s="17" t="s">
+      <c r="D202" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E202" s="14"/>
+      <c r="F202" s="15" t="s">
         <v>602</v>
       </c>
     </row>
     <row r="203" spans="1:6">
-      <c r="A203" s="13">
+      <c r="A203" s="11">
         <v>196</v>
       </c>
-      <c r="B203" s="14" t="s">
+      <c r="B203" s="12" t="s">
         <v>603</v>
       </c>
-      <c r="C203" s="15" t="s">
+      <c r="C203" s="13" t="s">
         <v>604</v>
       </c>
-      <c r="D203" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E203" s="16"/>
-      <c r="F203" s="17" t="s">
+      <c r="D203" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E203" s="14"/>
+      <c r="F203" s="15" t="s">
         <v>605</v>
       </c>
     </row>
     <row r="204" spans="1:6">
-      <c r="A204" s="13">
+      <c r="A204" s="11">
         <v>197</v>
       </c>
-      <c r="B204" s="14" t="s">
+      <c r="B204" s="12" t="s">
         <v>606</v>
       </c>
-      <c r="C204" s="15" t="s">
+      <c r="C204" s="13" t="s">
         <v>607</v>
       </c>
-      <c r="D204" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E204" s="16"/>
-      <c r="F204" s="17" t="s">
+      <c r="D204" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E204" s="14"/>
+      <c r="F204" s="15" t="s">
         <v>608</v>
       </c>
     </row>
     <row r="205" spans="1:6">
-      <c r="A205" s="13">
+      <c r="A205" s="11">
         <v>198</v>
       </c>
-      <c r="B205" s="14" t="s">
+      <c r="B205" s="12" t="s">
         <v>609</v>
       </c>
-      <c r="C205" s="15" t="s">
+      <c r="C205" s="13" t="s">
         <v>610</v>
       </c>
-      <c r="D205" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E205" s="16"/>
-      <c r="F205" s="17" t="s">
+      <c r="D205" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E205" s="14"/>
+      <c r="F205" s="15" t="s">
         <v>611</v>
       </c>
     </row>
     <row r="206" spans="1:6">
-      <c r="A206" s="13">
+      <c r="A206" s="11">
         <v>199</v>
       </c>
-      <c r="B206" s="14" t="s">
+      <c r="B206" s="12" t="s">
         <v>612</v>
       </c>
-      <c r="C206" s="15" t="s">
+      <c r="C206" s="13" t="s">
         <v>613</v>
       </c>
-      <c r="D206" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E206" s="16"/>
-      <c r="F206" s="17" t="s">
+      <c r="D206" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E206" s="14"/>
+      <c r="F206" s="15" t="s">
         <v>614</v>
       </c>
     </row>
     <row r="207" spans="1:6">
-      <c r="A207" s="13">
+      <c r="A207" s="11">
         <v>200</v>
       </c>
-      <c r="B207" s="14" t="s">
+      <c r="B207" s="12" t="s">
         <v>615</v>
       </c>
-      <c r="C207" s="15" t="s">
+      <c r="C207" s="13" t="s">
         <v>616</v>
       </c>
-      <c r="D207" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E207" s="16"/>
-      <c r="F207" s="17" t="s">
+      <c r="D207" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E207" s="14"/>
+      <c r="F207" s="15" t="s">
         <v>617</v>
       </c>
     </row>
     <row r="208" spans="1:6">
-      <c r="A208" s="13">
+      <c r="A208" s="11">
         <v>201</v>
       </c>
-      <c r="B208" s="14" t="s">
+      <c r="B208" s="12" t="s">
         <v>618</v>
       </c>
-      <c r="C208" s="15" t="s">
+      <c r="C208" s="13" t="s">
         <v>619</v>
       </c>
-      <c r="D208" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E208" s="16"/>
-      <c r="F208" s="17" t="s">
+      <c r="D208" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E208" s="14"/>
+      <c r="F208" s="15" t="s">
         <v>620</v>
       </c>
     </row>
     <row r="209" spans="1:6">
-      <c r="A209" s="13">
+      <c r="A209" s="11">
         <v>202</v>
       </c>
-      <c r="B209" s="14" t="s">
+      <c r="B209" s="12" t="s">
         <v>621</v>
       </c>
-      <c r="C209" s="15" t="s">
+      <c r="C209" s="13" t="s">
         <v>622</v>
       </c>
-      <c r="D209" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E209" s="16"/>
-      <c r="F209" s="17" t="s">
+      <c r="D209" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E209" s="14"/>
+      <c r="F209" s="15" t="s">
         <v>623</v>
       </c>
     </row>
     <row r="210" spans="1:6">
-      <c r="A210" s="13">
+      <c r="A210" s="11">
         <v>203</v>
       </c>
-      <c r="B210" s="14" t="s">
+      <c r="B210" s="12" t="s">
         <v>624</v>
       </c>
-      <c r="C210" s="15" t="s">
+      <c r="C210" s="13" t="s">
         <v>625</v>
       </c>
-      <c r="D210" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E210" s="16"/>
-      <c r="F210" s="17" t="s">
+      <c r="D210" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E210" s="14"/>
+      <c r="F210" s="15" t="s">
         <v>626</v>
       </c>
     </row>
     <row r="211" spans="1:6">
-      <c r="A211" s="13">
+      <c r="A211" s="11">
         <v>204</v>
       </c>
-      <c r="B211" s="14" t="s">
+      <c r="B211" s="12" t="s">
         <v>627</v>
       </c>
-      <c r="C211" s="15" t="s">
+      <c r="C211" s="13" t="s">
         <v>628</v>
       </c>
-      <c r="D211" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E211" s="16"/>
-      <c r="F211" s="17" t="s">
+      <c r="D211" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E211" s="14"/>
+      <c r="F211" s="15" t="s">
         <v>629</v>
       </c>
     </row>
     <row r="212" spans="1:6">
-      <c r="A212" s="13">
+      <c r="A212" s="11">
         <v>205</v>
       </c>
-      <c r="B212" s="14" t="s">
+      <c r="B212" s="12" t="s">
         <v>630</v>
       </c>
-      <c r="C212" s="15" t="s">
+      <c r="C212" s="13" t="s">
         <v>631</v>
       </c>
-      <c r="D212" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E212" s="16"/>
-      <c r="F212" s="17" t="s">
+      <c r="D212" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E212" s="14"/>
+      <c r="F212" s="15" t="s">
         <v>632</v>
       </c>
     </row>
     <row r="213" spans="1:6">
-      <c r="A213" s="13">
+      <c r="A213" s="11">
         <v>206</v>
       </c>
-      <c r="B213" s="14" t="s">
+      <c r="B213" s="12" t="s">
         <v>633</v>
       </c>
-      <c r="C213" s="15" t="s">
+      <c r="C213" s="13" t="s">
         <v>634</v>
       </c>
-      <c r="D213" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E213" s="16"/>
-      <c r="F213" s="17" t="s">
+      <c r="D213" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E213" s="14"/>
+      <c r="F213" s="15" t="s">
         <v>635</v>
       </c>
     </row>
     <row r="214" spans="1:6">
-      <c r="A214" s="13">
+      <c r="A214" s="11">
         <v>207</v>
       </c>
-      <c r="B214" s="14" t="s">
+      <c r="B214" s="12" t="s">
         <v>636</v>
       </c>
-      <c r="C214" s="15" t="s">
+      <c r="C214" s="13" t="s">
         <v>637</v>
       </c>
-      <c r="D214" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E214" s="16"/>
-      <c r="F214" s="17" t="s">
+      <c r="D214" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E214" s="14"/>
+      <c r="F214" s="15" t="s">
         <v>638</v>
       </c>
     </row>
     <row r="215" spans="1:6">
-      <c r="A215" s="13">
+      <c r="A215" s="11">
         <v>208</v>
       </c>
-      <c r="B215" s="14" t="s">
+      <c r="B215" s="12" t="s">
         <v>639</v>
       </c>
-      <c r="C215" s="15" t="s">
+      <c r="C215" s="13" t="s">
         <v>640</v>
       </c>
-      <c r="D215" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E215" s="16"/>
-      <c r="F215" s="17" t="s">
+      <c r="D215" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E215" s="14"/>
+      <c r="F215" s="15" t="s">
         <v>641</v>
       </c>
     </row>
     <row r="216" spans="1:6">
-      <c r="A216" s="13">
+      <c r="A216" s="11">
         <v>209</v>
       </c>
-      <c r="B216" s="14" t="s">
+      <c r="B216" s="12" t="s">
         <v>642</v>
       </c>
-      <c r="C216" s="15" t="s">
+      <c r="C216" s="13" t="s">
         <v>643</v>
       </c>
-      <c r="D216" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E216" s="16"/>
-      <c r="F216" s="17" t="s">
+      <c r="D216" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E216" s="14"/>
+      <c r="F216" s="15" t="s">
         <v>644</v>
       </c>
     </row>
     <row r="217" spans="1:6">
-      <c r="A217" s="13">
+      <c r="A217" s="11">
         <v>210</v>
       </c>
-      <c r="B217" s="14" t="s">
+      <c r="B217" s="12" t="s">
         <v>645</v>
       </c>
-      <c r="C217" s="15" t="s">
+      <c r="C217" s="13" t="s">
         <v>646</v>
       </c>
-      <c r="D217" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E217" s="16"/>
-      <c r="F217" s="17" t="s">
+      <c r="D217" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E217" s="14"/>
+      <c r="F217" s="15" t="s">
         <v>647</v>
       </c>
     </row>
     <row r="218" spans="1:6">
-      <c r="A218" s="13">
+      <c r="A218" s="11">
         <v>211</v>
       </c>
-      <c r="B218" s="14" t="s">
+      <c r="B218" s="12" t="s">
         <v>648</v>
       </c>
-      <c r="C218" s="15" t="s">
+      <c r="C218" s="13" t="s">
         <v>649</v>
       </c>
-      <c r="D218" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E218" s="16"/>
-      <c r="F218" s="17" t="s">
+      <c r="D218" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E218" s="14"/>
+      <c r="F218" s="15" t="s">
         <v>650</v>
       </c>
     </row>
     <row r="219" spans="1:6">
-      <c r="A219" s="13">
+      <c r="A219" s="11">
         <v>212</v>
       </c>
-      <c r="B219" s="14" t="s">
+      <c r="B219" s="12" t="s">
         <v>651</v>
       </c>
-      <c r="C219" s="15" t="s">
+      <c r="C219" s="13" t="s">
         <v>652</v>
       </c>
-      <c r="D219" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E219" s="16"/>
-      <c r="F219" s="17" t="s">
+      <c r="D219" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E219" s="14"/>
+      <c r="F219" s="15" t="s">
         <v>653</v>
       </c>
     </row>
     <row r="220" spans="1:6">
-      <c r="A220" s="13">
+      <c r="A220" s="11">
         <v>213</v>
       </c>
-      <c r="B220" s="14" t="s">
+      <c r="B220" s="12" t="s">
         <v>654</v>
       </c>
-      <c r="C220" s="15" t="s">
+      <c r="C220" s="13" t="s">
         <v>655</v>
       </c>
-      <c r="D220" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E220" s="16"/>
-      <c r="F220" s="17" t="s">
+      <c r="D220" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E220" s="14"/>
+      <c r="F220" s="15" t="s">
         <v>656</v>
       </c>
     </row>
     <row r="221" spans="1:6">
-      <c r="A221" s="13">
+      <c r="A221" s="11">
         <v>214</v>
       </c>
-      <c r="B221" s="14" t="s">
+      <c r="B221" s="12" t="s">
         <v>657</v>
       </c>
-      <c r="C221" s="15" t="s">
+      <c r="C221" s="13" t="s">
         <v>658</v>
       </c>
-      <c r="D221" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E221" s="16"/>
-      <c r="F221" s="17" t="s">
+      <c r="D221" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E221" s="14"/>
+      <c r="F221" s="15" t="s">
         <v>659</v>
       </c>
     </row>
     <row r="222" spans="1:6">
-      <c r="A222" s="13">
+      <c r="A222" s="11">
         <v>215</v>
       </c>
-      <c r="B222" s="14" t="s">
+      <c r="B222" s="12" t="s">
         <v>660</v>
       </c>
-      <c r="C222" s="15" t="s">
+      <c r="C222" s="13" t="s">
         <v>661</v>
       </c>
-      <c r="D222" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E222" s="16"/>
-      <c r="F222" s="17" t="s">
+      <c r="D222" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E222" s="14"/>
+      <c r="F222" s="15" t="s">
         <v>662</v>
       </c>
     </row>
     <row r="223" spans="1:6">
-      <c r="A223" s="13">
+      <c r="A223" s="11">
         <v>216</v>
       </c>
-      <c r="B223" s="14" t="s">
+      <c r="B223" s="12" t="s">
         <v>663</v>
       </c>
-      <c r="C223" s="15" t="s">
+      <c r="C223" s="13" t="s">
         <v>664</v>
       </c>
-      <c r="D223" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E223" s="16"/>
-      <c r="F223" s="17" t="s">
+      <c r="D223" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E223" s="14"/>
+      <c r="F223" s="15" t="s">
         <v>665</v>
       </c>
     </row>
     <row r="224" spans="1:6">
-      <c r="A224" s="13">
+      <c r="A224" s="11">
         <v>217</v>
       </c>
-      <c r="B224" s="14" t="s">
+      <c r="B224" s="12" t="s">
         <v>666</v>
       </c>
-      <c r="C224" s="15" t="s">
+      <c r="C224" s="13" t="s">
         <v>667</v>
       </c>
-      <c r="D224" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E224" s="16"/>
-      <c r="F224" s="17" t="s">
+      <c r="D224" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E224" s="14"/>
+      <c r="F224" s="15" t="s">
         <v>668</v>
       </c>
     </row>
     <row r="225" spans="1:6">
-      <c r="A225" s="13">
+      <c r="A225" s="11">
         <v>218</v>
       </c>
-      <c r="B225" s="14" t="s">
+      <c r="B225" s="12" t="s">
         <v>669</v>
       </c>
-      <c r="C225" s="15" t="s">
+      <c r="C225" s="13" t="s">
         <v>670</v>
       </c>
-      <c r="D225" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E225" s="16"/>
-      <c r="F225" s="17" t="s">
+      <c r="D225" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E225" s="14"/>
+      <c r="F225" s="15" t="s">
         <v>671</v>
       </c>
     </row>
     <row r="226" spans="1:6">
-      <c r="A226" s="13">
+      <c r="A226" s="11">
         <v>219</v>
       </c>
-      <c r="B226" s="14" t="s">
+      <c r="B226" s="12" t="s">
         <v>672</v>
       </c>
-      <c r="C226" s="15" t="s">
+      <c r="C226" s="13" t="s">
         <v>673</v>
       </c>
-      <c r="D226" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E226" s="16"/>
-      <c r="F226" s="17" t="s">
+      <c r="D226" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E226" s="14"/>
+      <c r="F226" s="15" t="s">
         <v>674</v>
       </c>
     </row>
     <row r="227" spans="1:6">
-      <c r="A227" s="13">
+      <c r="A227" s="11">
         <v>220</v>
       </c>
-      <c r="B227" s="14" t="s">
+      <c r="B227" s="12" t="s">
         <v>675</v>
       </c>
-      <c r="C227" s="15" t="s">
+      <c r="C227" s="13" t="s">
         <v>676</v>
       </c>
-      <c r="D227" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E227" s="16"/>
-      <c r="F227" s="17" t="s">
+      <c r="D227" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E227" s="14"/>
+      <c r="F227" s="15" t="s">
         <v>677</v>
       </c>
     </row>
     <row r="228" spans="1:6">
-      <c r="A228" s="13">
+      <c r="A228" s="11">
         <v>221</v>
       </c>
-      <c r="B228" s="14" t="s">
+      <c r="B228" s="12" t="s">
         <v>678</v>
       </c>
-      <c r="C228" s="15" t="s">
+      <c r="C228" s="13" t="s">
         <v>679</v>
       </c>
-      <c r="D228" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E228" s="16"/>
-      <c r="F228" s="17" t="s">
+      <c r="D228" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E228" s="14"/>
+      <c r="F228" s="15" t="s">
         <v>680</v>
       </c>
     </row>
     <row r="229" spans="1:6">
-      <c r="A229" s="13">
+      <c r="A229" s="11">
         <v>222</v>
       </c>
-      <c r="B229" s="14" t="s">
+      <c r="B229" s="12" t="s">
         <v>681</v>
       </c>
-      <c r="C229" s="15" t="s">
+      <c r="C229" s="13" t="s">
         <v>682</v>
       </c>
-      <c r="D229" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E229" s="16"/>
-      <c r="F229" s="17" t="s">
+      <c r="D229" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E229" s="14"/>
+      <c r="F229" s="15" t="s">
         <v>683</v>
       </c>
     </row>
     <row r="230" spans="1:6">
-      <c r="A230" s="13">
+      <c r="A230" s="11">
         <v>223</v>
       </c>
-      <c r="B230" s="14" t="s">
+      <c r="B230" s="12" t="s">
         <v>684</v>
       </c>
-      <c r="C230" s="15" t="s">
+      <c r="C230" s="13" t="s">
         <v>685</v>
       </c>
-      <c r="D230" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E230" s="16"/>
-      <c r="F230" s="17" t="s">
+      <c r="D230" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E230" s="14"/>
+      <c r="F230" s="15" t="s">
         <v>686</v>
       </c>
     </row>
     <row r="231" spans="1:6">
-      <c r="A231" s="13">
+      <c r="A231" s="11">
         <v>224</v>
       </c>
-      <c r="B231" s="14" t="s">
+      <c r="B231" s="12" t="s">
         <v>687</v>
       </c>
-      <c r="C231" s="15" t="s">
+      <c r="C231" s="13" t="s">
         <v>688</v>
       </c>
-      <c r="D231" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E231" s="16"/>
-      <c r="F231" s="17" t="s">
+      <c r="D231" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E231" s="14"/>
+      <c r="F231" s="15" t="s">
         <v>689</v>
       </c>
     </row>
     <row r="232" spans="1:6">
-      <c r="A232" s="13">
+      <c r="A232" s="11">
         <v>225</v>
       </c>
-      <c r="B232" s="14" t="s">
+      <c r="B232" s="12" t="s">
         <v>690</v>
       </c>
-      <c r="C232" s="15" t="s">
+      <c r="C232" s="13" t="s">
         <v>691</v>
       </c>
-      <c r="D232" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E232" s="16"/>
-      <c r="F232" s="17" t="s">
+      <c r="D232" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E232" s="14"/>
+      <c r="F232" s="15" t="s">
         <v>692</v>
       </c>
     </row>
     <row r="233" spans="1:6">
-      <c r="A233" s="13">
+      <c r="A233" s="11">
         <v>226</v>
       </c>
-      <c r="B233" s="14" t="s">
+      <c r="B233" s="12" t="s">
         <v>693</v>
       </c>
-      <c r="C233" s="15" t="s">
+      <c r="C233" s="13" t="s">
         <v>694</v>
       </c>
-      <c r="D233" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E233" s="16"/>
-      <c r="F233" s="17" t="s">
+      <c r="D233" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E233" s="14"/>
+      <c r="F233" s="15" t="s">
         <v>695</v>
       </c>
     </row>
     <row r="234" spans="1:6">
-      <c r="A234" s="13">
+      <c r="A234" s="11">
         <v>227</v>
       </c>
-      <c r="B234" s="14" t="s">
+      <c r="B234" s="12" t="s">
         <v>696</v>
       </c>
-      <c r="C234" s="15" t="s">
+      <c r="C234" s="13" t="s">
         <v>697</v>
       </c>
-      <c r="D234" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E234" s="16"/>
-      <c r="F234" s="17" t="s">
+      <c r="D234" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E234" s="14"/>
+      <c r="F234" s="15" t="s">
         <v>698</v>
       </c>
     </row>
     <row r="235" spans="1:6">
-      <c r="A235" s="13">
+      <c r="A235" s="11">
         <v>228</v>
       </c>
-      <c r="B235" s="14" t="s">
+      <c r="B235" s="12" t="s">
         <v>699</v>
       </c>
-      <c r="C235" s="15" t="s">
+      <c r="C235" s="13" t="s">
         <v>700</v>
       </c>
-      <c r="D235" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E235" s="16"/>
-      <c r="F235" s="17" t="s">
+      <c r="D235" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E235" s="14"/>
+      <c r="F235" s="15" t="s">
         <v>701</v>
       </c>
     </row>
     <row r="236" spans="1:6">
-      <c r="A236" s="13">
+      <c r="A236" s="11">
         <v>229</v>
       </c>
-      <c r="B236" s="14" t="s">
+      <c r="B236" s="12" t="s">
         <v>702</v>
       </c>
-      <c r="C236" s="15" t="s">
+      <c r="C236" s="13" t="s">
         <v>703</v>
       </c>
-      <c r="D236" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E236" s="16"/>
-      <c r="F236" s="17" t="s">
+      <c r="D236" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E236" s="14"/>
+      <c r="F236" s="15" t="s">
         <v>704</v>
       </c>
     </row>
     <row r="237" spans="1:6">
-      <c r="A237" s="13">
+      <c r="A237" s="11">
         <v>230</v>
       </c>
-      <c r="B237" s="14" t="s">
+      <c r="B237" s="12" t="s">
         <v>705</v>
       </c>
-      <c r="C237" s="15" t="s">
+      <c r="C237" s="13" t="s">
         <v>706</v>
       </c>
-      <c r="D237" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E237" s="16"/>
-      <c r="F237" s="17" t="s">
+      <c r="D237" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E237" s="14"/>
+      <c r="F237" s="15" t="s">
         <v>707</v>
       </c>
     </row>
     <row r="238" spans="1:6">
-      <c r="A238" s="13">
+      <c r="A238" s="11">
         <v>231</v>
       </c>
-      <c r="B238" s="14" t="s">
+      <c r="B238" s="12" t="s">
         <v>708</v>
       </c>
-      <c r="C238" s="15" t="s">
+      <c r="C238" s="13" t="s">
         <v>709</v>
       </c>
-      <c r="D238" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E238" s="16"/>
-      <c r="F238" s="17" t="s">
+      <c r="D238" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E238" s="14"/>
+      <c r="F238" s="15" t="s">
         <v>710</v>
       </c>
     </row>
     <row r="239" spans="1:6">
-      <c r="A239" s="13">
+      <c r="A239" s="11">
         <v>232</v>
       </c>
-      <c r="B239" s="14" t="s">
+      <c r="B239" s="12" t="s">
         <v>711</v>
       </c>
-      <c r="C239" s="15" t="s">
+      <c r="C239" s="13" t="s">
         <v>712</v>
       </c>
-      <c r="D239" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E239" s="16"/>
-      <c r="F239" s="17" t="s">
+      <c r="D239" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E239" s="14"/>
+      <c r="F239" s="15" t="s">
         <v>713</v>
       </c>
     </row>
     <row r="240" spans="1:6">
-      <c r="A240" s="13">
+      <c r="A240" s="11">
         <v>233</v>
       </c>
-      <c r="B240" s="14" t="s">
+      <c r="B240" s="12" t="s">
         <v>714</v>
       </c>
-      <c r="C240" s="15" t="s">
+      <c r="C240" s="13" t="s">
         <v>715</v>
       </c>
-      <c r="D240" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E240" s="16"/>
-      <c r="F240" s="17" t="s">
+      <c r="D240" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E240" s="14"/>
+      <c r="F240" s="15" t="s">
         <v>716</v>
       </c>
     </row>
     <row r="241" spans="1:6">
-      <c r="A241" s="13">
+      <c r="A241" s="11">
         <v>234</v>
       </c>
-      <c r="B241" s="14" t="s">
+      <c r="B241" s="12" t="s">
         <v>717</v>
       </c>
-      <c r="C241" s="15" t="s">
+      <c r="C241" s="13" t="s">
         <v>718</v>
       </c>
-      <c r="D241" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E241" s="16"/>
-      <c r="F241" s="17" t="s">
+      <c r="D241" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E241" s="14"/>
+      <c r="F241" s="15" t="s">
         <v>719</v>
       </c>
     </row>
     <row r="242" spans="1:6">
-      <c r="A242" s="13">
+      <c r="A242" s="11">
         <v>235</v>
       </c>
-      <c r="B242" s="14" t="s">
+      <c r="B242" s="12" t="s">
         <v>720</v>
       </c>
-      <c r="C242" s="15" t="s">
+      <c r="C242" s="13" t="s">
         <v>721</v>
       </c>
-      <c r="D242" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E242" s="16"/>
-      <c r="F242" s="17" t="s">
+      <c r="D242" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E242" s="14"/>
+      <c r="F242" s="15" t="s">
         <v>722</v>
       </c>
     </row>
     <row r="243" spans="1:6">
-      <c r="A243" s="13">
+      <c r="A243" s="11">
         <v>236</v>
       </c>
-      <c r="B243" s="14" t="s">
+      <c r="B243" s="12" t="s">
         <v>723</v>
       </c>
-      <c r="C243" s="15" t="s">
+      <c r="C243" s="13" t="s">
         <v>724</v>
       </c>
-      <c r="D243" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E243" s="16"/>
-      <c r="F243" s="17" t="s">
+      <c r="D243" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E243" s="14"/>
+      <c r="F243" s="15" t="s">
         <v>725</v>
       </c>
     </row>
     <row r="244" spans="1:6">
-      <c r="A244" s="13">
+      <c r="A244" s="11">
         <v>237</v>
       </c>
-      <c r="B244" s="14" t="s">
+      <c r="B244" s="12" t="s">
         <v>726</v>
       </c>
-      <c r="C244" s="15" t="s">
+      <c r="C244" s="13" t="s">
         <v>727</v>
       </c>
-      <c r="D244" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E244" s="16"/>
-      <c r="F244" s="17" t="s">
+      <c r="D244" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E244" s="14"/>
+      <c r="F244" s="15" t="s">
         <v>728</v>
       </c>
     </row>
     <row r="245" spans="1:6">
-      <c r="A245" s="13">
+      <c r="A245" s="11">
         <v>238</v>
       </c>
-      <c r="B245" s="14" t="s">
+      <c r="B245" s="12" t="s">
         <v>729</v>
       </c>
-      <c r="C245" s="15" t="s">
+      <c r="C245" s="13" t="s">
         <v>730</v>
       </c>
-      <c r="D245" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E245" s="16"/>
-      <c r="F245" s="17" t="s">
+      <c r="D245" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E245" s="14"/>
+      <c r="F245" s="15" t="s">
         <v>731</v>
       </c>
     </row>
     <row r="246" spans="1:6">
-      <c r="A246" s="13">
+      <c r="A246" s="11">
         <v>239</v>
       </c>
-      <c r="B246" s="14" t="s">
+      <c r="B246" s="12" t="s">
         <v>732</v>
       </c>
-      <c r="C246" s="15" t="s">
+      <c r="C246" s="13" t="s">
         <v>733</v>
       </c>
-      <c r="D246" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E246" s="16"/>
-      <c r="F246" s="17" t="s">
+      <c r="D246" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E246" s="14"/>
+      <c r="F246" s="15" t="s">
         <v>734</v>
       </c>
     </row>
     <row r="247" spans="1:6">
-      <c r="A247" s="13">
+      <c r="A247" s="11">
         <v>240</v>
       </c>
-      <c r="B247" s="14" t="s">
+      <c r="B247" s="12" t="s">
         <v>735</v>
       </c>
-      <c r="C247" s="15" t="s">
+      <c r="C247" s="13" t="s">
         <v>736</v>
       </c>
-      <c r="D247" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E247" s="16"/>
-      <c r="F247" s="17" t="s">
+      <c r="D247" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E247" s="14"/>
+      <c r="F247" s="15" t="s">
         <v>737</v>
       </c>
     </row>
     <row r="248" spans="1:6">
-      <c r="A248" s="13">
+      <c r="A248" s="11">
         <v>241</v>
       </c>
-      <c r="B248" s="14" t="s">
+      <c r="B248" s="12" t="s">
         <v>738</v>
       </c>
-      <c r="C248" s="15" t="s">
+      <c r="C248" s="13" t="s">
         <v>739</v>
       </c>
-      <c r="D248" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E248" s="16"/>
-      <c r="F248" s="17" t="s">
+      <c r="D248" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E248" s="14"/>
+      <c r="F248" s="15" t="s">
         <v>740</v>
       </c>
     </row>
     <row r="249" spans="1:6">
-      <c r="A249" s="13">
+      <c r="A249" s="11">
         <v>242</v>
       </c>
-      <c r="B249" s="14" t="s">
+      <c r="B249" s="12" t="s">
         <v>741</v>
       </c>
-      <c r="C249" s="15" t="s">
+      <c r="C249" s="13" t="s">
         <v>742</v>
       </c>
-      <c r="D249" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E249" s="16"/>
-      <c r="F249" s="17" t="s">
+      <c r="D249" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E249" s="14"/>
+      <c r="F249" s="15" t="s">
         <v>743</v>
       </c>
     </row>
     <row r="250" spans="1:6">
-      <c r="A250" s="13">
+      <c r="A250" s="11">
         <v>243</v>
       </c>
-      <c r="B250" s="14" t="s">
+      <c r="B250" s="12" t="s">
         <v>744</v>
       </c>
-      <c r="C250" s="15" t="s">
+      <c r="C250" s="13" t="s">
         <v>745</v>
       </c>
-      <c r="D250" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E250" s="16"/>
-      <c r="F250" s="17" t="s">
+      <c r="D250" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E250" s="14"/>
+      <c r="F250" s="15" t="s">
         <v>746</v>
       </c>
     </row>
     <row r="251" spans="1:6">
-      <c r="A251" s="13">
+      <c r="A251" s="11">
         <v>244</v>
       </c>
-      <c r="B251" s="14" t="s">
+      <c r="B251" s="12" t="s">
         <v>747</v>
       </c>
-      <c r="C251" s="15" t="s">
+      <c r="C251" s="13" t="s">
         <v>748</v>
       </c>
-      <c r="D251" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E251" s="16"/>
-      <c r="F251" s="17" t="s">
+      <c r="D251" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E251" s="14"/>
+      <c r="F251" s="15" t="s">
         <v>749</v>
       </c>
     </row>
     <row r="252" spans="1:6">
-      <c r="A252" s="13">
+      <c r="A252" s="11">
         <v>245</v>
       </c>
-      <c r="B252" s="14" t="s">
+      <c r="B252" s="12" t="s">
         <v>750</v>
       </c>
-      <c r="C252" s="15" t="s">
+      <c r="C252" s="13" t="s">
         <v>751</v>
       </c>
-      <c r="D252" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E252" s="16"/>
-      <c r="F252" s="17" t="s">
+      <c r="D252" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E252" s="14"/>
+      <c r="F252" s="15" t="s">
         <v>752</v>
       </c>
     </row>
     <row r="253" spans="1:6">
-      <c r="A253" s="13">
+      <c r="A253" s="11">
         <v>246</v>
       </c>
-      <c r="B253" s="14" t="s">
+      <c r="B253" s="12" t="s">
         <v>753</v>
       </c>
-      <c r="C253" s="15" t="s">
+      <c r="C253" s="13" t="s">
         <v>754</v>
       </c>
-      <c r="D253" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E253" s="16"/>
-      <c r="F253" s="17" t="s">
+      <c r="D253" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E253" s="14"/>
+      <c r="F253" s="15" t="s">
         <v>755</v>
       </c>
     </row>
     <row r="254" spans="1:6">
-      <c r="A254" s="13">
+      <c r="A254" s="11">
         <v>247</v>
       </c>
-      <c r="B254" s="14" t="s">
+      <c r="B254" s="12" t="s">
         <v>756</v>
       </c>
-      <c r="C254" s="15" t="s">
+      <c r="C254" s="13" t="s">
         <v>757</v>
       </c>
-      <c r="D254" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E254" s="16"/>
-      <c r="F254" s="17" t="s">
+      <c r="D254" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E254" s="14"/>
+      <c r="F254" s="15" t="s">
         <v>758</v>
       </c>
     </row>
     <row r="255" spans="1:6">
-      <c r="A255" s="13">
+      <c r="A255" s="11">
         <v>248</v>
       </c>
-      <c r="B255" s="14" t="s">
+      <c r="B255" s="12" t="s">
         <v>759</v>
       </c>
-      <c r="C255" s="15" t="s">
+      <c r="C255" s="13" t="s">
         <v>760</v>
       </c>
-      <c r="D255" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E255" s="16"/>
-      <c r="F255" s="17" t="s">
+      <c r="D255" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E255" s="14"/>
+      <c r="F255" s="15" t="s">
         <v>761</v>
       </c>
     </row>
     <row r="256" spans="1:6">
-      <c r="A256" s="13">
+      <c r="A256" s="11">
         <v>249</v>
       </c>
-      <c r="B256" s="14" t="s">
+      <c r="B256" s="12" t="s">
         <v>762</v>
       </c>
-      <c r="C256" s="15" t="s">
+      <c r="C256" s="13" t="s">
         <v>763</v>
       </c>
-      <c r="D256" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E256" s="16"/>
-      <c r="F256" s="17" t="s">
+      <c r="D256" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E256" s="14"/>
+      <c r="F256" s="15" t="s">
         <v>764</v>
       </c>
     </row>
     <row r="257" spans="1:6">
-      <c r="A257" s="13">
+      <c r="A257" s="11">
         <v>250</v>
       </c>
-      <c r="B257" s="14" t="s">
+      <c r="B257" s="12" t="s">
         <v>765</v>
       </c>
-      <c r="C257" s="15" t="s">
+      <c r="C257" s="13" t="s">
         <v>766</v>
       </c>
-      <c r="D257" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E257" s="16"/>
-      <c r="F257" s="17" t="s">
+      <c r="D257" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E257" s="14"/>
+      <c r="F257" s="15" t="s">
         <v>767</v>
       </c>
     </row>
     <row r="258" spans="1:6">
-      <c r="A258" s="13">
+      <c r="A258" s="11">
         <v>251</v>
       </c>
-      <c r="B258" s="14" t="s">
+      <c r="B258" s="12" t="s">
         <v>768</v>
       </c>
-      <c r="C258" s="15" t="s">
+      <c r="C258" s="13" t="s">
         <v>769</v>
       </c>
-      <c r="D258" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E258" s="16"/>
-      <c r="F258" s="17" t="s">
+      <c r="D258" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E258" s="14"/>
+      <c r="F258" s="15" t="s">
         <v>770</v>
       </c>
     </row>
     <row r="259" spans="1:6">
-      <c r="A259" s="13">
+      <c r="A259" s="11">
         <v>252</v>
       </c>
-      <c r="B259" s="14" t="s">
+      <c r="B259" s="12" t="s">
         <v>771</v>
       </c>
-      <c r="C259" s="15" t="s">
+      <c r="C259" s="13" t="s">
         <v>772</v>
       </c>
-      <c r="D259" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E259" s="16"/>
-      <c r="F259" s="17" t="s">
+      <c r="D259" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E259" s="14"/>
+      <c r="F259" s="15" t="s">
         <v>773</v>
       </c>
     </row>
     <row r="260" spans="1:6">
-      <c r="A260" s="13">
+      <c r="A260" s="11">
         <v>253</v>
       </c>
-      <c r="B260" s="14" t="s">
+      <c r="B260" s="12" t="s">
         <v>774</v>
       </c>
-      <c r="C260" s="15" t="s">
+      <c r="C260" s="13" t="s">
         <v>775</v>
       </c>
-      <c r="D260" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E260" s="16"/>
-      <c r="F260" s="17" t="s">
+      <c r="D260" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E260" s="14"/>
+      <c r="F260" s="15" t="s">
         <v>776</v>
       </c>
     </row>
     <row r="261" spans="1:6">
-      <c r="A261" s="13">
+      <c r="A261" s="11">
         <v>254</v>
       </c>
-      <c r="B261" s="14" t="s">
+      <c r="B261" s="12" t="s">
         <v>777</v>
       </c>
-      <c r="C261" s="15" t="s">
+      <c r="C261" s="13" t="s">
         <v>778</v>
       </c>
-      <c r="D261" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E261" s="16"/>
-      <c r="F261" s="17" t="s">
+      <c r="D261" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E261" s="14"/>
+      <c r="F261" s="15" t="s">
         <v>779</v>
       </c>
     </row>
     <row r="262" spans="1:6">
-      <c r="A262" s="13">
+      <c r="A262" s="11">
         <v>255</v>
       </c>
-      <c r="B262" s="14" t="s">
+      <c r="B262" s="12" t="s">
         <v>780</v>
       </c>
-      <c r="C262" s="15" t="s">
+      <c r="C262" s="13" t="s">
         <v>781</v>
       </c>
-      <c r="D262" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E262" s="16"/>
-      <c r="F262" s="17" t="s">
+      <c r="D262" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E262" s="14"/>
+      <c r="F262" s="15" t="s">
         <v>782</v>
       </c>
     </row>
     <row r="263" spans="1:6">
-      <c r="A263" s="13">
+      <c r="A263" s="11">
         <v>256</v>
       </c>
-      <c r="B263" s="14" t="s">
+      <c r="B263" s="12" t="s">
         <v>783</v>
       </c>
-      <c r="C263" s="15" t="s">
+      <c r="C263" s="13" t="s">
         <v>784</v>
       </c>
-      <c r="D263" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E263" s="16"/>
-      <c r="F263" s="17" t="s">
+      <c r="D263" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E263" s="14"/>
+      <c r="F263" s="15" t="s">
         <v>785</v>
       </c>
     </row>
     <row r="264" spans="1:6">
-      <c r="A264" s="13">
+      <c r="A264" s="11">
         <v>257</v>
       </c>
-      <c r="B264" s="14" t="s">
+      <c r="B264" s="12" t="s">
         <v>786</v>
       </c>
-      <c r="C264" s="15" t="s">
+      <c r="C264" s="13" t="s">
         <v>787</v>
       </c>
-      <c r="D264" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E264" s="16"/>
-      <c r="F264" s="17" t="s">
+      <c r="D264" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E264" s="14"/>
+      <c r="F264" s="15" t="s">
         <v>788</v>
       </c>
     </row>
     <row r="265" spans="1:6">
-      <c r="A265" s="13">
+      <c r="A265" s="11">
         <v>258</v>
       </c>
-      <c r="B265" s="14" t="s">
+      <c r="B265" s="12" t="s">
         <v>789</v>
       </c>
-      <c r="C265" s="15" t="s">
+      <c r="C265" s="13" t="s">
         <v>790</v>
       </c>
-      <c r="D265" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E265" s="16"/>
-      <c r="F265" s="17" t="s">
+      <c r="D265" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E265" s="14"/>
+      <c r="F265" s="15" t="s">
         <v>791</v>
       </c>
     </row>
     <row r="266" spans="1:6">
-      <c r="A266" s="13">
+      <c r="A266" s="11">
         <v>259</v>
       </c>
-      <c r="B266" s="14" t="s">
+      <c r="B266" s="12" t="s">
         <v>792</v>
       </c>
-      <c r="C266" s="15" t="s">
+      <c r="C266" s="13" t="s">
         <v>793</v>
       </c>
-      <c r="D266" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E266" s="16"/>
-      <c r="F266" s="17" t="s">
+      <c r="D266" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E266" s="14"/>
+      <c r="F266" s="15" t="s">
         <v>794</v>
       </c>
     </row>
     <row r="267" spans="1:6">
-      <c r="A267" s="13">
+      <c r="A267" s="11">
         <v>260</v>
       </c>
-      <c r="B267" s="14" t="s">
+      <c r="B267" s="12" t="s">
         <v>795</v>
       </c>
-      <c r="C267" s="15" t="s">
+      <c r="C267" s="13" t="s">
         <v>796</v>
       </c>
-      <c r="D267" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E267" s="16"/>
-      <c r="F267" s="17" t="s">
+      <c r="D267" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E267" s="14"/>
+      <c r="F267" s="15" t="s">
         <v>797</v>
       </c>
     </row>
     <row r="268" spans="1:6">
-      <c r="A268" s="13">
+      <c r="A268" s="11">
         <v>261</v>
       </c>
-      <c r="B268" s="14" t="s">
+      <c r="B268" s="12" t="s">
         <v>798</v>
       </c>
-      <c r="C268" s="15" t="s">
+      <c r="C268" s="13" t="s">
         <v>799</v>
       </c>
-      <c r="D268" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E268" s="16"/>
-      <c r="F268" s="17" t="s">
+      <c r="D268" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E268" s="14"/>
+      <c r="F268" s="15" t="s">
         <v>800</v>
       </c>
     </row>
     <row r="269" spans="1:6">
-      <c r="A269" s="13">
+      <c r="A269" s="11">
         <v>262</v>
       </c>
-      <c r="B269" s="14" t="s">
+      <c r="B269" s="12" t="s">
         <v>801</v>
       </c>
-      <c r="C269" s="15" t="s">
+      <c r="C269" s="13" t="s">
         <v>802</v>
       </c>
-      <c r="D269" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E269" s="16"/>
-      <c r="F269" s="17" t="s">
+      <c r="D269" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E269" s="14"/>
+      <c r="F269" s="15" t="s">
         <v>803</v>
       </c>
     </row>
     <row r="270" spans="1:6">
-      <c r="A270" s="13">
+      <c r="A270" s="11">
         <v>263</v>
       </c>
-      <c r="B270" s="14" t="s">
+      <c r="B270" s="12" t="s">
         <v>804</v>
       </c>
-      <c r="C270" s="15" t="s">
+      <c r="C270" s="13" t="s">
         <v>805</v>
       </c>
-      <c r="D270" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E270" s="16"/>
-      <c r="F270" s="17" t="s">
+      <c r="D270" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E270" s="14"/>
+      <c r="F270" s="15" t="s">
         <v>806</v>
       </c>
     </row>
     <row r="271" spans="1:6">
-      <c r="A271" s="13">
+      <c r="A271" s="11">
         <v>264</v>
       </c>
-      <c r="B271" s="14" t="s">
+      <c r="B271" s="12" t="s">
         <v>807</v>
       </c>
-      <c r="C271" s="15" t="s">
+      <c r="C271" s="13" t="s">
         <v>808</v>
       </c>
-      <c r="D271" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E271" s="16"/>
-      <c r="F271" s="17" t="s">
+      <c r="D271" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E271" s="14"/>
+      <c r="F271" s="15" t="s">
         <v>809</v>
       </c>
     </row>
     <row r="272" spans="1:6">
-      <c r="A272" s="13">
+      <c r="A272" s="11">
         <v>265</v>
       </c>
-      <c r="B272" s="14" t="s">
+      <c r="B272" s="12" t="s">
         <v>810</v>
       </c>
-      <c r="C272" s="15" t="s">
+      <c r="C272" s="13" t="s">
         <v>811</v>
       </c>
-      <c r="D272" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E272" s="16"/>
-      <c r="F272" s="17" t="s">
+      <c r="D272" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E272" s="14"/>
+      <c r="F272" s="15" t="s">
         <v>812</v>
       </c>
     </row>
     <row r="273" spans="1:6">
-      <c r="A273" s="13">
+      <c r="A273" s="11">
         <v>266</v>
       </c>
-      <c r="B273" s="14" t="s">
+      <c r="B273" s="12" t="s">
         <v>813</v>
       </c>
-      <c r="C273" s="15" t="s">
+      <c r="C273" s="13" t="s">
         <v>814</v>
       </c>
-      <c r="D273" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E273" s="16"/>
-      <c r="F273" s="17" t="s">
+      <c r="D273" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E273" s="14"/>
+      <c r="F273" s="15" t="s">
         <v>815</v>
       </c>
     </row>
     <row r="274" spans="1:6">
-      <c r="A274" s="13">
+      <c r="A274" s="11">
         <v>267</v>
       </c>
-      <c r="B274" s="14" t="s">
+      <c r="B274" s="12" t="s">
         <v>816</v>
       </c>
-      <c r="C274" s="15" t="s">
+      <c r="C274" s="13" t="s">
         <v>817</v>
       </c>
-      <c r="D274" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E274" s="16"/>
-      <c r="F274" s="17" t="s">
+      <c r="D274" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E274" s="14"/>
+      <c r="F274" s="15" t="s">
         <v>818</v>
       </c>
     </row>
     <row r="275" spans="1:6">
-      <c r="A275" s="13">
+      <c r="A275" s="11">
         <v>268</v>
       </c>
-      <c r="B275" s="14" t="s">
+      <c r="B275" s="12" t="s">
         <v>819</v>
       </c>
-      <c r="C275" s="15" t="s">
+      <c r="C275" s="13" t="s">
         <v>820</v>
       </c>
-      <c r="D275" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E275" s="16"/>
-      <c r="F275" s="17" t="s">
+      <c r="D275" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E275" s="14"/>
+      <c r="F275" s="15" t="s">
         <v>821</v>
       </c>
     </row>
     <row r="276" spans="1:6">
-      <c r="A276" s="13">
+      <c r="A276" s="11">
         <v>269</v>
       </c>
-      <c r="B276" s="14" t="s">
+      <c r="B276" s="12" t="s">
         <v>822</v>
       </c>
-      <c r="C276" s="15" t="s">
+      <c r="C276" s="13" t="s">
         <v>823</v>
       </c>
-      <c r="D276" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E276" s="16"/>
-      <c r="F276" s="17" t="s">
+      <c r="D276" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E276" s="14"/>
+      <c r="F276" s="15" t="s">
         <v>824</v>
       </c>
     </row>
     <row r="277" spans="1:6">
-      <c r="A277" s="13">
+      <c r="A277" s="11">
         <v>270</v>
       </c>
-      <c r="B277" s="14" t="s">
+      <c r="B277" s="12" t="s">
         <v>825</v>
       </c>
-      <c r="C277" s="15" t="s">
+      <c r="C277" s="13" t="s">
         <v>826</v>
       </c>
-      <c r="D277" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E277" s="16"/>
-      <c r="F277" s="17" t="s">
+      <c r="D277" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E277" s="14"/>
+      <c r="F277" s="15" t="s">
         <v>827</v>
       </c>
     </row>
     <row r="278" spans="1:6">
-      <c r="A278" s="13">
+      <c r="A278" s="11">
         <v>271</v>
       </c>
-      <c r="B278" s="14" t="s">
+      <c r="B278" s="12" t="s">
         <v>828</v>
       </c>
-      <c r="C278" s="15" t="s">
+      <c r="C278" s="13" t="s">
         <v>829</v>
       </c>
-      <c r="D278" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E278" s="16"/>
-      <c r="F278" s="17" t="s">
+      <c r="D278" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E278" s="14"/>
+      <c r="F278" s="15" t="s">
         <v>830</v>
       </c>
     </row>
     <row r="279" spans="1:6">
-      <c r="A279" s="13">
+      <c r="A279" s="11">
         <v>272</v>
       </c>
-      <c r="B279" s="14" t="s">
+      <c r="B279" s="12" t="s">
         <v>831</v>
       </c>
-      <c r="C279" s="15" t="s">
+      <c r="C279" s="13" t="s">
         <v>832</v>
       </c>
-      <c r="D279" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E279" s="16"/>
-      <c r="F279" s="17" t="s">
+      <c r="D279" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E279" s="14"/>
+      <c r="F279" s="15" t="s">
         <v>833</v>
       </c>
     </row>
     <row r="280" spans="1:6">
-      <c r="A280" s="13">
+      <c r="A280" s="11">
         <v>273</v>
       </c>
-      <c r="B280" s="14" t="s">
+      <c r="B280" s="12" t="s">
         <v>834</v>
       </c>
-      <c r="C280" s="15" t="s">
+      <c r="C280" s="13" t="s">
         <v>835</v>
       </c>
-      <c r="D280" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E280" s="16"/>
-      <c r="F280" s="17" t="s">
+      <c r="D280" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E280" s="14"/>
+      <c r="F280" s="15" t="s">
         <v>836</v>
       </c>
     </row>
     <row r="281" spans="1:6">
-      <c r="A281" s="13">
+      <c r="A281" s="11">
         <v>274</v>
       </c>
-      <c r="B281" s="14" t="s">
+      <c r="B281" s="12" t="s">
         <v>837</v>
       </c>
-      <c r="C281" s="15" t="s">
+      <c r="C281" s="13" t="s">
         <v>838</v>
       </c>
-      <c r="D281" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E281" s="16"/>
-      <c r="F281" s="17" t="s">
+      <c r="D281" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E281" s="14"/>
+      <c r="F281" s="15" t="s">
         <v>839</v>
       </c>
     </row>
     <row r="282" spans="1:6">
-      <c r="A282" s="13">
+      <c r="A282" s="11">
         <v>275</v>
       </c>
-      <c r="B282" s="14" t="s">
+      <c r="B282" s="12" t="s">
         <v>840</v>
       </c>
-      <c r="C282" s="15" t="s">
+      <c r="C282" s="13" t="s">
         <v>841</v>
       </c>
-      <c r="D282" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E282" s="16"/>
-      <c r="F282" s="17" t="s">
+      <c r="D282" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E282" s="14"/>
+      <c r="F282" s="15" t="s">
         <v>842</v>
       </c>
     </row>
     <row r="283" spans="1:6">
-      <c r="A283" s="13">
+      <c r="A283" s="11">
         <v>276</v>
       </c>
-      <c r="B283" s="14" t="s">
+      <c r="B283" s="12" t="s">
         <v>843</v>
       </c>
-      <c r="C283" s="15" t="s">
+      <c r="C283" s="13" t="s">
         <v>844</v>
       </c>
-      <c r="D283" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E283" s="16"/>
-      <c r="F283" s="17" t="s">
+      <c r="D283" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E283" s="14"/>
+      <c r="F283" s="15" t="s">
         <v>845</v>
       </c>
     </row>
     <row r="284" spans="1:6">
-      <c r="A284" s="13">
+      <c r="A284" s="11">
         <v>277</v>
       </c>
-      <c r="B284" s="14" t="s">
+      <c r="B284" s="12" t="s">
         <v>846</v>
       </c>
-      <c r="C284" s="15" t="s">
+      <c r="C284" s="13" t="s">
         <v>847</v>
       </c>
-      <c r="D284" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E284" s="16"/>
-      <c r="F284" s="17" t="s">
+      <c r="D284" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E284" s="14"/>
+      <c r="F284" s="15" t="s">
         <v>848</v>
       </c>
     </row>
     <row r="285" spans="1:6">
-      <c r="A285" s="13">
+      <c r="A285" s="11">
         <v>278</v>
       </c>
-      <c r="B285" s="14" t="s">
+      <c r="B285" s="12" t="s">
         <v>849</v>
       </c>
-      <c r="C285" s="15" t="s">
+      <c r="C285" s="13" t="s">
         <v>850</v>
       </c>
-      <c r="D285" s="15" t="s">
+      <c r="D285" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E285" s="16"/>
-      <c r="F285" s="17" t="s">
+      <c r="E285" s="14"/>
+      <c r="F285" s="15" t="s">
         <v>851</v>
       </c>
     </row>
     <row r="286" spans="1:6">
-      <c r="A286" s="13">
+      <c r="A286" s="11">
         <v>279</v>
       </c>
-      <c r="B286" s="14" t="s">
+      <c r="B286" s="12" t="s">
         <v>852</v>
       </c>
-      <c r="C286" s="15" t="s">
+      <c r="C286" s="13" t="s">
         <v>853</v>
       </c>
-      <c r="D286" s="15" t="s">
+      <c r="D286" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E286" s="16"/>
-      <c r="F286" s="17" t="s">
+      <c r="E286" s="14"/>
+      <c r="F286" s="15" t="s">
         <v>854</v>
       </c>
     </row>
     <row r="287" spans="1:6">
-      <c r="A287" s="13">
+      <c r="A287" s="11">
         <v>280</v>
       </c>
-      <c r="B287" s="14" t="s">
+      <c r="B287" s="12" t="s">
         <v>855</v>
       </c>
-      <c r="C287" s="15" t="s">
+      <c r="C287" s="13" t="s">
         <v>856</v>
       </c>
-      <c r="D287" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E287" s="16"/>
-      <c r="F287" s="17" t="s">
+      <c r="D287" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E287" s="14"/>
+      <c r="F287" s="15" t="s">
         <v>857</v>
       </c>
     </row>
     <row r="288" spans="1:6">
-      <c r="A288" s="13">
+      <c r="A288" s="11">
         <v>281</v>
       </c>
-      <c r="B288" s="14" t="s">
+      <c r="B288" s="12" t="s">
         <v>858</v>
       </c>
-      <c r="C288" s="15" t="s">
+      <c r="C288" s="13" t="s">
         <v>859</v>
       </c>
-      <c r="D288" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E288" s="16"/>
-      <c r="F288" s="17" t="s">
+      <c r="D288" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E288" s="14"/>
+      <c r="F288" s="15" t="s">
         <v>860</v>
       </c>
     </row>
     <row r="289" spans="1:7">
-      <c r="A289" s="13">
+      <c r="A289" s="11">
         <v>282</v>
       </c>
-      <c r="B289" s="14" t="s">
+      <c r="B289" s="12" t="s">
         <v>861</v>
       </c>
-      <c r="C289" s="15" t="s">
+      <c r="C289" s="13" t="s">
         <v>862</v>
       </c>
-      <c r="D289" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E289" s="16"/>
-      <c r="F289" s="17" t="s">
+      <c r="D289" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E289" s="14"/>
+      <c r="F289" s="15" t="s">
         <v>863</v>
       </c>
     </row>
     <row r="290" spans="1:7">
-      <c r="A290" s="13">
+      <c r="A290" s="11">
         <v>283</v>
       </c>
-      <c r="B290" s="14" t="s">
+      <c r="B290" s="12" t="s">
         <v>864</v>
       </c>
-      <c r="C290" s="15" t="s">
+      <c r="C290" s="13" t="s">
         <v>865</v>
       </c>
-      <c r="D290" s="15" t="s">
+      <c r="D290" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E290" s="16"/>
-      <c r="F290" s="17" t="s">
+      <c r="E290" s="14"/>
+      <c r="F290" s="15" t="s">
         <v>866</v>
       </c>
     </row>
     <row r="291" spans="1:7">
-      <c r="A291" s="13">
+      <c r="A291" s="11">
         <v>284</v>
       </c>
-      <c r="B291" s="14" t="s">
+      <c r="B291" s="12" t="s">
         <v>867</v>
       </c>
-      <c r="C291" s="15" t="s">
+      <c r="C291" s="13" t="s">
         <v>867</v>
       </c>
-      <c r="D291" s="15" t="s">
+      <c r="D291" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E291" s="16"/>
-      <c r="F291" s="17" t="s">
+      <c r="E291" s="14"/>
+      <c r="F291" s="15" t="s">
         <v>868</v>
       </c>
     </row>
     <row r="292" spans="1:7">
-      <c r="A292" s="13">
+      <c r="A292" s="11">
         <v>285</v>
       </c>
-      <c r="B292" s="14" t="s">
+      <c r="B292" s="12" t="s">
         <v>869</v>
       </c>
-      <c r="C292" s="15" t="s">
+      <c r="C292" s="13" t="s">
         <v>870</v>
       </c>
-      <c r="D292" s="15" t="s">
+      <c r="D292" s="13" t="s">
         <v>125</v>
       </c>
-      <c r="E292" s="16"/>
-      <c r="F292" s="17" t="s">
+      <c r="E292" s="14"/>
+      <c r="F292" s="15" t="s">
         <v>871</v>
       </c>
     </row>
     <row r="293" spans="1:7">
-      <c r="A293" s="13">
+      <c r="A293" s="11">
         <v>286</v>
       </c>
-      <c r="B293" s="14" t="s">
+      <c r="B293" s="12" t="s">
         <v>872</v>
       </c>
-      <c r="C293" s="15" t="s">
+      <c r="C293" s="13" t="s">
         <v>872</v>
       </c>
-      <c r="D293" s="15" t="s">
+      <c r="D293" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E293" s="16"/>
-      <c r="F293" s="17" t="s">
+      <c r="E293" s="14"/>
+      <c r="F293" s="15" t="s">
         <v>873</v>
       </c>
     </row>
@@ -8809,11 +9007,15 @@
       <c r="A294" s="1">
         <v>299</v>
       </c>
-      <c r="B294" s="28" t="s">
+      <c r="B294" s="26" t="s">
         <v>874</v>
       </c>
-      <c r="C294" s="29"/>
-      <c r="D294" s="3"/>
+      <c r="C294" s="27" t="s">
+        <v>892</v>
+      </c>
+      <c r="D294" s="13" t="s">
+        <v>16</v>
+      </c>
       <c r="F294" s="2" t="s">
         <v>875</v>
       </c>
@@ -8826,8 +9028,12 @@
       <c r="B295" s="1" t="s">
         <v>876</v>
       </c>
-      <c r="C295" s="4"/>
-      <c r="D295" s="3"/>
+      <c r="C295" s="27" t="s">
+        <v>891</v>
+      </c>
+      <c r="D295" s="13" t="s">
+        <v>16</v>
+      </c>
       <c r="F295" s="2" t="s">
         <v>877</v>
       </c>
@@ -8837,11 +9043,15 @@
       <c r="A296" s="1">
         <v>301</v>
       </c>
-      <c r="B296" s="28" t="s">
+      <c r="B296" s="26" t="s">
         <v>878</v>
       </c>
-      <c r="C296" s="29"/>
-      <c r="D296" s="3"/>
+      <c r="C296" s="27" t="s">
+        <v>893</v>
+      </c>
+      <c r="D296" s="13" t="s">
+        <v>16</v>
+      </c>
       <c r="F296" s="2" t="s">
         <v>879</v>
       </c>
@@ -8851,11 +9061,15 @@
       <c r="A297" s="1">
         <v>302</v>
       </c>
-      <c r="B297" s="28" t="s">
+      <c r="B297" s="26" t="s">
         <v>880</v>
       </c>
-      <c r="C297" s="29"/>
-      <c r="D297" s="3"/>
+      <c r="C297" s="27" t="s">
+        <v>880</v>
+      </c>
+      <c r="D297" s="13" t="s">
+        <v>16</v>
+      </c>
       <c r="F297" s="2" t="s">
         <v>881</v>
       </c>
@@ -8865,11 +9079,15 @@
       <c r="A298" s="1">
         <v>303</v>
       </c>
-      <c r="B298" s="28" t="s">
+      <c r="B298" s="26" t="s">
         <v>882</v>
       </c>
-      <c r="C298" s="29"/>
-      <c r="D298" s="3"/>
+      <c r="C298" s="27" t="s">
+        <v>918</v>
+      </c>
+      <c r="D298" s="13" t="s">
+        <v>16</v>
+      </c>
       <c r="F298" s="2" t="s">
         <v>883</v>
       </c>
@@ -8879,11 +9097,15 @@
       <c r="A299" s="1">
         <v>304</v>
       </c>
-      <c r="B299" s="28" t="s">
+      <c r="B299" s="26" t="s">
         <v>884</v>
       </c>
-      <c r="C299" s="29"/>
-      <c r="D299" s="3"/>
+      <c r="C299" s="27" t="s">
+        <v>895</v>
+      </c>
+      <c r="D299" s="13" t="s">
+        <v>16</v>
+      </c>
       <c r="F299" s="2" t="s">
         <v>885</v>
       </c>
@@ -8893,15 +9115,39 @@
       <c r="A300" s="1">
         <v>305</v>
       </c>
-      <c r="B300" s="28" t="s">
+      <c r="B300" s="26" t="s">
         <v>886</v>
       </c>
-      <c r="C300" s="29"/>
-      <c r="D300" s="3"/>
+      <c r="C300" s="27" t="s">
+        <v>894</v>
+      </c>
+      <c r="D300" s="13" t="s">
+        <v>16</v>
+      </c>
       <c r="F300" s="2" t="s">
         <v>887</v>
       </c>
       <c r="G300" s="2"/>
+    </row>
+    <row r="301" spans="1:7" ht="15" thickBot="1">
+      <c r="C301" s="43" t="s">
+        <v>248</v>
+      </c>
+      <c r="F301" t="str">
+        <f>VLOOKUP(C301,Diccionario!$C$7:$F$300,4,FALSE)</f>
+        <v>Promedio mensual de ingresos provenientes de suscontrapartes en los últimos 12 meses.</v>
+      </c>
+    </row>
+    <row r="302" spans="1:7">
+      <c r="B302" s="3" t="s">
+        <v>889</v>
+      </c>
+      <c r="C302" s="27" t="s">
+        <v>922</v>
+      </c>
+      <c r="F302" s="2" t="s">
+        <v>923</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -8911,15 +9157,1146 @@
     <mergeCell ref="C6:G6"/>
   </mergeCells>
   <conditionalFormatting sqref="A6">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
       <formula>"EN CONSTRUCCION"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
       <formula>"CONSTRUIDO"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A7 E9:E11">
-    <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
+      <formula>"PENDIENTE"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27DCCAE6-0E9B-4753-90E8-43F48446DEA8}">
+  <dimension ref="A1:C33"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="1" width="46.26953125" customWidth="1"/>
+    <col min="2" max="2" width="61.81640625" customWidth="1"/>
+    <col min="3" max="3" width="29.453125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="15" thickBot="1">
+      <c r="A2" s="12" t="s">
+        <v>559</v>
+      </c>
+      <c r="B2" s="43" t="str">
+        <f>VLOOKUP(A2,Diccionario!$C$7:$F$300,4,FALSE)</f>
+        <v>Cantidad de cargos  en los últimos 3 meses.</v>
+      </c>
+      <c r="C2" s="43"/>
+    </row>
+    <row r="3" spans="1:3" ht="15" thickBot="1">
+      <c r="A3" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="B3" s="43" t="str">
+        <f>VLOOKUP(A3,Diccionario!$C$7:$F$300,4,FALSE)</f>
+        <v>Monto de pasivos del cliente en moneda de tipo soles.</v>
+      </c>
+      <c r="C3" s="43"/>
+    </row>
+    <row r="4" spans="1:3" ht="15" thickBot="1">
+      <c r="A4" s="12" t="s">
+        <v>891</v>
+      </c>
+      <c r="B4" s="43" t="str">
+        <f>VLOOKUP(A4,Diccionario!$C$7:$F$300,4,FALSE)</f>
+        <v> Esta variable calcula la relación entre el pasivo total en soles y los ingresos totales (abonos) en los últimos 6 meses. Es un indicador de la capacidad de la empresa para cubrir sus pasivos con los ingresos generados.</v>
+      </c>
+      <c r="C4" s="43"/>
+    </row>
+    <row r="5" spans="1:3" ht="15" thickBot="1">
+      <c r="A5" s="12" t="s">
+        <v>445</v>
+      </c>
+      <c r="B5" s="43" t="str">
+        <f>VLOOKUP(A5,Diccionario!$C$7:$F$300,4,FALSE)</f>
+        <v>Promedio mensual de cantidad de abonos totales en los últimos 3 meses.</v>
+      </c>
+      <c r="C5" s="43"/>
+    </row>
+    <row r="6" spans="1:3" ht="15" thickBot="1">
+      <c r="A6" s="12" t="s">
+        <v>493</v>
+      </c>
+      <c r="B6" s="43" t="str">
+        <f>VLOOKUP(A6,Diccionario!$C$7:$F$300,4,FALSE)</f>
+        <v>Monto total de abonos en efectivo en los últimos 6 meses.</v>
+      </c>
+      <c r="C6" s="43"/>
+    </row>
+    <row r="7" spans="1:3" ht="15" thickBot="1">
+      <c r="A7" s="12" t="s">
+        <v>856</v>
+      </c>
+      <c r="B7" s="43" t="str">
+        <f>VLOOKUP(A7,Diccionario!$C$7:$F$300,4,FALSE)</f>
+        <v>Años de relación comercial con el cliente</v>
+      </c>
+      <c r="C7" s="43"/>
+    </row>
+    <row r="8" spans="1:3" ht="15" thickBot="1">
+      <c r="A8" s="12" t="s">
+        <v>634</v>
+      </c>
+      <c r="B8" s="43" t="str">
+        <f>VLOOKUP(A8,Diccionario!$C$7:$F$300,4,FALSE)</f>
+        <v>Total egresado en efectivo en los ultimos 6 meses.</v>
+      </c>
+      <c r="C8" s="43"/>
+    </row>
+    <row r="9" spans="1:3" ht="15" thickBot="1">
+      <c r="A9" s="52" t="s">
+        <v>918</v>
+      </c>
+      <c r="B9" s="43" t="str">
+        <f>VLOOKUP(A9,Diccionario!$C$7:$F$300,4,FALSE)</f>
+        <v>Este ratio mide la aceleración o desaceleración de los egresos (cargos) en el último mes en comparación con el promedio mensual de los últimos 6 meses. Es útil para identificar cambios recientes en el comportamiento de egresos.</v>
+      </c>
+      <c r="C9" s="43"/>
+    </row>
+    <row r="10" spans="1:3" ht="15" thickBot="1">
+      <c r="A10" s="12" t="s">
+        <v>670</v>
+      </c>
+      <c r="B10" s="43" t="str">
+        <f>VLOOKUP(A10,Diccionario!$C$7:$F$300,4,FALSE)</f>
+        <v>Número de meses, dentro de los últimos 12 meses, en que no se registraron cargos.</v>
+      </c>
+      <c r="C10" s="43"/>
+    </row>
+    <row r="11" spans="1:3" ht="15" thickBot="1">
+      <c r="A11" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="B11" s="43" t="str">
+        <f>VLOOKUP(A11,Diccionario!$C$7:$F$300,4,FALSE)</f>
+        <v>Cantidad total de alertas históricas relacionadas al cliente.</v>
+      </c>
+      <c r="C11" s="43"/>
+    </row>
+    <row r="12" spans="1:3" ht="15" thickBot="1">
+      <c r="A12" s="12" t="s">
+        <v>460</v>
+      </c>
+      <c r="B12" s="43" t="str">
+        <f>VLOOKUP(A12,Diccionario!$C$7:$F$300,4,FALSE)</f>
+        <v>Ratio de cantidad de abonos en efectivo respecto a la cantidad total de abonos, considerando ambos valores acumulados en los últimos 3 meses</v>
+      </c>
+      <c r="C12" s="43"/>
+    </row>
+    <row r="13" spans="1:3" ht="15" thickBot="1">
+      <c r="A13" s="12" t="s">
+        <v>643</v>
+      </c>
+      <c r="B13" s="43" t="str">
+        <f>VLOOKUP(A13,Diccionario!$C$7:$F$300,4,FALSE)</f>
+        <v>Promedio de los cargos totales en los últimos 3 meses.</v>
+      </c>
+      <c r="C13" s="43"/>
+    </row>
+    <row r="14" spans="1:3" ht="15" thickBot="1">
+      <c r="A14" s="12" t="s">
+        <v>655</v>
+      </c>
+      <c r="B14" s="43" t="str">
+        <f>VLOOKUP(A14,Diccionario!$C$7:$F$300,4,FALSE)</f>
+        <v>Porcentaje del monto de cargos realizados en efectivo sobre el total de cargos del último mes.</v>
+      </c>
+      <c r="C14" s="43"/>
+    </row>
+    <row r="15" spans="1:3" ht="15" thickBot="1">
+      <c r="A15" s="12" t="s">
+        <v>457</v>
+      </c>
+      <c r="B15" s="43" t="str">
+        <f>VLOOKUP(A15,Diccionario!$C$7:$F$300,4,FALSE)</f>
+        <v>Ratio de cantida de abonos en efectivo respecto a la cantidad total de abonos, considerando ambos valores acumulados en el último mes.</v>
+      </c>
+      <c r="C15" s="43"/>
+    </row>
+    <row r="16" spans="1:3" ht="15" thickBot="1">
+      <c r="A16" s="12" t="s">
+        <v>894</v>
+      </c>
+      <c r="B16" s="43" t="str">
+        <f>VLOOKUP(A16,Diccionario!$C$7:$F$300,4,FALSE)</f>
+        <v>Esta variable calcula la relación entre la cantidad de reportes de operaciones sospechosas (ROS) históricos y el número total de transacciones de egresos en los últimos 3 meses. Es un indicador de riesgo asociado a las operaciones recientes.</v>
+      </c>
+      <c r="C16" s="43"/>
+    </row>
+    <row r="17" spans="1:3" ht="15" thickBot="1">
+      <c r="A17" s="12" t="s">
+        <v>888</v>
+      </c>
+      <c r="B17" s="43" t="s">
+        <v>920</v>
+      </c>
+      <c r="C17" s="43"/>
+    </row>
+    <row r="18" spans="1:3" ht="15" thickBot="1">
+      <c r="A18" s="12" t="s">
+        <v>733</v>
+      </c>
+      <c r="B18" s="43" t="str">
+        <f>VLOOKUP(A18,Diccionario!$C$7:$F$300,4,FALSE)</f>
+        <v>Monto total recibido desde el exterior en los últimos 12 meses.</v>
+      </c>
+      <c r="C18" s="43"/>
+    </row>
+    <row r="19" spans="1:3" ht="15" thickBot="1">
+      <c r="A19" s="12" t="s">
+        <v>895</v>
+      </c>
+      <c r="B19" s="43" t="str">
+        <f>VLOOKUP(A19,Diccionario!$C$7:$F$300,4,FALSE)</f>
+        <v>Esta variable mide la proporción de ingresos provenientes del exterior en relación con los ingresos totales (abonos) en los últimos 12 meses. Es un indicador de la dependencia de la empresa en ingresos internacionales.</v>
+      </c>
+      <c r="C19" s="43"/>
+    </row>
+    <row r="20" spans="1:3" ht="15" thickBot="1">
+      <c r="A20" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="B20" s="43" t="str">
+        <f>VLOOKUP(A20,Diccionario!$C$7:$F$300,4,FALSE)</f>
+        <v>Monto máximo de egreso en un solo mes de una o más contrapartes dentro de los últimos 12 meses.</v>
+      </c>
+      <c r="C20" s="43"/>
+    </row>
+    <row r="21" spans="1:3" ht="15" thickBot="1">
+      <c r="A21" s="12" t="s">
+        <v>266</v>
+      </c>
+      <c r="B21" s="43" t="str">
+        <f>VLOOKUP(A21,Diccionario!$C$7:$F$300,4,FALSE)</f>
+        <v>Promedio mensual de egresos hacia contrapartes en los últimos 12 meses.</v>
+      </c>
+      <c r="C21" s="43"/>
+    </row>
+    <row r="22" spans="1:3" ht="15" thickBot="1">
+      <c r="A22" s="12" t="s">
+        <v>721</v>
+      </c>
+      <c r="B22" s="43" t="str">
+        <f>VLOOKUP(A22,Diccionario!$C$7:$F$300,4,FALSE)</f>
+        <v>Monto total enviado al exterior en los últimos 12 meses.</v>
+      </c>
+      <c r="C22" s="43"/>
+    </row>
+    <row r="23" spans="1:3" ht="15" thickBot="1">
+      <c r="A23" s="27" t="s">
+        <v>895</v>
+      </c>
+      <c r="B23" s="43" t="str">
+        <f>VLOOKUP(A23,Diccionario!$C$7:$F$300,4,FALSE)</f>
+        <v>Esta variable mide la proporción de ingresos provenientes del exterior en relación con los ingresos totales (abonos) en los últimos 12 meses. Es un indicador de la dependencia de la empresa en ingresos internacionales.</v>
+      </c>
+      <c r="C23" s="43"/>
+    </row>
+    <row r="24" spans="1:3" ht="15" thickBot="1">
+      <c r="A24" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="B24" s="43" t="str">
+        <f>VLOOKUP(A24,Diccionario!$C$7:$F$300,4,FALSE)</f>
+        <v>Número total de ROS en los que el cliente ha estado involucrado.</v>
+      </c>
+      <c r="C24" s="43"/>
+    </row>
+    <row r="25" spans="1:3" ht="15" thickBot="1">
+      <c r="A25" s="12" t="s">
+        <v>896</v>
+      </c>
+      <c r="B25" t="s">
+        <v>925</v>
+      </c>
+      <c r="C25" s="43"/>
+    </row>
+    <row r="26" spans="1:3" ht="15" thickBot="1">
+      <c r="A26" s="12" t="s">
+        <v>149</v>
+      </c>
+      <c r="B26" s="43" t="str">
+        <f>VLOOKUP(A26,Diccionario!$C$7:$F$300,4,FALSE)</f>
+        <v>Indicador si el cliente ha generado alguna alerta PLAFT en los últimos 12 meses.</v>
+      </c>
+      <c r="C26" s="43"/>
+    </row>
+    <row r="27" spans="1:3" ht="15" thickBot="1">
+      <c r="A27" s="12" t="s">
+        <v>850</v>
+      </c>
+      <c r="B27" s="43" t="str">
+        <f>VLOOKUP(A27,Diccionario!$C$7:$F$300,4,FALSE)</f>
+        <v>Si el monto total abonos del último mes es mayor al monto promedio total abonos de los últimos 5 meses coloco 1, caso contrario 0</v>
+      </c>
+      <c r="C27" s="43"/>
+    </row>
+    <row r="28" spans="1:3" ht="15" thickBot="1">
+      <c r="A28" s="12" t="s">
+        <v>248</v>
+      </c>
+      <c r="B28" s="43" t="str">
+        <f>VLOOKUP(A28,Diccionario!$C$7:$F$300,4,FALSE)</f>
+        <v>Promedio mensual de ingresos provenientes de suscontrapartes en los últimos 12 meses.</v>
+      </c>
+      <c r="C28" s="43"/>
+    </row>
+    <row r="29" spans="1:3" ht="15" thickBot="1">
+      <c r="A29" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="B29" s="43" t="str">
+        <f>VLOOKUP(A29,Diccionario!$C$7:$F$300,4,FALSE)</f>
+        <v>Número total de noticias negativas registradas del cliente.</v>
+      </c>
+      <c r="C29" s="43"/>
+    </row>
+    <row r="30" spans="1:3" ht="15" thickBot="1">
+      <c r="A30" s="12" t="s">
+        <v>890</v>
+      </c>
+      <c r="B30" s="43" t="s">
+        <v>924</v>
+      </c>
+      <c r="C30" s="43"/>
+    </row>
+    <row r="31" spans="1:3" ht="15" thickBot="1">
+      <c r="A31" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="B31" s="43" t="str">
+        <f>VLOOKUP(A31,Diccionario!$C$7:$F$300,4,FALSE)</f>
+        <v>Monto de facturación declarado del cliente, según SUNAT</v>
+      </c>
+      <c r="C31" s="43"/>
+    </row>
+    <row r="32" spans="1:3" ht="15" thickBot="1">
+      <c r="A32" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="B32" s="43" t="s">
+        <v>921</v>
+      </c>
+      <c r="C32" s="43"/>
+    </row>
+    <row r="33" spans="1:3" ht="15" thickBot="1">
+      <c r="A33" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="B33" s="43" t="str">
+        <f>VLOOKUP(A33,Diccionario!$C$7:$F$300,4,FALSE)</f>
+        <v>Identificador del sector asignado al cliente</v>
+      </c>
+      <c r="C33" s="43"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{374C8810-FB16-41CA-85D2-70D0F0D810E2}">
+  <dimension ref="A1:G36"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="1" width="11.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.36328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.90625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23.7265625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" s="44" t="s">
+        <v>897</v>
+      </c>
+      <c r="B1" s="44" t="s">
+        <v>898</v>
+      </c>
+      <c r="C1" s="45" t="s">
+        <v>899</v>
+      </c>
+      <c r="D1" s="45" t="s">
+        <v>900</v>
+      </c>
+      <c r="E1" s="45" t="s">
+        <v>901</v>
+      </c>
+      <c r="F1" s="45" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1" s="45" t="s">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="46" t="s">
+        <v>903</v>
+      </c>
+      <c r="B2" s="47" t="s">
+        <v>904</v>
+      </c>
+      <c r="C2" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="48"/>
+      <c r="G2" s="13" t="s">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="46" t="s">
+        <v>903</v>
+      </c>
+      <c r="B3" s="47" t="s">
+        <v>904</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" s="15" t="s">
+        <v>906</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" s="13" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="46" t="s">
+        <v>903</v>
+      </c>
+      <c r="B4" s="47" t="s">
+        <v>904</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>907</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4" s="13" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="46" t="s">
+        <v>903</v>
+      </c>
+      <c r="B5" s="47" t="s">
+        <v>904</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5" s="13" t="s">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="46" t="s">
+        <v>903</v>
+      </c>
+      <c r="B6" s="47" t="s">
+        <v>909</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>910</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>911</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="F6" s="48"/>
+      <c r="G6" s="13" t="s">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="46" t="s">
+        <v>903</v>
+      </c>
+      <c r="B7" s="47" t="s">
+        <v>904</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="F7" s="48"/>
+      <c r="G7" s="13" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="46" t="s">
+        <v>903</v>
+      </c>
+      <c r="B8" s="47" t="s">
+        <v>904</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>874</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>892</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="F8" s="48"/>
+      <c r="G8" s="49" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="46" t="s">
+        <v>903</v>
+      </c>
+      <c r="B9" s="47" t="s">
+        <v>904</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="D9" s="15" t="s">
+        <v>161</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="F9" s="48"/>
+      <c r="G9" s="15" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="46" t="s">
+        <v>903</v>
+      </c>
+      <c r="B10" s="47" t="s">
+        <v>904</v>
+      </c>
+      <c r="C10" s="50" t="s">
+        <v>492</v>
+      </c>
+      <c r="D10" s="50" t="s">
+        <v>493</v>
+      </c>
+      <c r="E10" s="51" t="s">
+        <v>88</v>
+      </c>
+      <c r="F10" s="48"/>
+      <c r="G10" s="15" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="46" t="s">
+        <v>903</v>
+      </c>
+      <c r="B11" s="47" t="s">
+        <v>904</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="D11" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="F11" s="48"/>
+      <c r="G11" s="15" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="46" t="s">
+        <v>903</v>
+      </c>
+      <c r="B12" s="47" t="s">
+        <v>904</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="F12" s="48"/>
+      <c r="G12" s="15" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="46" t="s">
+        <v>903</v>
+      </c>
+      <c r="B13" s="47" t="s">
+        <v>904</v>
+      </c>
+      <c r="C13" s="15" t="s">
+        <v>876</v>
+      </c>
+      <c r="D13" s="15" t="s">
+        <v>891</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>913</v>
+      </c>
+      <c r="F13" s="48"/>
+      <c r="G13" s="15" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="46" t="s">
+        <v>903</v>
+      </c>
+      <c r="B14" s="47" t="s">
+        <v>904</v>
+      </c>
+      <c r="C14" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="D14" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="F14" s="48"/>
+      <c r="G14" s="15" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="46" t="s">
+        <v>903</v>
+      </c>
+      <c r="B15" s="47" t="s">
+        <v>904</v>
+      </c>
+      <c r="C15" s="15" t="s">
+        <v>459</v>
+      </c>
+      <c r="D15" s="15" t="s">
+        <v>460</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="F15" s="48"/>
+      <c r="G15" s="15" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="46" t="s">
+        <v>903</v>
+      </c>
+      <c r="B16" s="47" t="s">
+        <v>904</v>
+      </c>
+      <c r="C16" s="15" t="s">
+        <v>855</v>
+      </c>
+      <c r="D16" s="15" t="s">
+        <v>856</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="F16" s="48"/>
+      <c r="G16" s="15" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="46" t="s">
+        <v>903</v>
+      </c>
+      <c r="B17" s="47" t="s">
+        <v>904</v>
+      </c>
+      <c r="C17" s="15" t="s">
+        <v>558</v>
+      </c>
+      <c r="D17" s="15" t="s">
+        <v>559</v>
+      </c>
+      <c r="E17" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="F17" s="48"/>
+      <c r="G17" s="15" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" s="46" t="s">
+        <v>903</v>
+      </c>
+      <c r="B18" s="47" t="s">
+        <v>904</v>
+      </c>
+      <c r="C18" s="15" t="s">
+        <v>886</v>
+      </c>
+      <c r="D18" s="15" t="s">
+        <v>894</v>
+      </c>
+      <c r="E18" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="F18" s="48"/>
+      <c r="G18" s="15" t="s">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="46" t="s">
+        <v>903</v>
+      </c>
+      <c r="B19" s="47" t="s">
+        <v>904</v>
+      </c>
+      <c r="C19" s="15" t="s">
+        <v>669</v>
+      </c>
+      <c r="D19" s="15" t="s">
+        <v>670</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="F19" s="48"/>
+      <c r="G19" s="15" t="s">
+        <v>915</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="46" t="s">
+        <v>903</v>
+      </c>
+      <c r="B20" s="47" t="s">
+        <v>904</v>
+      </c>
+      <c r="C20" s="15" t="s">
+        <v>878</v>
+      </c>
+      <c r="D20" s="15" t="s">
+        <v>893</v>
+      </c>
+      <c r="E20" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="F20" s="48"/>
+      <c r="G20" s="15" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" s="46" t="s">
+        <v>903</v>
+      </c>
+      <c r="B21" s="47" t="s">
+        <v>904</v>
+      </c>
+      <c r="C21" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="D21" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="E21" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="F21" s="48"/>
+      <c r="G21" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" s="46" t="s">
+        <v>903</v>
+      </c>
+      <c r="B22" s="47" t="s">
+        <v>904</v>
+      </c>
+      <c r="C22" s="15" t="s">
+        <v>633</v>
+      </c>
+      <c r="D22" s="15" t="s">
+        <v>634</v>
+      </c>
+      <c r="E22" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="F22" s="48"/>
+      <c r="G22" s="15" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" s="46" t="s">
+        <v>903</v>
+      </c>
+      <c r="B23" s="47" t="s">
+        <v>904</v>
+      </c>
+      <c r="C23" s="15" t="s">
+        <v>465</v>
+      </c>
+      <c r="D23" s="15" t="s">
+        <v>466</v>
+      </c>
+      <c r="E23" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="F23" s="48"/>
+      <c r="G23" s="15" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" s="46" t="s">
+        <v>903</v>
+      </c>
+      <c r="B24" s="47" t="s">
+        <v>904</v>
+      </c>
+      <c r="C24" s="15" t="s">
+        <v>884</v>
+      </c>
+      <c r="D24" s="15" t="s">
+        <v>895</v>
+      </c>
+      <c r="E24" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="F24" s="48"/>
+      <c r="G24" s="15" t="s">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" s="46" t="s">
+        <v>903</v>
+      </c>
+      <c r="B25" s="47" t="s">
+        <v>904</v>
+      </c>
+      <c r="C25" s="15" t="s">
+        <v>880</v>
+      </c>
+      <c r="D25" s="15" t="s">
+        <v>917</v>
+      </c>
+      <c r="E25" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="F25" s="48"/>
+      <c r="G25" s="15" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" s="46" t="s">
+        <v>903</v>
+      </c>
+      <c r="B26" s="47" t="s">
+        <v>904</v>
+      </c>
+      <c r="C26" s="15" t="s">
+        <v>148</v>
+      </c>
+      <c r="D26" s="15" t="s">
+        <v>149</v>
+      </c>
+      <c r="E26" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="F26" s="48"/>
+      <c r="G26" s="15" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" s="46" t="s">
+        <v>903</v>
+      </c>
+      <c r="B27" s="47" t="s">
+        <v>904</v>
+      </c>
+      <c r="C27" s="13" t="s">
+        <v>444</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>445</v>
+      </c>
+      <c r="E27" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="F27" s="48"/>
+      <c r="G27" s="13" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" s="46" t="s">
+        <v>903</v>
+      </c>
+      <c r="B28" s="47" t="s">
+        <v>904</v>
+      </c>
+      <c r="C28" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="E28" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="F28" s="48"/>
+      <c r="G28" s="13" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" s="46" t="s">
+        <v>903</v>
+      </c>
+      <c r="B29" s="47" t="s">
+        <v>904</v>
+      </c>
+      <c r="C29" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="D29" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="E29" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="F29" s="48"/>
+      <c r="G29" s="13" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" s="46" t="s">
+        <v>903</v>
+      </c>
+      <c r="B30" s="47" t="s">
+        <v>904</v>
+      </c>
+      <c r="C30" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="D30" s="13" t="s">
+        <v>173</v>
+      </c>
+      <c r="E30" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="F30" s="48"/>
+      <c r="G30" s="13" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" s="46" t="s">
+        <v>903</v>
+      </c>
+      <c r="B31" s="47" t="s">
+        <v>904</v>
+      </c>
+      <c r="C31" s="13" t="s">
+        <v>882</v>
+      </c>
+      <c r="D31" s="13" t="s">
+        <v>918</v>
+      </c>
+      <c r="E31" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="F31" s="48"/>
+      <c r="G31" s="13" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32" s="46" t="s">
+        <v>903</v>
+      </c>
+      <c r="B32" s="47" t="s">
+        <v>904</v>
+      </c>
+      <c r="C32" s="13" t="s">
+        <v>642</v>
+      </c>
+      <c r="D32" s="13" t="s">
+        <v>643</v>
+      </c>
+      <c r="E32" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="F32" s="48"/>
+      <c r="G32" s="13" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33" s="46" t="s">
+        <v>903</v>
+      </c>
+      <c r="B33" s="47" t="s">
+        <v>904</v>
+      </c>
+      <c r="C33" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="D33" s="13" t="s">
+        <v>164</v>
+      </c>
+      <c r="E33" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="F33" s="48"/>
+      <c r="G33" s="13" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34" s="46" t="s">
+        <v>903</v>
+      </c>
+      <c r="B34" s="47" t="s">
+        <v>904</v>
+      </c>
+      <c r="C34" s="13" t="s">
+        <v>720</v>
+      </c>
+      <c r="D34" s="13" t="s">
+        <v>721</v>
+      </c>
+      <c r="E34" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="F34" s="48"/>
+      <c r="G34" s="13" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35" s="46" t="s">
+        <v>903</v>
+      </c>
+      <c r="B35" s="47" t="s">
+        <v>904</v>
+      </c>
+      <c r="C35" s="13" t="s">
+        <v>869</v>
+      </c>
+      <c r="D35" s="13" t="s">
+        <v>870</v>
+      </c>
+      <c r="E35" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="F35" s="48"/>
+      <c r="G35" s="13" t="s">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36" s="46" t="s">
+        <v>903</v>
+      </c>
+      <c r="B36" s="47" t="s">
+        <v>904</v>
+      </c>
+      <c r="C36" s="13" t="s">
+        <v>872</v>
+      </c>
+      <c r="D36" s="13" t="s">
+        <v>872</v>
+      </c>
+      <c r="E36" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="F36" s="48"/>
+      <c r="G36" s="13" t="s">
+        <v>919</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="F3:F5">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"PENDIENTE"</formula>
     </cfRule>
   </conditionalFormatting>
